--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -607,7 +607,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1699,29 +1699,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>46266.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46268.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1748,29 +1748,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>46260.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46262.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1797,29 +1797,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46229.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46232.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2160,29 +2160,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>GRAND VENUS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9303211</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>040</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>040</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46226.29930555556</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2209,29 +2209,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46245.31875</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2258,29 +2258,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2307,29 +2307,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2344,7 +2344,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2356,26 +2356,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>46339.2625</v>
@@ -2393,7 +2393,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2405,29 +2405,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46286.5</v>
+        <v>46339.2625</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2442,7 +2442,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2454,29 +2454,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46233.6875</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2485,13 +2485,17 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="O42" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2503,29 +2507,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2540,7 +2544,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2552,29 +2556,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2583,13 +2587,17 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="O44" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>46231</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2601,29 +2609,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46242.5125</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2632,13 +2640,17 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2650,29 +2662,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46237.34375</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46286.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2681,17 +2693,13 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2713,19 +2721,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46286.25</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2734,13 +2742,17 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2752,29 +2764,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46243.01875</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2783,13 +2795,17 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="O48" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2801,29 +2817,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46286.25</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2832,17 +2848,13 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2854,29 +2866,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2891,7 +2903,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2903,29 +2915,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46235.60625</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2935,16 +2947,16 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" s="1" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2956,29 +2968,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2993,7 +3005,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3005,29 +3017,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>HESTIA LEADER</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9355226</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46226.02986111111</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46227.61805555555</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3036,13 +3048,17 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="O53" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3054,29 +3070,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3085,13 +3101,17 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="O54" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P54" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3103,29 +3123,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GRAND VENUS</t>
+          <t>GOLD XING</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9303211</t>
+          <t>9308807</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46226.29930555556</v>
+        <v>46227.39930555555</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46227.95694444444</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3134,13 +3154,17 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="O55" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P55" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3152,29 +3176,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3183,13 +3207,17 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="O56" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3201,29 +3229,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46363.2625</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3232,17 +3260,13 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>46231</v>
-      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3254,29 +3278,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>IVORY ARROW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9277838</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46226.29513888889</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46226.74652777778</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3286,16 +3310,16 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" s="1" t="n">
-        <v>46247</v>
+        <v>46227</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46247</v>
+        <v>46227</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3307,29 +3331,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>POSEIDON LEADER</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9335965</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46227.69097222222</v>
+        <v>46234.425</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46229.66041666667</v>
+        <v>46339.2625</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3338,17 +3362,13 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46230</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3380,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46234.425</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3391,13 +3411,17 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="O60" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3409,29 +3433,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3446,7 +3470,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3458,29 +3482,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3489,13 +3513,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3507,29 +3535,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46240.33125</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46339.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3538,17 +3566,13 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3560,29 +3584,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3591,17 +3615,13 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3613,29 +3633,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3650,7 +3670,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3662,29 +3682,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46286.5</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3693,13 +3713,17 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="O66" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3711,29 +3735,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46245.29375</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3748,7 +3772,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3760,29 +3784,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HESTIA LEADER</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9355226</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46226.02986111111</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46227.61805555555</v>
+        <v>46363.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3791,17 +3815,13 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" s="1" t="n">
-        <v>46228</v>
-      </c>
-      <c r="P68" s="1" t="n">
-        <v>46228</v>
-      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3813,29 +3833,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46286.5</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3844,17 +3864,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3866,29 +3882,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3897,13 +3913,17 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="O70" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3915,29 +3935,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GOLD XING</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9308807</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46227.39930555555</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46227.95694444444</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3947,16 +3967,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -3968,29 +3988,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46286.25</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3999,17 +4019,13 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P72" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4021,29 +4037,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46339.2625</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4052,17 +4068,13 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P73" s="1" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4074,29 +4086,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46286.2625</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4105,17 +4117,13 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P74" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4127,29 +4135,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4159,16 +4167,16 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" s="1" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4180,29 +4188,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4211,17 +4219,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4233,29 +4237,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4265,16 +4269,16 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4286,29 +4290,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ELEGANT ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9561265</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46227.48402777778</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46229.15833333333</v>
+        <v>46233.9375</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4318,16 +4322,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4339,29 +4343,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46286.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4376,7 +4380,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4388,29 +4392,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4425,7 +4429,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4437,29 +4441,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>ELEGANT ACE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9561265</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46227.48402777778</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46229.15833333333</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4469,16 +4473,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" s="1" t="n">
-        <v>46243</v>
+        <v>46229</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46243</v>
+        <v>46229</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4490,29 +4494,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4521,17 +4525,13 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P82" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4543,29 +4543,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IVORY ARROW</t>
+          <t>POSEIDON LEADER</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9277838</t>
+          <t>9335965</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46226.29513888889</v>
+        <v>46227.69097222222</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46226.74652777778</v>
+        <v>46229.66041666667</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4575,16 +4575,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4596,29 +4596,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46229.3625</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -4628,16 +4628,16 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7819,29 +7819,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46229.25</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46232.25</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7868,29 +7868,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GREBE ARROW</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>9077070</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46228.99305555555</v>
+        <v>46266.25</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>46232.8875</v>
+        <v>46268.25</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -7899,17 +7899,13 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
-      <c r="O152" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P152" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -7921,29 +7917,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>GREBE ARROW</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9077070</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46269.25</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>46271.25</v>
+        <v>46232.8875</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -7952,13 +7948,17 @@
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
+      <c r="O153" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P153" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11223,7 +11223,7 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12916,7 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -12985,7 +12985,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13123,7 +13123,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13671,7 +13671,7 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13874,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14353,7 +14353,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14556,7 +14556,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15238,7 @@
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15648,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16385,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17033,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17358,7 +17358,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17614,7 +17614,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18919,7 @@
       <c r="R318" t="inlineStr"/>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18990,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19118,7 +19118,7 @@
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19295,7 @@
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19413,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19472,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-13 06:25:39</t>
+          <t>2026-08-13 06:31:45</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -607,7 +607,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46260.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46262.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2160,29 +2160,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GRAND VENUS</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9303211</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46226.29930555556</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2209,29 +2209,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2240,13 +2240,17 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="O37" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2258,29 +2262,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2289,13 +2293,17 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="O38" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>46229</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2307,26 +2315,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>46339.2625</v>
@@ -2344,7 +2352,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2356,29 +2364,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>ELEGANT ACE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9561265</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46227.48402777778</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46229.15833333333</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2387,13 +2395,17 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="O40" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <v>46229</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2405,29 +2417,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2442,7 +2454,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2454,29 +2466,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2486,16 +2498,16 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2507,29 +2519,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2544,7 +2556,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2556,29 +2568,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46243.01875</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2588,16 +2600,16 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" s="1" t="n">
-        <v>46231</v>
+        <v>46247</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46231</v>
+        <v>46247</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2609,29 +2621,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.31875</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2640,17 +2652,13 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2662,29 +2670,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2693,13 +2701,17 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="O46" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2711,29 +2723,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46363.2625</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2742,17 +2754,13 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2764,29 +2772,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2795,17 +2803,13 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P48" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2817,29 +2821,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46286.25</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2848,13 +2852,17 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="O49" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2866,29 +2874,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46234.425</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46286.5</v>
+        <v>46339.2625</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2903,7 +2911,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2915,29 +2923,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46229.3625</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2947,16 +2955,16 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" s="1" t="n">
-        <v>46242</v>
+        <v>46232</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46242</v>
+        <v>46232</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -2968,29 +2976,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3005,7 +3013,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3017,29 +3025,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HESTIA LEADER</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9355226</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46226.02986111111</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46227.61805555555</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3049,16 +3057,16 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3070,29 +3078,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3101,17 +3109,13 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3123,29 +3127,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GOLD XING</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9308807</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46227.39930555555</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46227.95694444444</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3155,16 +3159,16 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3180,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>POSEIDON LEADER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9335965</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46227.69097222222</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46229.66041666667</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3208,16 +3212,16 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" s="1" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3229,29 +3233,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3266,7 +3270,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3282,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IVORY ARROW</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9277838</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46226.29513888889</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46226.74652777778</v>
+        <v>46286.2625</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3309,17 +3313,13 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>46227</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3331,29 +3331,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46234.425</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3368,7 +3368,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3380,29 +3380,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>IVORY ARROW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9277838</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46226.29513888889</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46226.74652777778</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3412,16 +3412,16 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" s="1" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3433,29 +3433,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46233.9375</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3464,13 +3464,17 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3482,29 +3486,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>GRAND VENUS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9303211</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>040</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>040</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46226.29930555556</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46286.2625</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3513,17 +3517,13 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3535,29 +3535,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3584,29 +3584,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46235.60625</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3615,13 +3615,17 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3633,29 +3637,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>HESTIA LEADER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9355226</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46226.02986111111</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46227.61805555555</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3664,13 +3668,17 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="O65" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3682,29 +3690,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46286.2625</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3713,17 +3721,13 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3735,29 +3739,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3772,7 +3776,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3784,29 +3788,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3821,7 +3825,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3833,29 +3837,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>GOLD XING</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9308807</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46227.39930555555</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46286.5</v>
+        <v>46227.95694444444</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3864,13 +3868,17 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3931,7 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3935,29 +3943,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3966,17 +3974,13 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P71" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -3988,29 +3992,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46240.33125</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4025,7 +4029,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4037,29 +4041,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46233.6875</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4068,13 +4072,17 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4086,29 +4094,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4117,13 +4125,17 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="O74" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4135,29 +4147,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4166,17 +4178,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4188,29 +4196,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4225,7 +4233,7 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4237,29 +4245,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.29375</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4268,17 +4276,13 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P77" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4290,29 +4294,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4322,16 +4326,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4343,29 +4347,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46242.5125</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4374,13 +4378,17 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4392,29 +4400,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4429,7 +4437,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4441,29 +4449,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ELEGANT ACE</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9561265</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46227.48402777778</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46229.15833333333</v>
+        <v>46286.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4472,17 +4480,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4494,29 +4498,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4525,13 +4529,17 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="O82" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4543,29 +4551,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>POSEIDON LEADER</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9335965</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46227.69097222222</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46229.66041666667</v>
+        <v>46339.2625</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4574,17 +4582,13 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="P83" s="1" t="n">
-        <v>46230</v>
-      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4596,29 +4600,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46237.34375</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -4627,17 +4631,13 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="P84" s="1" t="n">
-        <v>46232</v>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7501,29 +7501,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MAERSK RIO DELTA</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>9357951</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F145" s="1" t="n">
-        <v>46256.875</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G145" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46261.39583333334</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -7537,12 +7537,12 @@
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7607,29 +7607,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46242.54166666666</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>46261.39583333334</v>
+        <v>46242.95833333334</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7660,29 +7660,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>UBENA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9690078</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F148" s="1" t="n">
-        <v>46247.85416666666</v>
+        <v>46257.10416666666</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>46248.29166666666</v>
+        <v>46257.58333333334</v>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -7696,12 +7696,12 @@
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7713,29 +7713,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>UBENA</t>
+          <t>MAERSK RIO DELTA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>9690078</t>
+          <t>9357951</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
         <v>46257.02083333334</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -7749,12 +7749,12 @@
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46242.54166666666</v>
+        <v>46247.85416666666</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>46242.95833333334</v>
+        <v>46248.29166666666</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7819,29 +7819,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46229.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>46232.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7868,29 +7868,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46266.25</v>
+        <v>46229.25</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>46268.25</v>
+        <v>46232.25</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8347,17 +8347,17 @@
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46096.125</v>
+        <v>46356.25</v>
       </c>
       <c r="G160" s="1" t="n">
         <v>46387.25</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" s="1" t="n">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" s="1" t="n">
@@ -8373,7 +8373,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8385,12 +8385,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8404,17 +8404,17 @@
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46356.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G161" s="1" t="n">
         <v>46387.25</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46268</v>
+        <v>46209</v>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" s="1" t="n">
-        <v>46268</v>
+        <v>46209</v>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" s="1" t="n">
@@ -8430,7 +8430,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46254.58333333334</v>
+        <v>46254.91666666666</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46256.25</v>
+        <v>46256.875</v>
       </c>
       <c r="H172" s="1" t="n">
         <v>46250.25</v>
@@ -9094,12 +9094,12 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46252.875</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="G174" s="1" t="n">
         <v>46253.91666666666</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46252.20833333334</v>
+        <v>46252.6875</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46254.47916666666</v>
+        <v>46254.8125</v>
       </c>
       <c r="H177" s="1" t="n">
         <v>46246.58333333334</v>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
         <v>46251.54166666666</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46252.58333333334</v>
+        <v>46252.91666666666</v>
       </c>
       <c r="H178" s="1" t="n">
         <v>46246.25</v>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9501,38 +9501,38 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PRIDE C</t>
+          <t>EVER SUPERB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>9978640</t>
+          <t>9300427</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>030W</t>
+          <t>0115S</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>030E</t>
+          <t>0115N</t>
         </is>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46250.91666666666</v>
+        <v>46251.25</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>46251.5</v>
+        <v>46253.25</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="I179" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="J179" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="K179" s="1" t="n">
         <v>46250.75</v>
@@ -9544,21 +9544,21 @@
         <v>46250.75</v>
       </c>
       <c r="N179" s="1" t="n">
-        <v>46250.75</v>
+        <v>46252.25</v>
       </c>
       <c r="O179" s="1" t="n">
-        <v>46251.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="P179" s="1" t="n">
-        <v>46251.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="Q179" s="1" t="n">
-        <v>46254.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9570,38 +9570,38 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EVER SUPERB</t>
+          <t>OOCL MIAMI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>9300427</t>
+          <t>9477892</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0115S</t>
+          <t>114S</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0115N</t>
+          <t>114N</t>
         </is>
       </c>
       <c r="F180" s="1" t="n">
-        <v>46251.25</v>
+        <v>46251.5</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>46253.25</v>
+        <v>46254.75</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="J180" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="K180" s="1" t="n">
         <v>46250.75</v>
@@ -9613,7 +9613,7 @@
         <v>46250.75</v>
       </c>
       <c r="N180" s="1" t="n">
-        <v>46252.25</v>
+        <v>46250.75</v>
       </c>
       <c r="O180" s="1" t="n">
         <v>46252.00069444445</v>
@@ -9627,7 +9627,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9639,38 +9639,38 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OOCL MIAMI</t>
+          <t>PRIDE C</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>9477892</t>
+          <t>9978640</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>114S</t>
+          <t>030W</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>114N</t>
+          <t>030E</t>
         </is>
       </c>
       <c r="F181" s="1" t="n">
+        <v>46250.91666666666</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>46251.5</v>
       </c>
-      <c r="G181" s="1" t="n">
-        <v>46254.75</v>
-      </c>
       <c r="H181" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="I181" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="K181" s="1" t="n">
         <v>46250.75</v>
@@ -9685,18 +9685,18 @@
         <v>46250.75</v>
       </c>
       <c r="O181" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46251.00069444445</v>
       </c>
       <c r="P181" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46251.00069444445</v>
       </c>
       <c r="Q181" s="1" t="n">
-        <v>46255.00069444445</v>
+        <v>46254.00069444445</v>
       </c>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10017,133 +10017,133 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CMA CGM GREEN</t>
+          <t>OOCL YOKOHAMA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>9810915</t>
+          <t>9329538</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>213S</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>213N</t>
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46250.02083333334</v>
+        <v>46250.25</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>46250.47916666666</v>
+        <v>46251.95833333334</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46244.91666666666</v>
-      </c>
-      <c r="I187" s="1" t="n">
-        <v>46246.91666666666</v>
-      </c>
-      <c r="J187" t="inlineStr"/>
+        <v>46244.25</v>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" s="1" t="n">
+        <v>46244.25</v>
+      </c>
       <c r="K187" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
       <c r="L187" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
-      <c r="M187" s="1" t="n">
-        <v>46248.91666666666</v>
-      </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" s="1" t="n">
+        <v>46249.08333333334</v>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OOCL YOKOHAMA</t>
+          <t>CMA CGM GREEN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>9329538</t>
+          <t>9810915</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>213S</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>213N</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F188" s="1" t="n">
-        <v>46250.25</v>
+        <v>46250.02083333334</v>
       </c>
       <c r="G188" s="1" t="n">
-        <v>46251.95833333334</v>
+        <v>46250.47916666666</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" s="1" t="n">
-        <v>46244.25</v>
-      </c>
+        <v>46244.91666666666</v>
+      </c>
+      <c r="I188" s="1" t="n">
+        <v>46246.91666666666</v>
+      </c>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
       <c r="L188" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" s="1" t="n">
-        <v>46249.08333333334</v>
-      </c>
+      <c r="M188" s="1" t="n">
+        <v>46248.91666666666</v>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10218,29 +10218,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>OOCL TEXAS</t>
+          <t>MSC DAISY</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>9329552</t>
+          <t>9295165</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>230S</t>
+          <t>KQ628A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>230N</t>
+          <t>KQ633R</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46249.04166666666</v>
+        <v>46248.5</v>
       </c>
       <c r="G190" s="1" t="n">
-        <v>46249.91666666666</v>
+        <v>46250.25</v>
       </c>
       <c r="H190" s="1" t="n">
         <v>46244.23958333334</v>
@@ -10261,7 +10261,7 @@
         <v>46248.5</v>
       </c>
       <c r="N190" s="1" t="n">
-        <v>46249.25</v>
+        <v>46248.5</v>
       </c>
       <c r="O190" s="1" t="n">
         <v>46249.00069444445</v>
@@ -10275,7 +10275,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10287,29 +10287,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MSC DAISY</t>
+          <t>OOCL TEXAS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>9295165</t>
+          <t>9329552</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>KQ628A</t>
+          <t>230S</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>KQ633R</t>
+          <t>230N</t>
         </is>
       </c>
       <c r="F191" s="1" t="n">
-        <v>46248.5</v>
+        <v>46249.04166666666</v>
       </c>
       <c r="G191" s="1" t="n">
-        <v>46250.25</v>
+        <v>46249.91666666666</v>
       </c>
       <c r="H191" s="1" t="n">
         <v>46244.23958333334</v>
@@ -10330,7 +10330,7 @@
         <v>46248.5</v>
       </c>
       <c r="N191" s="1" t="n">
-        <v>46248.5</v>
+        <v>46249.25</v>
       </c>
       <c r="O191" s="1" t="n">
         <v>46249.00069444445</v>
@@ -10344,7 +10344,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10413,49 +10413,51 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9919254</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46250.91666666666</v>
+        <v>46247.375</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>46252.10416666666</v>
+        <v>46249.04166666666</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46241.25</v>
+        <v>46241.23958333334</v>
       </c>
       <c r="I193" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="J193" t="inlineStr"/>
+        <v>46241.23958333334</v>
+      </c>
+      <c r="J193" s="1" t="n">
+        <v>46241.23958333334</v>
+      </c>
       <c r="K193" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -10465,68 +10467,64 @@
       <c r="M193" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" s="1" t="n">
+        <v>46247.91666666666</v>
+      </c>
       <c r="O193" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="P193" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="Q193" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46251.00069444445</v>
+      </c>
+      <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9919254</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46247.375</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="G194" s="1" t="n">
-        <v>46249.04166666666</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46241.23958333334</v>
+        <v>46241.25</v>
       </c>
       <c r="I194" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
-      <c r="J194" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
+        <v>46244.25</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -10536,22 +10534,24 @@
       <c r="M194" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N194" s="1" t="n">
-        <v>46247.75</v>
-      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="P194" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="Q194" s="1" t="n">
-        <v>46251.00069444445</v>
-      </c>
-      <c r="R194" t="inlineStr"/>
+        <v>46255</v>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10685,49 +10685,49 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MONACO</t>
+          <t>EVER ENVOY</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>9314961</t>
+          <t>9241308</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>203S</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>203N</t>
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46246.24305555555</v>
+        <v>46247.66666666666</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>46247.42013888889</v>
+        <v>46249.91666666666</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46241.20833333334</v>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" s="1" t="n">
-        <v>46241.20833333334</v>
-      </c>
+        <v>46240.58333333334</v>
+      </c>
+      <c r="I197" s="1" t="n">
+        <v>46243.58333333334</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" s="1" t="n">
         <v>46245.58333333334</v>
       </c>
@@ -10735,64 +10735,68 @@
         <v>46245.58333333334</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>46246.375</v>
-      </c>
-      <c r="N197" s="1" t="n">
-        <v>46247.58333333334</v>
-      </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+        <v>46245.58333333334</v>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="1" t="n">
+        <v>46250.25</v>
+      </c>
+      <c r="P197" s="1" t="n">
+        <v>46250.25</v>
+      </c>
+      <c r="Q197" s="1" t="n">
+        <v>46253</v>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EVER ENVOY</t>
+          <t>MONACO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>9241308</t>
+          <t>9314961</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>203S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>203N</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46247.66666666666</v>
+        <v>46246.24305555555</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>46249.91666666666</v>
+        <v>46247.42013888889</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46240.58333333334</v>
-      </c>
-      <c r="I198" s="1" t="n">
-        <v>46243.58333333334</v>
-      </c>
-      <c r="J198" t="inlineStr"/>
+        <v>46241.20833333334</v>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" s="1" t="n">
+        <v>46241.20833333334</v>
+      </c>
       <c r="K198" s="1" t="n">
         <v>46245.58333333334</v>
       </c>
@@ -10800,26 +10804,22 @@
         <v>46245.58333333334</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>46245.58333333334</v>
-      </c>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" s="1" t="n">
-        <v>46250.25</v>
-      </c>
-      <c r="P198" s="1" t="n">
-        <v>46250.25</v>
-      </c>
-      <c r="Q198" s="1" t="n">
-        <v>46253</v>
-      </c>
+        <v>46246.375</v>
+      </c>
+      <c r="N198" s="1" t="n">
+        <v>46247.58333333334</v>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46250.25</v>
+        <v>46247.73958333334</v>
       </c>
       <c r="G203" s="1" t="n">
         <v>46251.25</v>
@@ -11154,7 +11154,7 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11223,7 +11223,7 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12916,7 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -12985,7 +12985,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13123,7 +13123,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13671,7 +13671,7 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13874,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14353,7 +14353,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14556,7 +14556,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15238,7 @@
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15648,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16385,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17033,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17358,7 +17358,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17614,7 +17614,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18919,7 @@
       <c r="R318" t="inlineStr"/>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18990,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19118,7 +19118,7 @@
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19295,7 @@
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19413,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19472,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-13 06:31:45</t>
+          <t>2026-08-13 07:05:10</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -778,7 +778,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1874,29 +1874,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>46266.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46268.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1923,29 +1923,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46266.25</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46268.25</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -1972,29 +1972,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>46229.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46232.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2335,29 +2335,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46233.9375</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2366,13 +2366,17 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="O39" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2384,29 +2388,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>POSEIDON LEADER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9335965</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46227.69097222222</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46229.66041666667</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2416,16 +2420,16 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" s="1" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2437,29 +2441,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46286.5</v>
+        <v>46286.25</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2474,7 +2478,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2486,29 +2490,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46229.3625</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2517,13 +2521,17 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="O42" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>46232</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2535,29 +2543,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>POSEIDON LEADER</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9335965</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46227.69097222222</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46229.66041666667</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2567,16 +2575,16 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" s="1" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2588,29 +2596,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2625,7 +2633,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2637,29 +2645,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46234.425</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2668,13 +2676,17 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2735,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2735,29 +2747,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46237.34375</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2772,7 +2784,7 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2784,29 +2796,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2815,13 +2827,17 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="O48" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2833,29 +2849,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2864,17 +2880,13 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2898,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2918,16 +2930,16 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2939,29 +2951,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2970,13 +2982,17 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="O51" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>46248</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -2988,29 +3004,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46234.425</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3025,7 +3041,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3037,29 +3053,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3068,17 +3084,13 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="P53" s="1" t="n">
-        <v>46232</v>
-      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3102,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46286.2625</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3121,17 +3133,13 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>46231</v>
-      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3143,26 +3151,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46339.2625</v>
@@ -3180,7 +3188,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3200,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46286.2625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3223,17 +3231,13 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3245,29 +3249,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46233.6875</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3277,16 +3281,16 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" s="1" t="n">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3298,29 +3302,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3335,7 +3339,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3347,29 +3351,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46243.01875</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3379,16 +3383,16 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3400,26 +3404,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46339.2625</v>
@@ -3437,7 +3441,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3449,29 +3453,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3481,16 +3485,16 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" s="1" t="n">
-        <v>46243</v>
+        <v>46238</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46243</v>
+        <v>46238</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3502,29 +3506,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46242.5125</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3533,13 +3537,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3551,29 +3559,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GOLD XING</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9308807</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46227.39930555555</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46227.95694444444</v>
+        <v>46286.5</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3582,17 +3590,13 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="1" t="n">
-        <v>46228</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>46228</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3604,29 +3608,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3635,13 +3639,17 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3653,29 +3661,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46286.5</v>
+        <v>46339.2625</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3690,7 +3698,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3702,29 +3710,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46242.26875</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3734,16 +3742,16 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3755,29 +3763,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3787,16 +3795,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3808,29 +3816,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>ELEGANT ACE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9561265</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46227.48402777778</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46229.15833333333</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3840,16 +3848,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" s="1" t="n">
-        <v>46242</v>
+        <v>46229</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46242</v>
+        <v>46229</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3861,29 +3869,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3892,17 +3900,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3914,29 +3918,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3946,16 +3950,16 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" s="1" t="n">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -3967,29 +3971,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3998,13 +4002,17 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="O71" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="P71" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4016,29 +4024,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4053,7 +4061,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4065,29 +4073,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46235.60625</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4096,13 +4104,17 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4114,26 +4126,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46240.33125</v>
       </c>
       <c r="G74" s="1" t="n">
         <v>46339.2625</v>
@@ -4151,7 +4163,7 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4163,29 +4175,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ELEGANT ACE</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9561265</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46227.48402777778</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46229.15833333333</v>
+        <v>46286.5</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4194,17 +4206,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4216,29 +4224,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4247,13 +4255,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="O76" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>46231</v>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4265,26 +4277,26 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G77" s="1" t="n">
         <v>46339.2625</v>
@@ -4302,7 +4314,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4314,29 +4326,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4351,7 +4363,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4363,29 +4375,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4400,7 +4412,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4412,29 +4424,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>GOLD XING</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9308807</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46227.39930555555</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46227.95694444444</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4444,16 +4456,16 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" s="1" t="n">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4465,26 +4477,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46245.31875</v>
       </c>
       <c r="G81" s="1" t="n">
         <v>46363.2625</v>
@@ -4502,7 +4514,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4514,29 +4526,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4545,17 +4557,13 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P82" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4567,26 +4575,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G83" s="1" t="n">
         <v>46286.2625</v>
@@ -4604,7 +4612,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4616,29 +4624,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46245.29375</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -4647,17 +4655,13 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P84" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4669,29 +4673,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -4700,17 +4704,13 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P85" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8037,29 +8037,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46269.25</v>
+        <v>46229.25</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>46271.25</v>
+        <v>46232.25</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -8074,7 +8074,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10825,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11294,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13608,7 @@
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14014,7 +14014,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,7 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14558,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15788,7 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16267,7 +16267,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16456,7 +16456,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16781,7 +16781,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16844,7 +16844,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17299,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17429,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18225,7 @@
       <c r="R308" t="inlineStr"/>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18296,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18990,7 @@
       <c r="R319" t="inlineStr"/>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19248,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19307,7 +19307,7 @@
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19366,7 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19425,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>
@@ -19543,7 +19543,7 @@
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:12</t>
+          <t>2026-08-13 22:24:56</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -778,7 +778,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1825,29 +1825,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46260.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46262.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1874,29 +1874,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>46269.25</v>
+        <v>46229.25</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46271.25</v>
+        <v>46232.25</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1923,29 +1923,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>46266.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46268.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -1972,29 +1972,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>GREBE ARROW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9077070</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46232.8875</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2003,13 +2003,17 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="O32" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2062,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2115,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2168,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2221,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2274,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2380,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2388,29 +2392,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>POSEIDON LEADER</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9335965</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46227.69097222222</v>
+        <v>46245.29375</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46229.66041666667</v>
+        <v>46363.2625</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2419,17 +2423,13 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>46230</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2441,29 +2441,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46240.33125</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2490,29 +2490,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2521,17 +2521,13 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="P42" s="1" t="n">
-        <v>46232</v>
-      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2543,29 +2539,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2575,16 +2571,16 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" s="1" t="n">
-        <v>46229</v>
+        <v>46248</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46229</v>
+        <v>46248</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2596,29 +2592,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>POSEIDON LEADER</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9335965</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46227.69097222222</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46229.66041666667</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2627,13 +2623,17 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="O44" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>46230</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2645,29 +2645,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2676,17 +2676,13 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2694,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46237.34375</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46286.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2735,7 +2731,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2747,29 +2743,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46242.5125</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2778,13 +2774,17 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2796,29 +2796,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2828,16 +2828,16 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2849,29 +2849,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2898,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2929,17 +2929,13 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -2951,29 +2947,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46245.31875</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46363.2625</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2982,17 +2978,13 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3004,26 +2996,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46234.425</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46339.2625</v>
@@ -3041,7 +3033,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3053,29 +3045,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>GOLD XING</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9308807</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46227.39930555555</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46227.95694444444</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3084,13 +3076,17 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="O53" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3102,29 +3098,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3139,7 +3135,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3151,29 +3147,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3182,13 +3178,17 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="O55" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P55" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3200,29 +3200,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3249,29 +3249,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46229.3625</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3281,16 +3281,16 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3302,29 +3302,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3351,29 +3351,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46286.2625</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3382,17 +3382,13 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3404,29 +3400,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3435,13 +3431,17 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="O60" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>46231</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3453,29 +3453,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3484,17 +3484,13 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3506,29 +3502,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>ELEGANT ACE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9561265</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46227.48402777778</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46229.15833333333</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3538,16 +3534,16 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" s="1" t="n">
-        <v>46243</v>
+        <v>46229</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46243</v>
+        <v>46229</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3559,29 +3555,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46234.425</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46286.5</v>
+        <v>46339.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3596,7 +3592,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3608,29 +3604,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3639,17 +3635,13 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3661,29 +3653,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3698,7 +3690,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3710,29 +3702,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46243.01875</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3742,16 +3734,16 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3763,29 +3755,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3795,16 +3787,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3816,29 +3808,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ELEGANT ACE</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9561265</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46227.48402777778</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46229.15833333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3847,17 +3839,13 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P68" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3869,29 +3857,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3906,7 +3894,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3918,29 +3906,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3950,16 +3938,16 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" s="1" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -3971,29 +3959,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46235.60625</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4003,16 +3991,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4024,29 +4012,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4055,13 +4043,17 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="O72" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4073,29 +4065,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46286.5</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4104,17 +4096,13 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P73" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4126,29 +4114,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4157,13 +4145,17 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="O74" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>46229</v>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4175,29 +4167,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46286.5</v>
+        <v>46286.25</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4212,7 +4204,7 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4224,29 +4216,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4255,17 +4247,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46231</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4277,29 +4265,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4314,7 +4302,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4326,29 +4314,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4357,13 +4345,17 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="O78" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4375,29 +4367,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4412,7 +4404,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4424,29 +4416,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GOLD XING</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9308807</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46227.39930555555</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46227.95694444444</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4456,16 +4448,16 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4477,29 +4469,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4514,7 +4506,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4526,29 +4518,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46233.6875</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4557,13 +4549,17 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="O82" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4575,29 +4571,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4606,13 +4602,17 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="O83" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4624,29 +4624,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -4655,13 +4655,17 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="O84" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4673,29 +4677,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -4710,7 +4714,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4760,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4808,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4853,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4898,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4943,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4988,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5033,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5082,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5131,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5184,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5231,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5325,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5372,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5419,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5466,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5513,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5560,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5607,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5654,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5701,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5748,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5795,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5842,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5889,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5936,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5983,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6032,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6077,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6126,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6175,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6224,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6273,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6322,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6367,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6422,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6467,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6512,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6557,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6606,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6655,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6704,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6753,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6802,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6847,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6888,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6937,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6982,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7031,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7080,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7129,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7174,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7223,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7272,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7321,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7366,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7411,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7460,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7517,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7562,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7611,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7619,29 +7623,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46247.22916666666</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>46249.04166666666</v>
+        <v>46261.39583333334</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -7660,7 +7664,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7697,9 @@
       <c r="F148" s="1" t="n">
         <v>46262.04166666666</v>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" s="1" t="n">
+        <v>46263.04166666666</v>
+      </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
@@ -7704,10 +7710,14 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7719,29 +7729,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>TAMPA I</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9196840</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>159S</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>159N</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
-        <v>46253.91666666666</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>46255.75</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -7755,12 +7765,12 @@
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7772,29 +7782,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>UBENA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9690078</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46257.10416666666</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>46261.39583333334</v>
+        <v>46257.58333333334</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -7808,12 +7818,12 @@
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7825,29 +7835,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>UBENA</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>9690078</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46257.10416666666</v>
+        <v>46247.22916666666</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46249.04166666666</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -7861,12 +7871,12 @@
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7878,29 +7888,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MAERSK RIO DELTA</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>9357951</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46257.02083333334</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46255.75</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -7914,12 +7924,12 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7931,29 +7941,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TAMPA I</t>
+          <t>MAERSK RIO DELTA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>9196840</t>
+          <t>9357951</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>159S</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>159N</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46257.02083333334</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>46262.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -7972,7 +7982,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -7984,29 +7994,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GREBE ARROW</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>9077070</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F154" s="1" t="n">
-        <v>46228.99305555555</v>
+        <v>46260.25</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>46232.8875</v>
+        <v>46262.25</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -8015,17 +8025,13 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
-      <c r="O154" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P154" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8037,29 +8043,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46229.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>46232.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -8074,7 +8080,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8145,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8204,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8263,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8322,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8381,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8438,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8450,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8463,17 +8469,17 @@
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46204.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G162" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46104.25</v>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" s="1" t="n">
@@ -8489,7 +8495,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8552,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8564,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8577,17 +8583,17 @@
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46386.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G164" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>46104.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" s="1" t="n">
-        <v>46284.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" s="1" t="n">
@@ -8603,7 +8609,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8666,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8725,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8784,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8847,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8910,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8973,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9032,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9084,12 +9090,12 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9158,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9221,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9284,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9347,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9416,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9479,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9548,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9617,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9686,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9755,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9824,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9887,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9950,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10019,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10088,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10157,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10220,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10289,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10352,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10421,7 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10490,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10559,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10628,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10697,7 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10762,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10831,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10896,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10965,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11034,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11103,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11162,7 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11231,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11300,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11369,7 @@
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11438,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11507,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11576,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11610,7 @@
         <v>46245.52083333334</v>
       </c>
       <c r="G210" s="1" t="n">
-        <v>46248.625</v>
+        <v>46248.375</v>
       </c>
       <c r="H210" s="1" t="n">
         <v>46237.58333333334</v>
@@ -11635,7 +11641,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11706,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11771,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11840,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11909,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11978,7 @@
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12047,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12116,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12185,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12254,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12323,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12390,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12459,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12528,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12597,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12666,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12731,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12796,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12865,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12930,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -12987,7 +12993,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13062,7 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13131,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13200,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13269,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13338,7 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13407,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13476,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13545,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13614,7 @@
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13679,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13748,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13817,7 @@
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13886,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13951,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14014,7 +14020,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14089,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14158,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14223,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14292,7 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14361,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14430,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14495,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14564,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14633,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14702,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14767,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14836,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14905,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14974,7 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15043,7 @@
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15112,7 @@
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15181,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15250,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15315,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15384,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15449,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15518,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15587,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15656,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15725,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15794,7 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15863,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15932,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -15995,7 +16001,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16070,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16139,7 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16208,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16267,7 +16273,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16338,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16403,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16456,7 +16462,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16527,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16592,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16651,7 +16657,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16722,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16781,7 +16787,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16844,7 +16850,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16915,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16980,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17039,7 +17045,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17110,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17175,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17240,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17305,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17370,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17435,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17500,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17565,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17630,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17691,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17756,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17821,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17888,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17959,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18030,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18101,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18172,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18231,7 @@
       <c r="R308" t="inlineStr"/>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18296,7 +18302,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18373,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18444,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18513,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18584,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18653,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18720,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18791,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18862,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18933,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18996,7 @@
       <c r="R319" t="inlineStr"/>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19067,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19130,7 +19136,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19195,7 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19254,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19307,7 +19313,7 @@
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19372,7 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19431,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19490,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
@@ -19543,7 +19549,7 @@
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-13 22:24:56</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -1541,31 +1541,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUBE PORTS - FREMANTLE 1   - FW10K</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9531715</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EE216</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EE216</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>193N</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46262.71527777778</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>46264.71527777778</v>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1576,7 +1580,11 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>2026-08-15 13:24:29</t>
@@ -1624,7 +1632,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1677,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1722,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1767,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1812,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1857,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1902,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1947,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1992,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2037,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2082,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2127,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2172,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2217,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2254,41 +2262,41 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AAT VICTORIA DOCK - GG43P</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AAL BANGKOK</t>
+          <t>NABUCCO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9521564</t>
+          <t>9731652</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>46089.25</v>
+        <v>46231.37013888889</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46092.25</v>
+        <v>46232.62847222222</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2297,13 +2305,17 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="O34" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2315,29 +2327,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NABUCCO</t>
+          <t>HOEGH TRACER</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9731652</t>
+          <t>9684990</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>46231.37013888889</v>
+        <v>46229.77361111111</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46232.62847222222</v>
+        <v>46230.58333333334</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2347,16 +2359,16 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" s="1" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2368,29 +2380,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HOEGH TRACER</t>
+          <t>CHESAPEAKE HIGHWAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9684990</t>
+          <t>9565546</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46229.77361111111</v>
+        <v>46236.03611111111</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46230.58333333334</v>
+        <v>46237.14305555556</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2400,16 +2412,16 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2421,29 +2433,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CHESAPEAKE HIGHWAY</t>
+          <t>HOEGH SHANGHAI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9565546</t>
+          <t>9312482</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46236.03611111111</v>
+        <v>46241.45625</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46237.14305555556</v>
+        <v>46242.90902777778</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2453,16 +2465,16 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" s="1" t="n">
-        <v>46237</v>
+        <v>46243</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46237</v>
+        <v>46243</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2474,29 +2486,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HOEGH SHANGHAI</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9312482</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46241.45625</v>
+        <v>46229.3625</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46242.90902777778</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2506,16 +2518,16 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" s="1" t="n">
-        <v>46243</v>
+        <v>46232</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46243</v>
+        <v>46232</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2527,29 +2539,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46316.2625</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2558,17 +2570,13 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2580,29 +2588,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46286.5</v>
+        <v>46233.9375</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2611,13 +2619,17 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="O40" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2629,29 +2641,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46242.26875</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2661,16 +2673,16 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2682,29 +2694,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46235.60625</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2713,13 +2725,17 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="O42" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2731,29 +2747,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46363.2625</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2762,17 +2778,13 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>46231</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2784,29 +2796,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46233.6875</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2815,13 +2827,17 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="O44" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2833,29 +2849,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2864,17 +2880,13 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2898,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46286.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2917,17 +2929,13 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2939,29 +2947,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2970,13 +2978,17 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>46229</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -2988,29 +3000,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -3019,13 +3031,17 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="O48" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3037,29 +3053,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46242.5125</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3068,13 +3084,17 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="O49" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3106,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -3117,13 +3137,17 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="O50" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3135,26 +3159,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46234.425</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46339.2625</v>
@@ -3172,7 +3196,7 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3208,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3215,13 +3239,17 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="O52" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="P52" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3233,29 +3261,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3265,16 +3293,16 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3355,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3339,29 +3367,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3370,17 +3398,13 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3392,29 +3416,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3423,13 +3447,17 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="O56" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3441,26 +3469,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46339.2625</v>
@@ -3478,7 +3506,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3490,29 +3518,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3527,7 +3555,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3539,29 +3567,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3576,7 +3604,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3588,26 +3616,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46339.2625</v>
@@ -3625,7 +3653,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3637,29 +3665,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46286.5</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3668,13 +3696,17 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46231</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3686,26 +3718,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46240.33125</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>46339.2625</v>
@@ -3723,7 +3755,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3735,29 +3767,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3772,7 +3804,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3784,29 +3816,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46237.34375</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46286.2625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3815,17 +3847,13 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3837,29 +3865,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46243.01875</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3868,13 +3896,17 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="O65" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3886,29 +3918,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3917,13 +3949,17 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="O66" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3935,29 +3971,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3967,16 +4003,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -3988,29 +4024,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4019,17 +4055,13 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P68" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4041,29 +4073,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4072,17 +4104,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46232</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4094,29 +4122,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4125,17 +4153,13 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P70" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4147,29 +4171,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4178,17 +4202,13 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P71" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4200,29 +4220,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46245.29375</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4231,17 +4251,13 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="P72" s="1" t="n">
-        <v>46229</v>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4253,29 +4269,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4284,17 +4300,13 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P73" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4306,29 +4318,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46286.25</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4337,13 +4349,17 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="O74" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4355,29 +4371,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4387,16 +4403,16 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" s="1" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4408,29 +4424,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4439,17 +4455,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4461,29 +4473,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4498,7 +4510,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4510,29 +4522,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4547,7 +4559,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4559,29 +4571,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46339.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4590,17 +4602,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P79" s="1" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4612,29 +4620,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4649,7 +4657,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4661,29 +4669,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46234.425</v>
+        <v>46245.31875</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4698,42 +4706,39 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>QUBE PORTS 
+NO 1 BURNIE FX86E</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>BBC DESTINY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9347839</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>128703</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>044</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="n">
-        <v>46245.29375</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>46363.2625</v>
-      </c>
+          <t>128703</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -4747,7 +4752,7 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4755,31 +4760,33 @@
       <c r="A83" t="inlineStr">
         <is>
           <t>QUBE PORTS 
-NO 1 BURNIE FX86E</t>
+NO 1 RISDON FX88K</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BBC DESTINY</t>
+          <t>MARATHA PRESTIGE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9347839</t>
+          <t>9561332</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>128703</t>
+          <t>205852</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>128703</t>
+          <t>205852</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" s="1" t="n">
+        <v>46364.51388888889</v>
+      </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
@@ -4793,41 +4800,38 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUBE PORTS 
-NO 1 RISDON FX88K</t>
+          <t>QUBE PORTS - BUNBURY   - FV97B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MARATHA PRESTIGE</t>
+          <t>YASA MIMOSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9561332</t>
+          <t>9786061</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>205852</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>205852</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" s="1" t="n">
-        <v>46364.51388888889</v>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -4841,34 +4845,34 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QUBE PORTS - BUNBURY   - FV97B</t>
+          <t>QUBE PORTS - FREMANTLE 1   - FW10K</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YASA MIMOSA</t>
+          <t>TULANE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9786061</t>
+          <t>9505089</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>EF405</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>EF405</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -4886,7 +4890,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4898,22 +4902,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TULANE</t>
+          <t>BOHEME</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9505089</t>
+          <t>9176565</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EF405</t>
+          <t>EE513</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>EF405</t>
+          <t>EE513</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -4931,7 +4935,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4943,22 +4947,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BOHEME</t>
+          <t>TULANE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9176565</t>
+          <t>9505089</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EE513</t>
+          <t>EF609</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EE513</t>
+          <t>EF609</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -4976,7 +4980,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -4988,22 +4992,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TULANE</t>
+          <t>TAMERLANE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9505089</t>
+          <t>9218648</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EF609</t>
+          <t>EE414</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EF609</t>
+          <t>EE414</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -5021,7 +5025,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5033,22 +5037,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TAMERLANE</t>
+          <t>21 SUNNY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9218648</t>
+          <t>9615107</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EE414</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>EE414</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -5066,7 +5070,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5078,22 +5082,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>21 SUNNY</t>
+          <t>MORNING CAPO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9615107</t>
+          <t>9663295</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>EE520</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>EE520</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -5111,7 +5115,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5123,22 +5127,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MORNING CAPO</t>
+          <t>MIGNON</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9663295</t>
+          <t>9189251</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EE520</t>
+          <t>EE607</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>EE520</t>
+          <t>EE607</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -5156,7 +5160,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5168,22 +5172,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MIGNON</t>
+          <t>TAMERLANE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9189251</t>
+          <t>9218648</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EE607</t>
+          <t>EZ301</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>EE607</t>
+          <t>EZ301</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -5201,7 +5205,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5213,22 +5217,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TAMERLANE</t>
+          <t>TULANE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9218648</t>
+          <t>9505089</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EZ301</t>
+          <t>EF320</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>EZ301</t>
+          <t>EF320</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -5246,7 +5250,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5258,22 +5262,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TULANE</t>
+          <t>ELEKTRA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9505089</t>
+          <t>9176577</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EF320</t>
+          <t>EE606</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>EF320</t>
+          <t>EE606</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -5291,7 +5295,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5303,22 +5307,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ELEKTRA</t>
+          <t>TAMERLANE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9176577</t>
+          <t>9218648</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EE606</t>
+          <t>EF608</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>EE606</t>
+          <t>EF608</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -5336,7 +5340,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5348,22 +5352,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TAMERLANE</t>
+          <t>TULANE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9218648</t>
+          <t>9505089</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EF608</t>
+          <t>EF512</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>EF608</t>
+          <t>EF512</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -5381,7 +5385,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5397,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TULANE</t>
+          <t>BESS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9505089</t>
+          <t>9531715</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EF512</t>
+          <t>EE216</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>EF512</t>
+          <t>EE216</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -5426,7 +5430,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5479,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5532,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5581,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5628,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5675,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5722,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5769,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5816,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5863,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5910,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5957,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6004,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6051,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6098,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6145,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6192,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6239,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6286,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6333,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6380,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6425,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6474,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6523,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6572,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6617,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6672,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6717,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6762,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6807,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6856,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6905,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6954,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -6999,7 +7003,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7052,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7097,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7138,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7187,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7232,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7281,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7330,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7379,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7424,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7473,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7522,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7567,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7612,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7661,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7718,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7763,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7771,29 +7775,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46262.91666666666</v>
+        <v>46248.05555555555</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>46264.85416666666</v>
+        <v>46248.14583333334</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -7812,7 +7816,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7824,29 +7828,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>UBENA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9690078</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F148" s="1" t="n">
-        <v>46262.71527777778</v>
+        <v>46257.02083333334</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>46264.71527777778</v>
+        <v>46257.54166666666</v>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -7865,7 +7869,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7877,29 +7881,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OLIVIA MAERSK</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>9251638</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>635N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
-        <v>46262.54166666666</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>46263.8125</v>
+        <v>46261.39583333334</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -7913,12 +7917,12 @@
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7930,29 +7934,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>OLIVIA MAERSK</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9251638</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>635N</t>
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46248.05555555555</v>
+        <v>46262.54166666666</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>46248.14583333334</v>
+        <v>46263.91666666666</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -7966,12 +7970,12 @@
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -7983,29 +7987,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>MAERSK RIO DELTA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9357951</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46256.875</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>46261.39583333334</v>
+        <v>46257.58333333334</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -8019,12 +8023,12 @@
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8036,29 +8040,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MAERSK RIO DELTA</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>9357951</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46257.04166666666</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>46257.9375</v>
+        <v>46255.75</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -8072,12 +8076,12 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8089,29 +8093,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46253.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>46255.75</v>
+        <v>46263.58333333334</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -8125,46 +8129,46 @@
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>AAT APPLETON DOCK MELBOURNE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UBENA</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>9690078</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F154" s="1" t="n">
-        <v>46257.02083333334</v>
+        <v>46229.25</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46232.25</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -8176,14 +8180,10 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8195,29 +8195,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46266.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>46268.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -8232,7 +8232,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8293,29 +8293,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GREBE ARROW</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9077070</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46229.25</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>46232.25</v>
+        <v>46232.8875</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -8324,13 +8324,17 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
+      <c r="O157" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P157" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8342,29 +8346,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46266.25</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46268.25</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -8379,7 +8383,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8391,29 +8395,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GREBE ARROW</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>9077070</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46228.99305555555</v>
+        <v>46241.7875</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46232.8875</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8422,51 +8426,47 @@
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P159" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AAT APPLETON DOCK MELBOURNE</t>
+          <t>AAT VICTORIA DOCK - GG43P</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>AAL BANGKOK</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9521564</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46269.25</v>
+        <v>46089.25</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46271.25</v>
+        <v>46092.25</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8481,7 +8481,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8908,12 +8908,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8927,17 +8927,17 @@
         </is>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46096.125</v>
+        <v>46204.25</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" s="1" t="n">
@@ -8953,7 +8953,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8984,17 +8984,17 @@
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46204.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" s="1" t="n">
@@ -9010,7 +9010,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
         <v>46260.875</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46262.58333333334</v>
+        <v>46262.47916666666</v>
       </c>
       <c r="H173" s="1" t="n">
         <v>46255.25</v>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46258.02083333334</v>
+        <v>46257.6875</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46260.25</v>
+        <v>46259.91666666666</v>
       </c>
       <c r="H176" s="1" t="n">
         <v>46252.58333333334</v>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
         <v>46255.58333333334</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46256.91666666666</v>
       </c>
       <c r="H180" s="1" t="n">
         <v>46250.91666666666</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
         <v>46254.91666666666</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>46256.91666666666</v>
+        <v>46256.47916666666</v>
       </c>
       <c r="H183" s="1" t="n">
         <v>46250.25</v>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46252.6875</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="G190" s="1" t="n">
         <v>46254.8125</v>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10420,38 +10420,38 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OOCL MIAMI</t>
+          <t>EVER SUPERB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>9477892</t>
+          <t>9300427</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>114S</t>
+          <t>0115S</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>114N</t>
+          <t>0115N</t>
         </is>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46251.25</v>
+        <v>46252.5</v>
       </c>
       <c r="G192" s="1" t="n">
-        <v>46254.25</v>
+        <v>46254.5</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="I192" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="J192" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="K192" s="1" t="n">
         <v>46250.75</v>
@@ -10463,21 +10463,21 @@
         <v>46250.75</v>
       </c>
       <c r="N192" s="1" t="n">
-        <v>46252.75</v>
+        <v>46253.25</v>
       </c>
       <c r="O192" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46253.00069444445</v>
       </c>
       <c r="P192" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46253.00069444445</v>
       </c>
       <c r="Q192" s="1" t="n">
-        <v>46255.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10489,38 +10489,38 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EVER SUPERB</t>
+          <t>OOCL MIAMI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9300427</t>
+          <t>9477892</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0115S</t>
+          <t>114S</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0115N</t>
+          <t>114N</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46252.5</v>
+        <v>46251.25</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>46254.5</v>
+        <v>46254.25</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="I193" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="J193" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="K193" s="1" t="n">
         <v>46250.75</v>
@@ -10532,21 +10532,21 @@
         <v>46250.75</v>
       </c>
       <c r="N193" s="1" t="n">
-        <v>46253.25</v>
+        <v>46252.75</v>
       </c>
       <c r="O193" s="1" t="n">
-        <v>46253.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="P193" s="1" t="n">
-        <v>46253.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="Q193" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="F199" s="1" t="n">
-        <v>46249.875</v>
+        <v>46249.89583333334</v>
       </c>
       <c r="G199" s="1" t="n">
         <v>46250.91666666666</v>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46250.25</v>
+        <v>46250.1875</v>
       </c>
       <c r="G201" s="1" t="n">
         <v>46250.66666666666</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
         <v>46248.56180555555</v>
       </c>
       <c r="G205" s="1" t="n">
-        <v>46249.6875</v>
+        <v>46249.68680555555</v>
       </c>
       <c r="H205" s="1" t="n">
         <v>46243.91666666666</v>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
         <v>46251.33333333334</v>
       </c>
       <c r="G206" s="1" t="n">
-        <v>46252.41666666666</v>
+        <v>46252.47916666666</v>
       </c>
       <c r="H206" s="1" t="n">
         <v>46241.25</v>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
         <v>46247.70138888889</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>46250.14583333334</v>
+        <v>46250.08333333334</v>
       </c>
       <c r="H211" s="1" t="n">
         <v>46240.58333333334</v>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12306,49 +12306,49 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MAERSK RIO NEGRO</t>
+          <t>SYDNEY EXPRESS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>9357975</t>
+          <t>9723265</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>629S</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F220" s="1" t="n">
-        <v>46243.00416666667</v>
+        <v>46245.52083333334</v>
       </c>
       <c r="G220" s="1" t="n">
-        <v>46244.28819444445</v>
+        <v>46248.375</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>46237.91666666666</v>
-      </c>
-      <c r="I220" s="1" t="n">
-        <v>46239.91666666666</v>
-      </c>
-      <c r="J220" t="inlineStr"/>
+        <v>46237.58333333334</v>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" s="1" t="n">
+        <v>46237.58333333334</v>
+      </c>
       <c r="K220" s="1" t="n">
         <v>46241.91666666666</v>
       </c>
@@ -12356,68 +12356,64 @@
         <v>46241.91666666666</v>
       </c>
       <c r="M220" s="1" t="n">
-        <v>46241.91666666666</v>
-      </c>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="P220" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="Q220" s="1" t="n">
-        <v>46247</v>
-      </c>
+        <v>46244.58333333334</v>
+      </c>
+      <c r="N220" s="1" t="n">
+        <v>46244.625</v>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SYDNEY EXPRESS</t>
+          <t>MAERSK RIO NEGRO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>9723265</t>
+          <t>9357975</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>629S</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="F221" s="1" t="n">
-        <v>46245.52083333334</v>
+        <v>46243.00416666667</v>
       </c>
       <c r="G221" s="1" t="n">
-        <v>46248.375</v>
+        <v>46244.28819444445</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46237.58333333334</v>
-      </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" s="1" t="n">
-        <v>46237.58333333334</v>
-      </c>
+        <v>46237.91666666666</v>
+      </c>
+      <c r="I221" s="1" t="n">
+        <v>46239.91666666666</v>
+      </c>
+      <c r="J221" t="inlineStr"/>
       <c r="K221" s="1" t="n">
         <v>46241.91666666666</v>
       </c>
@@ -12425,22 +12421,26 @@
         <v>46241.91666666666</v>
       </c>
       <c r="M221" s="1" t="n">
-        <v>46244.58333333334</v>
-      </c>
-      <c r="N221" s="1" t="n">
-        <v>46244.625</v>
-      </c>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
+        <v>46241.91666666666</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" s="1" t="n">
+        <v>46244.25</v>
+      </c>
+      <c r="P221" s="1" t="n">
+        <v>46244.25</v>
+      </c>
+      <c r="Q221" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13396,49 +13396,49 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MAERSK YELLOWSTONE</t>
+          <t>OOCL CHICAGO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>9943114</t>
+          <t>9199270</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>626S</t>
+          <t>121S</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>631N</t>
+          <t>121N</t>
         </is>
       </c>
       <c r="F236" s="1" t="n">
-        <v>46237.55625</v>
+        <v>46238.84583333333</v>
       </c>
       <c r="G236" s="1" t="n">
-        <v>46238.48888888889</v>
+        <v>46240.33333333334</v>
       </c>
       <c r="H236" s="1" t="n">
-        <v>46231.91666666666</v>
-      </c>
-      <c r="I236" s="1" t="n">
-        <v>46234.91666666666</v>
-      </c>
-      <c r="J236" t="inlineStr"/>
+        <v>46232.25</v>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" s="1" t="n">
+        <v>46232.25</v>
+      </c>
       <c r="K236" s="1" t="n">
         <v>46236.58333333334</v>
       </c>
@@ -13446,68 +13446,64 @@
         <v>46236.58333333334</v>
       </c>
       <c r="M236" s="1" t="n">
-        <v>46236.58333333334</v>
-      </c>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" s="1" t="n">
-        <v>46238.25</v>
-      </c>
-      <c r="P236" s="1" t="n">
-        <v>46238.25</v>
-      </c>
-      <c r="Q236" s="1" t="n">
-        <v>46241</v>
-      </c>
+        <v>46238.75</v>
+      </c>
+      <c r="N236" s="1" t="n">
+        <v>46239.375</v>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OOCL CHICAGO</t>
+          <t>MAERSK YELLOWSTONE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>9199270</t>
+          <t>9943114</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>121S</t>
+          <t>626S</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>121N</t>
+          <t>631N</t>
         </is>
       </c>
       <c r="F237" s="1" t="n">
-        <v>46238.84583333333</v>
+        <v>46237.55625</v>
       </c>
       <c r="G237" s="1" t="n">
-        <v>46240.33333333334</v>
+        <v>46238.48888888889</v>
       </c>
       <c r="H237" s="1" t="n">
-        <v>46232.25</v>
-      </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" s="1" t="n">
-        <v>46232.25</v>
-      </c>
+        <v>46231.91666666666</v>
+      </c>
+      <c r="I237" s="1" t="n">
+        <v>46234.91666666666</v>
+      </c>
+      <c r="J237" t="inlineStr"/>
       <c r="K237" s="1" t="n">
         <v>46236.58333333334</v>
       </c>
@@ -13515,22 +13511,26 @@
         <v>46236.58333333334</v>
       </c>
       <c r="M237" s="1" t="n">
-        <v>46238.75</v>
-      </c>
-      <c r="N237" s="1" t="n">
-        <v>46239.375</v>
-      </c>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
+        <v>46236.58333333334</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" s="1" t="n">
+        <v>46238.25</v>
+      </c>
+      <c r="P237" s="1" t="n">
+        <v>46238.25</v>
+      </c>
+      <c r="Q237" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13676,29 +13676,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MAERSK FUKUOKA</t>
+          <t>TAKUTAI CHIEF</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>9991147</t>
+          <t>9519327</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>626S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="F240" s="1" t="n">
-        <v>46235.58125</v>
+        <v>46235.33055555556</v>
       </c>
       <c r="G240" s="1" t="n">
-        <v>46237.31597222222</v>
+        <v>46235.89305555556</v>
       </c>
       <c r="H240" s="1" t="n">
         <v>46230.25</v>
@@ -13713,21 +13713,23 @@
       <c r="L240" s="1" t="n">
         <v>46234.58333333334</v>
       </c>
-      <c r="M240" t="inlineStr"/>
+      <c r="M240" s="1" t="n">
+        <v>46235.5</v>
+      </c>
       <c r="N240" s="1" t="n">
-        <v>46235.625</v>
+        <v>46234.58333333334</v>
       </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>BTH1</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13739,29 +13741,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>TAKUTAI CHIEF</t>
+          <t>MAERSK FUKUOKA</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>9519327</t>
+          <t>9991147</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>626S</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2617N</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="F241" s="1" t="n">
-        <v>46235.33055555556</v>
+        <v>46235.58125</v>
       </c>
       <c r="G241" s="1" t="n">
-        <v>46235.89305555556</v>
+        <v>46237.31597222222</v>
       </c>
       <c r="H241" s="1" t="n">
         <v>46230.25</v>
@@ -13776,23 +13778,21 @@
       <c r="L241" s="1" t="n">
         <v>46234.58333333334</v>
       </c>
-      <c r="M241" s="1" t="n">
-        <v>46235.5</v>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" s="1" t="n">
-        <v>46234.58333333334</v>
+        <v>46235.625</v>
       </c>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13804,38 +13804,38 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SEASMILE</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>9632820</t>
+          <t>9926233</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6S</t>
+          <t>0012S</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>6N</t>
+          <t>0012N</t>
         </is>
       </c>
       <c r="F242" s="1" t="n">
-        <v>46235.47083333333</v>
+        <v>46235.02916666667</v>
       </c>
       <c r="G242" s="1" t="n">
-        <v>46236.74166666667</v>
+        <v>46236.99583333333</v>
       </c>
       <c r="H242" s="1" t="n">
-        <v>46232.23958333334</v>
+        <v>46229.73958333334</v>
       </c>
       <c r="I242" s="1" t="n">
-        <v>46232.23958333334</v>
+        <v>46229.73958333334</v>
       </c>
       <c r="J242" s="1" t="n">
-        <v>46232.23958333334</v>
+        <v>46229.73958333334</v>
       </c>
       <c r="K242" s="1" t="n">
         <v>46234.25</v>
@@ -13850,18 +13850,18 @@
         <v>46235.66666666666</v>
       </c>
       <c r="O242" s="1" t="n">
-        <v>46236.00069444445</v>
+        <v>46235.00069444445</v>
       </c>
       <c r="P242" s="1" t="n">
-        <v>46236.00069444445</v>
+        <v>46235.00069444445</v>
       </c>
       <c r="Q242" s="1" t="n">
-        <v>46239.00069444445</v>
+        <v>46238.00069444445</v>
       </c>
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13873,38 +13873,38 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PHOEBE</t>
+          <t>SEASMILE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>9926233</t>
+          <t>9632820</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0012S</t>
+          <t>6S</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0012N</t>
+          <t>6N</t>
         </is>
       </c>
       <c r="F243" s="1" t="n">
-        <v>46235.02916666667</v>
+        <v>46235.47083333333</v>
       </c>
       <c r="G243" s="1" t="n">
-        <v>46236.99583333333</v>
+        <v>46236.74166666667</v>
       </c>
       <c r="H243" s="1" t="n">
-        <v>46229.73958333334</v>
+        <v>46232.23958333334</v>
       </c>
       <c r="I243" s="1" t="n">
-        <v>46229.73958333334</v>
+        <v>46232.23958333334</v>
       </c>
       <c r="J243" s="1" t="n">
-        <v>46229.73958333334</v>
+        <v>46232.23958333334</v>
       </c>
       <c r="K243" s="1" t="n">
         <v>46234.25</v>
@@ -13919,18 +13919,18 @@
         <v>46235.66666666666</v>
       </c>
       <c r="O243" s="1" t="n">
-        <v>46235.00069444445</v>
+        <v>46236.00069444445</v>
       </c>
       <c r="P243" s="1" t="n">
-        <v>46235.00069444445</v>
+        <v>46236.00069444445</v>
       </c>
       <c r="Q243" s="1" t="n">
-        <v>46238.00069444445</v>
+        <v>46239.00069444445</v>
       </c>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14137,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14413,7 +14413,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14559,29 +14559,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MSC JESSENIA R</t>
+          <t>APL VANCOUVER</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>9215672</t>
+          <t>9597472</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>FE624R</t>
+          <t>MA621A</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>KH631A</t>
+          <t>MA629R</t>
         </is>
       </c>
       <c r="F253" s="1" t="n">
-        <v>46234.16666666666</v>
+        <v>46231.84583333333</v>
       </c>
       <c r="G253" s="1" t="n">
-        <v>46235.25</v>
+        <v>46233.67083333333</v>
       </c>
       <c r="H253" s="1" t="n">
         <v>46226.23958333334</v>
@@ -14602,21 +14602,21 @@
         <v>46230.75</v>
       </c>
       <c r="N253" s="1" t="n">
-        <v>46234.5</v>
+        <v>46232.25</v>
       </c>
       <c r="O253" s="1" t="n">
-        <v>46234.00069444445</v>
+        <v>46232.00069444445</v>
       </c>
       <c r="P253" s="1" t="n">
-        <v>46234.00069444445</v>
+        <v>46232.00069444445</v>
       </c>
       <c r="Q253" s="1" t="n">
-        <v>46237.00069444445</v>
+        <v>46235.00069444445</v>
       </c>
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14628,29 +14628,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>APL VANCOUVER</t>
+          <t>MSC JESSENIA R</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>9597472</t>
+          <t>9215672</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>MA621A</t>
+          <t>FE624R</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>MA629R</t>
+          <t>KH631A</t>
         </is>
       </c>
       <c r="F254" s="1" t="n">
-        <v>46231.84583333333</v>
+        <v>46234.16666666666</v>
       </c>
       <c r="G254" s="1" t="n">
-        <v>46233.67083333333</v>
+        <v>46235.25</v>
       </c>
       <c r="H254" s="1" t="n">
         <v>46226.23958333334</v>
@@ -14671,21 +14671,21 @@
         <v>46230.75</v>
       </c>
       <c r="N254" s="1" t="n">
-        <v>46232.25</v>
+        <v>46234.5</v>
       </c>
       <c r="O254" s="1" t="n">
-        <v>46232.00069444445</v>
+        <v>46234.00069444445</v>
       </c>
       <c r="P254" s="1" t="n">
-        <v>46232.00069444445</v>
+        <v>46234.00069444445</v>
       </c>
       <c r="Q254" s="1" t="n">
-        <v>46235.00069444445</v>
+        <v>46237.00069444445</v>
       </c>
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15643,7 +15643,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15781,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16126,7 +16126,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16195,7 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16333,7 +16333,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16666,7 +16666,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16855,7 +16855,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17828,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18293,7 +18293,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18364,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18494,7 +18494,7 @@
       <c r="R311" t="inlineStr"/>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18636,7 +18636,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18916,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -18983,7 +18983,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19125,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19259,7 +19259,7 @@
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19517,7 +19517,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19635,7 +19635,7 @@
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19694,7 @@
       <c r="R329" t="inlineStr"/>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-15 13:24:29</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -1663,34 +1663,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>AAT APPLETON DOCK MELBOURNE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>GREBE ARROW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9077070</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>101S</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>101N</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46261.29166666666</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46262.95833333334</v>
+        <v>46232.8875</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1699,8 +1699,12 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="O20" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
@@ -1712,34 +1716,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COLOMBO</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9256212</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>084S</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>084N</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>46258.25</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46259.95833333334</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1748,14 +1752,14 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="O21" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>46229</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>BTH2</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>2026-08-15 23:57:00</t>
@@ -1770,29 +1774,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OOCL PANAMA</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9355769</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>335S</t>
+          <t>101S</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>335N</t>
+          <t>101N</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46259.625</v>
+        <v>46261.29166666666</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46260.625</v>
+        <v>46262.95833333334</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1807,39 +1811,41 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUBE ADELAIDE FW37J</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RHEA LEADER</t>
+          <t>COLOMBO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9355214</t>
+          <t>9256212</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>084S</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>084N</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46258.25</v>
+      </c>
       <c r="G23" s="1" t="n">
-        <v>46105.52638888889</v>
+        <v>46259.95833333334</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1851,42 +1857,48 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>BTH2</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUBE ADELAIDE FW37J</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>OOCL PANAMA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9355769</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>335S</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>335N</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>46259.625</v>
+      </c>
       <c r="G24" s="1" t="n">
-        <v>46037.5375</v>
+        <v>46260.625</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1901,7 +1913,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -1913,27 +1925,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TULANE</t>
+          <t>RHEA LEADER</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9505089</t>
+          <t>9355214</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EF609</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EF609</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" s="1" t="n">
-        <v>46212.53472222222</v>
+        <v>46105.52638888889</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1948,7 +1960,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -1960,27 +1972,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>152</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" s="1" t="n">
-        <v>46373.36805555555</v>
+        <v>46037.5375</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1995,7 +2007,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2007,27 +2019,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BLUE RIDGE HIGHWAY</t>
+          <t>TULANE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9510151</t>
+          <t>9505089</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>EF609</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>EF609</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" s="1" t="n">
-        <v>46315.35277777778</v>
+        <v>46212.53472222222</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2042,7 +2054,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2054,22 +2066,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RHEA LEADER</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9355214</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>095</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>095</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2089,7 +2101,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2101,27 +2113,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DUGONG ACE</t>
+          <t>BLUE RIDGE HIGHWAY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9777838</t>
+          <t>9510151</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" s="1" t="n">
-        <v>46037.5375</v>
+        <v>46315.35277777778</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2136,7 +2148,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2148,27 +2160,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EUPHRATES HIGHWAY</t>
+          <t>RHEA LEADER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9604926</t>
+          <t>9355214</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>136</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" s="1" t="n">
-        <v>46037.5375</v>
+        <v>46373.36805555555</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2183,7 +2195,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2217,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>046</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>046</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -2230,7 +2242,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2242,27 +2254,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DUGONG ACE</t>
+          <t>EUPHRATES HIGHWAY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9777838</t>
+          <t>9604926</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" s="1" t="n">
-        <v>46315.35277777778</v>
+        <v>46037.5375</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2277,7 +2289,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2311,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>060</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>060</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -2324,7 +2336,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2336,27 +2348,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RHEA LEADER</t>
+          <t>DUGONG ACE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9355214</t>
+          <t>9777838</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>055</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>055</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" s="1" t="n">
-        <v>46105.52638888889</v>
+        <v>46315.35277777778</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2371,7 +2383,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2383,22 +2395,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>DUGONG ACE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9777838</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>047</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>047</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -2418,7 +2430,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2430,27 +2442,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DOVER HIGHWAY</t>
+          <t>RHEA LEADER</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9574107</t>
+          <t>9355214</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" s="1" t="n">
-        <v>46037.5375</v>
+        <v>46105.52638888889</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2465,7 +2477,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2477,27 +2489,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" s="1" t="n">
-        <v>46171.58402777778</v>
+        <v>46037.5375</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2512,7 +2524,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2524,22 +2536,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DUGONG ACE</t>
+          <t>DOVER HIGHWAY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9777838</t>
+          <t>9574107</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2559,7 +2571,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2571,27 +2583,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HOEGH TARGET</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9684976</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>099</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>099</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" s="1" t="n">
-        <v>46056.56666666667</v>
+        <v>46171.58402777778</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2606,38 +2618,40 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>QUBE ADELAIDE FW37J</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MSC CAPE III</t>
+          <t>DUGONG ACE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9360271</t>
+          <t>9777838</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FP539A</t>
+          <t>045</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FP543R</t>
+          <t>045</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" s="1" t="n">
+        <v>46037.5375</v>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2651,41 +2665,39 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>QUBE ADELAIDE FW37J</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MSC SOMYA III</t>
+          <t>HOEGH TARGET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9220328</t>
+          <t>9684976</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KN629A</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KN632R</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>46261.75</v>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" s="1" t="n">
-        <v>46262.75</v>
+        <v>46056.56666666667</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2700,7 +2712,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2712,30 +2724,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MSC DAVAO III</t>
+          <t>MSC CAPE III</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9243241</t>
+          <t>9360271</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KH635A</t>
+          <t>FP539A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KH635A</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>46261.5</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>46262.95833333334</v>
-      </c>
+          <t>FP543R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -2749,7 +2757,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2761,29 +2769,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>MSC SOMYA III</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9220328</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>KN629A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>KN632R</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46261.75</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46258.95833333334</v>
+        <v>46262.75</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2798,7 +2806,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2810,26 +2818,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VICTORIA WEBB</t>
+          <t>MSC DAVAO III</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0123456</t>
+          <t>9243241</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OUT999</t>
+          <t>KH635A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OUT999</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>KH635A</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>46261.5</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46262.95833333334</v>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -2843,7 +2855,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2855,29 +2867,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KN628A</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KN628A</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46244.90833333333</v>
+        <v>46256.95833333334</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46245.39583333334</v>
+        <v>46258.95833333334</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2886,19 +2898,13 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" s="1" t="n">
-        <v>46245.00069444445</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>46245.00069444445</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>46248.00069444445</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2910,22 +2916,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MSC NURYA G</t>
+          <t>VICTORIA WEBB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9955791</t>
+          <t>0123456</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FP610R</t>
+          <t>OUT999</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FP610R</t>
+          <t>OUT999</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -2943,7 +2949,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -2955,26 +2961,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BBC DENMARK</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9605891</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>F006W</t>
+          <t>KN628A</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>F006E</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>KN628A</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>46244.90833333333</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46245.39583333334</v>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -2982,13 +2992,19 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="O47" s="1" t="n">
+        <v>46245.00069444445</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>46245.00069444445</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>46248.00069444445</v>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3000,22 +3016,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MSC TANIA</t>
+          <t>MSC NURYA G</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9316373</t>
+          <t>9955791</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>XA410R</t>
+          <t>FP610R</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>XA410R</t>
+          <t>FP610R</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3033,7 +3049,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3045,30 +3061,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>BBC DENMARK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9363376</t>
+          <t>9605891</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>044S</t>
+          <t>F006W</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>044N</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>46258.25</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>46259.25</v>
-      </c>
+          <t>F006E</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -3082,7 +3094,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3094,30 +3106,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ARTEMIS</t>
+          <t>MSC TANIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9339595</t>
+          <t>9316373</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KN630A</t>
+          <t>XA410R</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KN633R</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>46263.04166666666</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>46264.25</v>
-      </c>
+          <t>XA410R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -3131,7 +3139,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3143,29 +3151,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OOCL CANADA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9477880</t>
+          <t>9363376</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>123S</t>
+          <t>044S</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>123N</t>
+          <t>044N</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
         <v>46258.25</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46260.25</v>
+        <v>46259.25</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3180,7 +3188,7 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3200,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MARTI CROWN</t>
+          <t>ARTEMIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9626247</t>
+          <t>9339595</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>062E</t>
+          <t>KN630A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>062E</t>
+          <t>KN633R</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46260.75</v>
+        <v>46263.04166666666</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46261.5</v>
+        <v>46264.25</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3229,7 +3237,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3241,29 +3249,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VICTORIA WEBB</t>
+          <t>OOCL CANADA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0123456</t>
+          <t>9477880</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>123S</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>123N</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46215.63125</v>
+        <v>46258.25</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46221.41319444445</v>
+        <v>46260.25</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3278,7 +3286,7 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3290,26 +3298,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MSC BEIRA IV</t>
+          <t>MARTI CROWN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9477309</t>
+          <t>9626247</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KN520A</t>
+          <t>062E</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KN520A</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>062E</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>46260.75</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46261.5</v>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -3323,7 +3335,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3335,22 +3347,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OOCL NORFOLK</t>
+          <t>VICTORIA WEBB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9440045</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>0123456</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>056N</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>46215.63125</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46221.41319444445</v>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -3364,7 +3384,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3376,30 +3396,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COSCO ISTANBUL</t>
+          <t>MSC BEIRA IV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9484340</t>
+          <t>9477309</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>094S</t>
+          <t>KN520A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>094N</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>46265.25</v>
-      </c>
+          <t>KN520A</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3413,7 +3429,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3425,22 +3441,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MSC MELANI III</t>
+          <t>OOCL NORFOLK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9399741</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FE629A</t>
-        </is>
-      </c>
+          <t>9440045</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FE629A</t>
+          <t>056N</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -3458,7 +3470,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3482,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GREENVILLE</t>
+          <t>COSCO ISTANBUL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9970014</t>
+          <t>9484340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FE614A</t>
+          <t>094S</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FE614A</t>
+          <t>094N</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46114.04166666666</v>
+        <v>46264.25</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46115.25</v>
+        <v>46265.25</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3507,7 +3519,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3519,30 +3531,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MSC NURYA G</t>
+          <t>MSC MELANI III</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9955791</t>
+          <t>9399741</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FE635A</t>
+          <t>FE629A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FE635A</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="n">
-        <v>46260.75</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>46261.75</v>
-      </c>
+          <t>FE629A</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3556,7 +3564,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3568,29 +3576,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VICTORIA WEBB</t>
+          <t>GREENVILLE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0123456</t>
+          <t>9970014</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>999S</t>
+          <t>FE614A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>999N</t>
+          <t>FE614A</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46217.58333333334</v>
+        <v>46114.04166666666</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46350.58333333334</v>
+        <v>46115.25</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3605,7 +3613,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3617,26 +3625,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MSC NIMISHA III</t>
+          <t>MSC NURYA G</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9315886</t>
+          <t>9955791</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FP538A</t>
+          <t>FE635A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FP542R</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>FE635A</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>46260.75</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46261.75</v>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -3650,7 +3662,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3662,29 +3674,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MSC CAPETOWN III</t>
+          <t>VICTORIA WEBB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9311737</t>
+          <t>0123456</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FP628A</t>
+          <t>999S</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FP632R</t>
+          <t>999N</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46257.75</v>
+        <v>46217.58333333334</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46258.75</v>
+        <v>46350.58333333334</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3699,7 +3711,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3711,30 +3723,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MSC JOANNA</t>
+          <t>MSC NIMISHA III</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9304435</t>
+          <t>9315886</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MA624A</t>
+          <t>FP538A</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MA632R</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>46258.75</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46260.75</v>
-      </c>
+          <t>FP542R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3748,7 +3756,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3760,26 +3768,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>MSC CAPETOWN III</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9311737</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KH623R</t>
+          <t>FP628A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KN625R</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+          <t>FP632R</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>46257.75</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46258.75</v>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -3793,7 +3805,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3805,26 +3817,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MSC NURYA G</t>
+          <t>MSC JOANNA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9955791</t>
+          <t>9304435</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KN523R</t>
+          <t>MA624A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KN523R</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>MA632R</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>46258.75</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46260.75</v>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3838,7 +3854,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3850,30 +3866,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MSC UNITY VI</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9169158</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KQ630A</t>
+          <t>KH623R</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KQ635R</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="n">
-        <v>46262.75</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>46264.75</v>
-      </c>
+          <t>KN625R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -3887,7 +3899,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3899,52 +3911,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VICTORIA WEBB</t>
+          <t>MSC NURYA G</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0123456</t>
+          <t>9955791</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GSL999</t>
+          <t>KN523R</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GSL999</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="n">
-        <v>46235.99861111111</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>46235.99930555555</v>
-      </c>
-      <c r="H67" s="1" t="n">
-        <v>46212.25</v>
-      </c>
-      <c r="I67" s="1" t="n">
-        <v>46212.25</v>
-      </c>
-      <c r="J67" s="1" t="n">
-        <v>46212.25</v>
-      </c>
+          <t>KN523R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="1" t="n">
-        <v>46234.99861111111</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -3956,26 +3956,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MSC MARITINA V</t>
+          <t>MSC UNITY VI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9294408</t>
+          <t>9169158</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KN602A</t>
+          <t>KQ630A</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KN602A</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+          <t>KQ635R</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>46262.75</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>46264.75</v>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -3989,95 +3993,95 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OLIVIA MAERSK</t>
+          <t>VICTORIA WEBB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9251638</t>
+          <t>0123456</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>GSL999</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>635N</t>
+          <t>GSL999</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46262.54166666666</v>
+        <v>46235.99861111111</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46263.91666666666</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+        <v>46235.99930555555</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>46212.25</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>46212.25</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>46212.25</v>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" s="1" t="n">
+        <v>46234.99861111111</v>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>MSC MARITINA V</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9294408</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>KN602A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>008N</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="n">
-        <v>46253.91666666666</v>
-      </c>
-      <c r="G70" s="1" t="n">
-        <v>46255.75</v>
-      </c>
+          <t>KN602A</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -4088,14 +4092,10 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4107,29 +4107,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46263.58333333334</v>
+        <v>46255.75</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4143,12 +4143,12 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4213,29 +4213,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CMA CGM NEVA</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9745548</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46263.91666666666</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46264.58333333334</v>
+        <v>46261.39583333334</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4249,12 +4249,12 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4372,29 +4372,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46261.39583333334</v>
+        <v>46263.58333333334</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4408,46 +4408,46 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AAT APPLETON DOCK MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>CMA CGM NEVA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9745548</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46266.25</v>
+        <v>46263.91666666666</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46268.25</v>
+        <v>46264.58333333334</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4459,44 +4459,48 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AAT APPLETON DOCK MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>OLIVIA MAERSK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9251638</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>635N</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46269.25</v>
+        <v>46262.54166666666</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46271.25</v>
+        <v>46263.91666666666</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4508,10 +4512,14 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4523,29 +4531,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46229.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46232.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4560,7 +4568,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4572,29 +4580,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46269.25</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46271.25</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4609,7 +4617,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4621,29 +4629,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GREBE ARROW</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9077070</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46228.99305555555</v>
+        <v>46229.25</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46232.8875</v>
+        <v>46232.25</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4652,17 +4660,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4678,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4693,10 +4697,10 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46260.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46262.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4711,41 +4715,41 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AAT VICTORIA DOCK - GG43P</t>
+          <t>AAT APPLETON DOCK MELBOURNE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AAL BANGKOK</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9521564</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46089.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46092.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4760,41 +4764,41 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>AAT VICTORIA DOCK - GG43P</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NABUCCO</t>
+          <t>AAL BANGKOK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9731652</t>
+          <t>9521564</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46231.37013888889</v>
+        <v>46089.25</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46232.62847222222</v>
+        <v>46092.25</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -4803,17 +4807,13 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P84" s="1" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4825,29 +4825,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HOEGH TRACER</t>
+          <t>NABUCCO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9684990</t>
+          <t>9731652</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46229.77361111111</v>
+        <v>46231.37013888889</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46230.58333333334</v>
+        <v>46232.62847222222</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -4857,16 +4857,16 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4878,29 +4878,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CHESAPEAKE HIGHWAY</t>
+          <t>HOEGH TRACER</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9565546</t>
+          <t>9684990</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F86" s="1" t="n">
-        <v>46236.03611111111</v>
+        <v>46229.77361111111</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46237.14305555556</v>
+        <v>46230.58333333334</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -4910,16 +4910,16 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" s="1" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4931,29 +4931,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HOEGH SHANGHAI</t>
+          <t>CHESAPEAKE HIGHWAY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9312482</t>
+          <t>9565546</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46241.45625</v>
+        <v>46236.03611111111</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46242.90902777778</v>
+        <v>46237.14305555556</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4963,16 +4963,16 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" s="1" t="n">
-        <v>46243</v>
+        <v>46237</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46243</v>
+        <v>46237</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -4984,29 +4984,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>HOEGH SHANGHAI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9312482</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F88" s="1" t="n">
-        <v>46232.35902777778</v>
+        <v>46241.45625</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46286.5</v>
+        <v>46242.90902777778</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5015,13 +5015,17 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="O88" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P88" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5033,29 +5037,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F89" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5064,17 +5068,13 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P89" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5086,29 +5086,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F90" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46232.35902777778</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5135,29 +5135,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F91" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46234.425</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -5172,7 +5172,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5184,29 +5184,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F92" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46286.25</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -5215,17 +5215,13 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P92" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5237,29 +5233,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F93" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46235.60625</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -5268,13 +5264,17 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="O93" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5286,29 +5286,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F94" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46233.06736111111</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -5317,13 +5317,17 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="O94" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5335,29 +5339,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F95" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46233.6875</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5366,13 +5370,17 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="O95" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P95" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5384,29 +5392,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F96" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46240.33125</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46339.2625</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -5415,17 +5423,13 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P96" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5437,29 +5441,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F97" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46231.89444444444</v>
+        <v>46339.2625</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -5468,17 +5472,13 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="P97" s="1" t="n">
-        <v>46231</v>
-      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5490,29 +5490,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F98" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5539,29 +5539,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F99" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
@@ -5571,16 +5571,16 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" s="1" t="n">
-        <v>46243</v>
+        <v>46235</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>46243</v>
+        <v>46235</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5592,29 +5592,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F100" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
@@ -5629,7 +5629,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5641,29 +5641,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F101" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.5</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5690,26 +5690,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F102" s="1" t="n">
-        <v>46245.31180555555</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G102" s="1" t="n">
         <v>46286.2625</v>
@@ -5727,7 +5727,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5739,29 +5739,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F103" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46363.2625</v>
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -5770,17 +5770,13 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P103" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5792,29 +5788,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F104" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G104" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46363.2625</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
@@ -5823,17 +5819,13 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P104" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5845,26 +5837,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F105" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G105" s="1" t="n">
         <v>46339.2625</v>
@@ -5882,7 +5874,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5894,29 +5886,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F106" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G106" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
@@ -5925,13 +5917,17 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
+      <c r="O106" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P106" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5943,29 +5939,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F107" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46243.01875</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
@@ -5974,13 +5970,17 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
+      <c r="O107" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P107" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -5992,29 +5992,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F108" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G108" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -6029,7 +6029,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6041,29 +6041,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F109" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46231.52222222222</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -6073,16 +6073,16 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" s="1" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="P109" s="1" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6094,29 +6094,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F110" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G110" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -6125,13 +6125,17 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
+      <c r="O110" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P110" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6143,29 +6147,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F111" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
@@ -6174,17 +6178,13 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P111" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6196,29 +6196,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F112" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G112" s="1" t="n">
-        <v>46286.25</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -6227,13 +6227,17 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="O112" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P112" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6245,26 +6249,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F113" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G113" s="1" t="n">
         <v>46339.2625</v>
@@ -6282,7 +6286,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6294,29 +6298,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F114" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -6331,7 +6335,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6343,29 +6347,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F115" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46237.34375</v>
       </c>
       <c r="G115" s="1" t="n">
-        <v>46286.5</v>
+        <v>46286.2625</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -6380,7 +6384,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6392,29 +6396,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F116" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G116" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -6424,16 +6428,16 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" s="1" t="n">
-        <v>46233</v>
+        <v>46248</v>
       </c>
       <c r="P116" s="1" t="n">
-        <v>46233</v>
+        <v>46248</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6445,29 +6449,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F117" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G117" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46286.2625</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -6476,17 +6480,13 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P117" s="1" t="n">
-        <v>46233</v>
-      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6498,29 +6498,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F118" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46245.29375</v>
       </c>
       <c r="G118" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46363.2625</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -6529,17 +6529,13 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P118" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6551,29 +6547,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F119" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G119" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -6588,7 +6584,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6600,29 +6596,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F120" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G120" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -6632,16 +6628,16 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="P120" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6653,29 +6649,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F121" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G121" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46233.9375</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -6685,16 +6681,16 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" s="1" t="n">
-        <v>46248</v>
+        <v>46234</v>
       </c>
       <c r="P121" s="1" t="n">
-        <v>46248</v>
+        <v>46234</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6706,26 +6702,26 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F122" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G122" s="1" t="n">
         <v>46339.2625</v>
@@ -6743,7 +6739,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6755,29 +6751,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F123" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G123" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -6786,13 +6782,17 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+      <c r="O123" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P123" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6804,29 +6804,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F124" s="1" t="n">
-        <v>46234.425</v>
+        <v>46245.31180555555</v>
       </c>
       <c r="G124" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6853,29 +6853,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F125" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46242.5125</v>
       </c>
       <c r="G125" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -6884,13 +6884,17 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+      <c r="O125" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P125" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6902,29 +6906,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F126" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G126" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -6933,17 +6937,13 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P126" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -6955,29 +6955,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F127" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G127" s="1" t="n">
-        <v>46229.39097222222</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -6987,16 +6987,16 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="P127" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7008,29 +7008,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F128" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46229.3625</v>
       </c>
       <c r="G128" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -7039,13 +7039,17 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
+      <c r="O128" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="P128" s="1" t="n">
+        <v>46232</v>
+      </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7057,29 +7061,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F129" s="1" t="n">
-        <v>46237.32916666667</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G129" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46231.89444444444</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -7089,16 +7093,16 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" s="1" t="n">
-        <v>46250</v>
+        <v>46231</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>46250</v>
+        <v>46231</v>
       </c>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7110,29 +7114,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F130" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46237.32916666667</v>
       </c>
       <c r="G130" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
@@ -7142,16 +7146,16 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" s="1" t="n">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7163,29 +7167,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F131" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46245.31875</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46363.2625</v>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
@@ -7194,17 +7198,13 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P131" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8904,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9030,12 +9030,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9049,17 +9049,17 @@
         </is>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46386.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G170" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46104.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" s="1" t="n">
-        <v>46284.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" s="1" t="n">
@@ -9075,7 +9075,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9106,17 +9106,17 @@
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46204.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G171" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46104.25</v>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" s="1" t="n">
@@ -9132,7 +9132,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9307,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10008,26 +10008,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>HANSA FREYBURG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9256389</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051W</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051E</t>
         </is>
       </c>
       <c r="F186" s="1" t="n">
-        <v>46254.25</v>
+        <v>46254.5</v>
       </c>
       <c r="G186" s="1" t="n">
         <v>46255.25</v>
@@ -10065,7 +10065,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10077,26 +10077,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HANSA FREYBURG</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>9256389</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>051W</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>051E</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46254.5</v>
+        <v>46254.25</v>
       </c>
       <c r="G187" s="1" t="n">
         <v>46255.25</v>
@@ -10134,7 +10134,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10219,29 +10219,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F189" s="1" t="n">
-        <v>46253.02083333334</v>
+        <v>46280.25</v>
       </c>
       <c r="G189" s="1" t="n">
-        <v>46253.91666666666</v>
+        <v>46281.58333333334</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46247.25</v>
+        <v>46246.91666666666</v>
       </c>
       <c r="I189" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46251.93055555555</v>
       </c>
       <c r="L189" s="1" t="n">
         <v>46251.91666666666</v>
@@ -10250,23 +10250,17 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="P189" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="Q189" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10288,29 +10282,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46280.25</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="G190" s="1" t="n">
-        <v>46281.58333333334</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46246.91666666666</v>
+        <v>46247.25</v>
       </c>
       <c r="I190" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" s="1" t="n">
-        <v>46251.93055555555</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="L190" s="1" t="n">
         <v>46251.91666666666</v>
@@ -10319,17 +10313,23 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
+      <c r="O190" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="P190" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="Q190" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10542,38 +10542,38 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EVER SUPERB</t>
+          <t>OOCL MIAMI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>9300427</t>
+          <t>9477892</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0115S</t>
+          <t>114S</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>0115N</t>
+          <t>114N</t>
         </is>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46252.5</v>
+        <v>46251.25</v>
       </c>
       <c r="G194" s="1" t="n">
-        <v>46254.5</v>
+        <v>46254.25</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="I194" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="J194" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="K194" s="1" t="n">
         <v>46250.75</v>
@@ -10585,21 +10585,21 @@
         <v>46250.75</v>
       </c>
       <c r="N194" s="1" t="n">
-        <v>46253.25</v>
+        <v>46252.75</v>
       </c>
       <c r="O194" s="1" t="n">
-        <v>46253.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="P194" s="1" t="n">
-        <v>46253.00069444445</v>
+        <v>46252.00069444445</v>
       </c>
       <c r="Q194" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10611,38 +10611,38 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PRIDE C</t>
+          <t>EVER SUPERB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>9978640</t>
+          <t>9300427</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>030W</t>
+          <t>0115S</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>030E</t>
+          <t>0115N</t>
         </is>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46251.25</v>
+        <v>46252.5</v>
       </c>
       <c r="G195" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46254.5</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="I195" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="J195" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="K195" s="1" t="n">
         <v>46250.75</v>
@@ -10654,21 +10654,21 @@
         <v>46250.75</v>
       </c>
       <c r="N195" s="1" t="n">
-        <v>46251.45833333334</v>
+        <v>46253.25</v>
       </c>
       <c r="O195" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46253.00069444445</v>
       </c>
       <c r="P195" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46253.00069444445</v>
       </c>
       <c r="Q195" s="1" t="n">
-        <v>46255.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10680,38 +10680,38 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>OOCL MIAMI</t>
+          <t>PRIDE C</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>9477892</t>
+          <t>9978640</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>114S</t>
+          <t>030W</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>114N</t>
+          <t>030E</t>
         </is>
       </c>
       <c r="F196" s="1" t="n">
         <v>46251.25</v>
       </c>
       <c r="G196" s="1" t="n">
-        <v>46254.25</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="I196" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="J196" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="K196" s="1" t="n">
         <v>46250.75</v>
@@ -10723,7 +10723,7 @@
         <v>46250.75</v>
       </c>
       <c r="N196" s="1" t="n">
-        <v>46252.75</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="O196" s="1" t="n">
         <v>46252.00069444445</v>
@@ -10737,7 +10737,7 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11074,49 +11074,49 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CMA CGM GREEN</t>
+          <t>OOCL YOKOHAMA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>9810915</t>
+          <t>9329538</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>213S</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>213N</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46250.1875</v>
+        <v>46250.11458333334</v>
       </c>
       <c r="G202" s="1" t="n">
-        <v>46250.66666666666</v>
+        <v>46251.625</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46244.91666666666</v>
-      </c>
-      <c r="I202" s="1" t="n">
-        <v>46246.91666666666</v>
-      </c>
-      <c r="J202" t="inlineStr"/>
+        <v>46244.25</v>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" s="1" t="n">
+        <v>46244.25</v>
+      </c>
       <c r="K202" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
@@ -11124,68 +11124,64 @@
         <v>46248.91666666666</v>
       </c>
       <c r="M202" s="1" t="n">
-        <v>46248.91666666666</v>
-      </c>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" s="1" t="n">
-        <v>46250.58333333334</v>
-      </c>
-      <c r="P202" s="1" t="n">
-        <v>46250.58333333334</v>
-      </c>
-      <c r="Q202" s="1" t="n">
-        <v>46254</v>
-      </c>
+        <v>46250.5</v>
+      </c>
+      <c r="N202" s="1" t="n">
+        <v>46249.08333333334</v>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>OOCL YOKOHAMA</t>
+          <t>CMA CGM GREEN</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9329538</t>
+          <t>9810915</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>213S</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>213N</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46250.25</v>
+        <v>46250.1875</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>46251.625</v>
+        <v>46250.66666666666</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" s="1" t="n">
-        <v>46244.25</v>
-      </c>
+        <v>46244.91666666666</v>
+      </c>
+      <c r="I203" s="1" t="n">
+        <v>46246.91666666666</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
@@ -11193,22 +11189,26 @@
         <v>46248.91666666666</v>
       </c>
       <c r="M203" s="1" t="n">
-        <v>46250.5</v>
-      </c>
-      <c r="N203" s="1" t="n">
-        <v>46249.08333333334</v>
-      </c>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
+        <v>46248.91666666666</v>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="1" t="n">
+        <v>46250.58333333334</v>
+      </c>
+      <c r="P203" s="1" t="n">
+        <v>46250.58333333334</v>
+      </c>
+      <c r="Q203" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11285,26 +11285,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OOCL TEXAS</t>
+          <t>MSC DAISY</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>9329552</t>
+          <t>9295165</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>230S</t>
+          <t>KQ628A</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>230N</t>
+          <t>KQ633R</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46250.0625</v>
+        <v>46249.98958333334</v>
       </c>
       <c r="G205" s="1" t="n">
         <v>46251.25</v>
@@ -11328,7 +11328,7 @@
         <v>46248.5</v>
       </c>
       <c r="N205" s="1" t="n">
-        <v>46249.25</v>
+        <v>46248.75</v>
       </c>
       <c r="O205" s="1" t="n">
         <v>46250.00069444445</v>
@@ -11342,7 +11342,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11354,26 +11354,26 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MSC DAISY</t>
+          <t>OOCL TEXAS</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>9295165</t>
+          <t>9329552</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>KQ628A</t>
+          <t>230S</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KQ633R</t>
+          <t>230N</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46249.95833333334</v>
+        <v>46250.08333333334</v>
       </c>
       <c r="G206" s="1" t="n">
         <v>46251.25</v>
@@ -11397,7 +11397,7 @@
         <v>46248.5</v>
       </c>
       <c r="N206" s="1" t="n">
-        <v>46248.75</v>
+        <v>46249.25</v>
       </c>
       <c r="O206" s="1" t="n">
         <v>46250.00069444445</v>
@@ -11411,7 +11411,7 @@
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11480,49 +11480,51 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>9919254</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46251.33333333334</v>
+        <v>46247.375</v>
       </c>
       <c r="G208" s="1" t="n">
-        <v>46252.47916666666</v>
+        <v>46250.99305555555</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46241.25</v>
+        <v>46241.23958333334</v>
       </c>
       <c r="I208" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="J208" t="inlineStr"/>
+        <v>46241.23958333334</v>
+      </c>
+      <c r="J208" s="1" t="n">
+        <v>46241.23958333334</v>
+      </c>
       <c r="K208" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -11532,68 +11534,64 @@
       <c r="M208" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" s="1" t="n">
+        <v>46247.91666666666</v>
+      </c>
       <c r="O208" s="1" t="n">
-        <v>46252.58333333334</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="P208" s="1" t="n">
-        <v>46252.58333333334</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="Q208" s="1" t="n">
-        <v>46256</v>
-      </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46251.00069444445</v>
+      </c>
+      <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9919254</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="F209" s="1" t="n">
-        <v>46247.375</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="G209" s="1" t="n">
-        <v>46249.95833333334</v>
+        <v>46252.47916666666</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46241.23958333334</v>
+        <v>46241.25</v>
       </c>
       <c r="I209" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
-      <c r="J209" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
+        <v>46244.25</v>
+      </c>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -11603,22 +11601,24 @@
       <c r="M209" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N209" s="1" t="n">
-        <v>46247.91666666666</v>
-      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="P209" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="Q209" s="1" t="n">
-        <v>46251.00069444445</v>
-      </c>
-      <c r="R209" t="inlineStr"/>
+        <v>46256</v>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12968,7 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13380,7 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14190,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14535,7 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14807,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15217,7 +15217,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15765,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16110,7 @@
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16317,7 +16317,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16589,7 +16589,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16719,7 +16719,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17491,7 +17491,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17556,7 +17556,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17946,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
       <c r="R312" t="inlineStr"/>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19312,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19383,7 +19383,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19570,7 @@
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19629,7 +19629,7 @@
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19688,7 @@
       <c r="R329" t="inlineStr"/>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19806,7 +19806,7 @@
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -2657,7 +2657,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -2984,29 +2984,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HOEGH SHANGHAI</t>
+          <t>HORIZON HIGHWAY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9312482</t>
+          <t>9726700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>097</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>097</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46241.45625</v>
+        <v>46250.93055555555</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46242.90902777778</v>
+        <v>46251.98055555556</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -3016,16 +3016,16 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3037,29 +3037,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>HOEGH SHANGHAI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9312482</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46241.45625</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.90902777778</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3068,13 +3068,17 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3090,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46234.425</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -3117,17 +3121,13 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3139,29 +3139,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -3170,17 +3170,13 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3188,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -3229,7 +3225,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3241,29 +3237,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3272,17 +3268,13 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3294,29 +3286,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -3325,13 +3317,17 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="O50" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3343,29 +3339,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3380,7 +3376,7 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3429,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3445,29 +3441,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3476,13 +3472,17 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="O53" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3494,29 +3494,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3526,16 +3526,16 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" s="1" t="n">
-        <v>46234</v>
+        <v>46247</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46234</v>
+        <v>46247</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3547,29 +3547,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46237.34166666667</v>
+        <v>46245.29375</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3578,17 +3578,13 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>46253</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3600,26 +3596,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46363.2625</v>
@@ -3637,7 +3633,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3649,29 +3645,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3686,7 +3682,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3698,29 +3694,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46243.01875</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3730,16 +3726,16 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3751,29 +3747,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46286.25</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3782,17 +3778,13 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3804,29 +3796,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46242.5125</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46243.0625</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3836,16 +3828,16 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" s="1" t="n">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3857,29 +3849,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46237.34375</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3888,17 +3880,13 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3910,29 +3898,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3941,13 +3929,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -3959,26 +3951,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>46339.2625</v>
@@ -3996,7 +3988,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4008,29 +4000,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HOEGH AUSTRALIS</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9962691</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46234.37916666667</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46286.25</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4040,16 +4032,16 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" s="1" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4061,29 +4053,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4092,13 +4084,17 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="O65" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4110,29 +4106,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46286.2625</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4141,17 +4137,13 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4163,29 +4155,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4195,16 +4187,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4216,29 +4208,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46245.31875</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46286.5</v>
+        <v>46363.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4253,7 +4245,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4265,29 +4257,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4302,7 +4294,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4314,29 +4306,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46240.33125</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46286.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4351,7 +4343,7 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4363,29 +4355,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4394,13 +4386,17 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="O71" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P71" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4412,29 +4408,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46235.60625</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4444,16 +4440,16 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" s="1" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4465,29 +4461,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46237.34652777778</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46316.2625</v>
+        <v>46233.9375</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4497,16 +4493,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" s="1" t="n">
-        <v>46254</v>
+        <v>46234</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46254</v>
+        <v>46234</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4518,26 +4514,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G74" s="1" t="n">
         <v>46339.2625</v>
@@ -4555,7 +4551,7 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4567,29 +4563,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46237.34652777778</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46316.2625</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4598,13 +4594,17 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="O75" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46237.34166666667</v>
       </c>
       <c r="G76" s="1" t="n">
         <v>46286.2625</v>
@@ -4647,13 +4647,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="O76" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>46253</v>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4665,29 +4669,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4696,13 +4700,17 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="O77" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4714,29 +4722,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46339.2625</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4745,17 +4753,13 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P78" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4767,29 +4771,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46234.425</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4798,13 +4802,17 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4816,29 +4824,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46363.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4847,17 +4855,13 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P80" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4869,29 +4873,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4900,17 +4904,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4922,29 +4922,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46286.5</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4953,17 +4953,13 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P82" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -4975,29 +4971,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -5007,16 +5003,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5028,29 +5024,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -5059,13 +5055,17 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="O84" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ANDROKLIS</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9961441</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46266.91666666666</v>
+        <v>46266.75</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46267.8125</v>
+        <v>46268.75</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8640,12 +8640,12 @@
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8657,29 +8657,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46266.75</v>
+        <v>46257.25</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46268.75</v>
+        <v>46258.91666666666</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8763,29 +8763,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>ANDROKLIS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9961441</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46257.25</v>
+        <v>46266.91666666666</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46258.91666666666</v>
+        <v>46267.8125</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -8799,12 +8799,12 @@
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8816,29 +8816,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46269.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>46271.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8865,29 +8865,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46260.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>46262.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
@@ -8902,7 +8902,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8914,29 +8914,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46260.25</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46262.25</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -8963,29 +8963,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F167" s="1" t="n">
-        <v>46266.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G167" s="1" t="n">
-        <v>46268.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
@@ -9000,7 +9000,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9061,29 +9061,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CHESAPEAKE HIGHWAY</t>
+          <t>HOEGH AUSTRALIS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>9565546</t>
+          <t>9962691</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46236.03611111111</v>
+        <v>46234.37916666667</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>46237.14305555556</v>
+        <v>46286.25</v>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -9093,16 +9093,16 @@
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" s="1" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="P169" s="1" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HORIZON HIGHWAY</t>
+          <t>CHESAPEAKE HIGHWAY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>9726700</t>
+          <t>9565546</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46250.93055555555</v>
+        <v>46236.03611111111</v>
       </c>
       <c r="G170" s="1" t="n">
-        <v>46251.98055555556</v>
+        <v>46237.14305555556</v>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -9146,16 +9146,16 @@
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" s="1" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="P170" s="1" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9468,12 +9468,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9487,17 +9487,17 @@
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46356.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46268</v>
+        <v>46104.25</v>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" s="1" t="n">
-        <v>46268</v>
+        <v>46284.25</v>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" s="1" t="n">
@@ -9513,7 +9513,7 @@
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9544,17 +9544,17 @@
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46096.125</v>
+        <v>46204.25</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" s="1" t="n">
@@ -9570,7 +9570,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9601,17 +9601,17 @@
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46386.25</v>
+        <v>46356.25</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46104.25</v>
+        <v>46268</v>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" s="1" t="n">
-        <v>46284.25</v>
+        <v>46268</v>
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" s="1" t="n">
@@ -9627,7 +9627,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9658,17 +9658,17 @@
         </is>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46204.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" s="1" t="n">
@@ -9684,7 +9684,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10237,133 +10237,133 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OOCL PANAMA</t>
+          <t>GREEN WAVE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>9355769</t>
+          <t>9867724</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>335S</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>335N</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F189" s="1" t="n">
-        <v>46259.625</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="G189" s="1" t="n">
-        <v>46260.625</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>46254.25</v>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" s="1" t="n">
-        <v>46254.25</v>
-      </c>
+        <v>46253.91666666666</v>
+      </c>
+      <c r="I189" s="1" t="n">
+        <v>46256.91666666666</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L189" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" s="1" t="n">
+      <c r="M189" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GREEN WAVE</t>
+          <t>OOCL PANAMA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>9867724</t>
+          <t>9355769</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>335S</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>335N</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46259.625</v>
       </c>
       <c r="G190" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46260.625</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46253.91666666666</v>
-      </c>
-      <c r="I190" s="1" t="n">
-        <v>46256.91666666666</v>
-      </c>
-      <c r="J190" t="inlineStr"/>
+        <v>46254.25</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" s="1" t="n">
+        <v>46254.25</v>
+      </c>
       <c r="K190" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L190" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M190" s="1" t="n">
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11232,29 +11232,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>HANSA FREYBURG</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9256389</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051W</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051E</t>
         </is>
       </c>
       <c r="F204" s="1" t="n">
+        <v>46255.5</v>
+      </c>
+      <c r="G204" s="1" t="n">
         <v>46256.25</v>
-      </c>
-      <c r="G204" s="1" t="n">
-        <v>46257.25</v>
       </c>
       <c r="H204" s="1" t="n">
         <v>46249.23958333334</v>
@@ -11278,18 +11278,18 @@
         <v>46253.75</v>
       </c>
       <c r="O204" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="P204" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="Q204" s="1" t="n">
-        <v>46260.00069444445</v>
+        <v>46259.00069444445</v>
       </c>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11301,29 +11301,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HANSA FREYBURG</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>9256389</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>051W</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>051E</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46255.5</v>
+        <v>46256.25</v>
       </c>
       <c r="G205" s="1" t="n">
-        <v>46256.25</v>
+        <v>46257.25</v>
       </c>
       <c r="H205" s="1" t="n">
         <v>46249.23958333334</v>
@@ -11347,18 +11347,18 @@
         <v>46253.75</v>
       </c>
       <c r="O205" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="P205" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="Q205" s="1" t="n">
-        <v>46259.00069444445</v>
+        <v>46260.00069444445</v>
       </c>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46253.10416666666</v>
+        <v>46253.12708333333</v>
       </c>
       <c r="G208" s="1" t="n">
         <v>46253.91666666666</v>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11721,7 +11721,7 @@
         <v>46251.69444444445</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>46252.99930555555</v>
+        <v>46253.02222222222</v>
       </c>
       <c r="H211" s="1" t="n">
         <v>46246.25</v>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11963,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12568,7 @@
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12637,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13516,7 @@
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14125,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14470,7 @@
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15554,7 +15554,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16305,7 +16305,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16581,7 +16581,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16719,7 +16719,7 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16788,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17064,7 +17064,7 @@
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17913,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18368,7 +18368,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18433,7 +18433,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19022,7 +19022,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19507,7 +19507,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       <c r="R334" t="inlineStr"/>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20258,7 +20258,7 @@
       <c r="R337" t="inlineStr"/>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20317,7 +20317,7 @@
       <c r="R338" t="inlineStr"/>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20376,7 +20376,7 @@
       <c r="R339" t="inlineStr"/>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20435,7 +20435,7 @@
       <c r="R340" t="inlineStr"/>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20494,7 +20494,7 @@
       <c r="R341" t="inlineStr"/>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20553,7 @@
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20612,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-19 00:58:09</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -2876,7 +2876,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3068,29 +3068,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46235.07847222222</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -3099,13 +3099,17 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="O44" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3117,29 +3121,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3148,13 +3152,17 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>46248</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3166,29 +3174,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46237.34375</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46286.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -3203,7 +3211,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3215,29 +3223,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46240.33125</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46339.2625</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -3246,17 +3254,13 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>46254</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3268,29 +3272,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46242.5125</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -3299,13 +3303,17 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="O48" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3317,29 +3325,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46339.2625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3348,17 +3356,13 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>46253</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3370,29 +3374,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46339.2625</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -3401,17 +3405,13 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3423,29 +3423,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3454,13 +3454,17 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="O51" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3472,29 +3476,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3503,13 +3507,17 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="O52" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P52" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3570,7 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3574,29 +3582,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3611,7 +3619,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3623,29 +3631,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46245.29375</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46363.2625</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3654,17 +3662,13 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3676,29 +3680,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3707,17 +3711,13 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3729,29 +3729,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3778,29 +3778,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3810,16 +3810,16 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" s="1" t="n">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3831,29 +3831,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46233.9375</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3863,16 +3863,16 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" s="1" t="n">
-        <v>46243</v>
+        <v>46234</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46243</v>
+        <v>46234</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3884,29 +3884,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3915,13 +3915,17 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="O60" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3933,29 +3937,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3964,13 +3968,17 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -3982,29 +3990,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4014,16 +4022,16 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" s="1" t="n">
-        <v>46250</v>
+        <v>46243</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46250</v>
+        <v>46243</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4035,26 +4043,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>46363.2625</v>
@@ -4072,7 +4080,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4084,29 +4092,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.25</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4121,7 +4129,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4133,29 +4141,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46253.44375</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46235.63472222222</v>
+        <v>46288.25</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4164,17 +4172,13 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4186,29 +4190,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4223,7 +4227,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4235,29 +4239,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46288.25</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4266,13 +4270,17 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="O67" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4284,29 +4292,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46242.26875</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4325,7 +4333,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4337,29 +4345,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4368,17 +4376,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4390,29 +4394,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46234.425</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46339.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4422,16 +4426,16 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" s="1" t="n">
-        <v>46242</v>
+        <v>46255</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46242</v>
+        <v>46255</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4443,29 +4447,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46243.01875</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4475,16 +4479,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4496,29 +4500,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4527,17 +4531,13 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P72" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4549,29 +4549,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4598,29 +4598,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4630,16 +4630,16 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4651,26 +4651,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G75" s="1" t="n">
         <v>46339.2625</v>
@@ -4688,7 +4688,7 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4700,29 +4700,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46235.60625</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4731,13 +4731,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="O76" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4749,29 +4753,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4780,17 +4784,13 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P77" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4802,29 +4802,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4834,16 +4834,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46250</v>
+        <v>46238</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46250</v>
+        <v>46238</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4855,29 +4855,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4886,13 +4886,17 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4904,29 +4908,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46234.425</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4936,16 +4940,16 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" s="1" t="n">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -4957,29 +4961,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46245.31875</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46363.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4988,17 +4992,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
         <v>46255.10416666666</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>46255.5</v>
+        <v>46256.25</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -7473,7 +7473,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8476,29 +8476,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>ANDROKLIS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9961441</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F156" s="1" t="n">
-        <v>46266.75</v>
+        <v>46266.54166666666</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>46267.33333333334</v>
+        <v>46267.58333333334</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -8512,12 +8512,12 @@
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8529,29 +8529,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ANDROKLIS</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9961441</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46266.58333333334</v>
+        <v>46268.25</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>46267.58333333334</v>
+        <v>46270.25</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8635,29 +8635,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46268.25</v>
+        <v>46266.75</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46270.25</v>
+        <v>46267.33333333334</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8671,12 +8671,12 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8737,29 +8737,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46275.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46277.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8786,29 +8786,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46260.25</v>
+        <v>46275.25</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46262.25</v>
+        <v>46277.25</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8823,7 +8823,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8884,29 +8884,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46269.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>46271.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9194,26 +9194,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G170" s="1" t="n">
         <v>46339.2625</v>
@@ -9231,7 +9231,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9318,36 +9318,36 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MSC999</t>
+          <t>COS999</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>MSC999</t>
+          <t>COS999</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46367.99930555555</v>
+        <v>46387.99861111111</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46383.99930555555</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46023.25</v>
+        <v>46254.66666666666</v>
       </c>
       <c r="I172" s="1" t="n">
-        <v>46023.25</v>
+        <v>46254.66666666666</v>
       </c>
       <c r="J172" s="1" t="n">
-        <v>46023.25</v>
+        <v>46254.66666666666</v>
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" s="1" t="n">
-        <v>46174.75</v>
+        <v>46254.99930555555</v>
       </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" s="1" t="n">
-        <v>46174.75</v>
+        <v>46254.99930555555</v>
       </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
@@ -9355,7 +9355,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9377,36 +9377,36 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>HMM999</t>
+          <t>MSC999</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>HMM999</t>
+          <t>MSC999</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46387.99861111111</v>
+        <v>46367.99930555555</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46383.99930555555</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>46240.95833333334</v>
+        <v>46023.25</v>
       </c>
       <c r="I173" s="1" t="n">
-        <v>46240.95833333334</v>
+        <v>46023.25</v>
       </c>
       <c r="J173" s="1" t="n">
-        <v>46240.95833333334</v>
+        <v>46023.25</v>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" s="1" t="n">
-        <v>46068.75</v>
+        <v>46174.75</v>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" s="1" t="n">
-        <v>46068.75</v>
+        <v>46174.75</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EMC999</t>
+          <t>HMM999</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>EMC999</t>
+          <t>HMM999</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
@@ -9451,21 +9451,21 @@
         <v>46387.99930555555</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46206.23958333334</v>
+        <v>46240.95833333334</v>
       </c>
       <c r="I174" s="1" t="n">
-        <v>46206.23958333334</v>
+        <v>46240.95833333334</v>
       </c>
       <c r="J174" s="1" t="n">
-        <v>46206.23958333334</v>
+        <v>46240.95833333334</v>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" s="1" t="n">
-        <v>46036.75</v>
+        <v>46068.75</v>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" s="1" t="n">
-        <v>46036.75</v>
+        <v>46068.75</v>
       </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9495,12 +9495,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>COS999</t>
+          <t>EMC999</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>COS999</t>
+          <t>EMC999</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
@@ -9510,21 +9510,21 @@
         <v>46387.99930555555</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>46202.23958333334</v>
+        <v>46206.23958333334</v>
       </c>
       <c r="I175" s="1" t="n">
-        <v>46202.23958333334</v>
+        <v>46206.23958333334</v>
       </c>
       <c r="J175" s="1" t="n">
-        <v>46202.23958333334</v>
+        <v>46206.23958333334</v>
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" s="1" t="n">
-        <v>46036.25</v>
+        <v>46036.75</v>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" s="1" t="n">
-        <v>46036.25</v>
+        <v>46036.75</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
@@ -9532,7 +9532,7 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9563,17 +9563,17 @@
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46204.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" s="1" t="n">
@@ -9589,7 +9589,7 @@
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9620,17 +9620,17 @@
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46096.125</v>
+        <v>46204.25</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" s="1" t="n">
@@ -9646,7 +9646,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9817,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
         <v>46265.25</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>46266.25</v>
+        <v>46266.58333333334</v>
       </c>
       <c r="H183" s="1" t="n">
         <v>46259.91666666666</v>
@@ -9993,12 +9993,12 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G190" s="1" t="n">
         <v>46263.58333333334</v>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10508,139 +10508,139 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TAMPA I</t>
+          <t>COLOMBO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>9196840</t>
+          <t>9256212</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>159S</t>
+          <t>084S</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>159N</t>
+          <t>084N</t>
         </is>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46260.6875</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="G192" s="1" t="n">
-        <v>46262.58333333334</v>
+        <v>46261.95833333334</v>
       </c>
       <c r="H192" s="1" t="n">
         <v>46255.25</v>
       </c>
-      <c r="I192" s="1" t="n">
-        <v>46258.25</v>
-      </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" s="1" t="n">
+        <v>46255.25</v>
+      </c>
       <c r="K192" s="1" t="n">
-        <v>46260.25</v>
+        <v>46259.91666666666</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>46260.25</v>
-      </c>
-      <c r="M192" s="1" t="n">
-        <v>46260.25</v>
-      </c>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="P192" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="Q192" s="1" t="n">
-        <v>46266</v>
-      </c>
+        <v>46259.91666666666</v>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" s="1" t="n">
+        <v>46259.91666666666</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH1</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>COLOMBO</t>
+          <t>TAMPA I</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9256212</t>
+          <t>9196840</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>084S</t>
+          <t>159S</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>084N</t>
+          <t>159N</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46260.6875</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>46261.95833333334</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46255.25</v>
-      </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" s="1" t="n">
-        <v>46255.25</v>
-      </c>
+        <v>46254.91666666666</v>
+      </c>
+      <c r="I193" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
       <c r="L193" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" s="1" t="n">
+      <c r="M193" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="P193" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="Q193" s="1" t="n">
+        <v>46266</v>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10772,139 +10772,139 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GREEN WAVE</t>
+          <t>OOCL PANAMA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>9867724</t>
+          <t>9355769</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>335S</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>335N</t>
         </is>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46259.625</v>
       </c>
       <c r="G196" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46260.625</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46253.91666666666</v>
-      </c>
-      <c r="I196" s="1" t="n">
-        <v>46256.91666666666</v>
-      </c>
-      <c r="J196" t="inlineStr"/>
+        <v>46254.25</v>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" s="1" t="n">
+        <v>46254.25</v>
+      </c>
       <c r="K196" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L196" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M196" s="1" t="n">
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" s="1" t="n">
-        <v>46260.58333333334</v>
-      </c>
-      <c r="P196" s="1" t="n">
-        <v>46260.58333333334</v>
-      </c>
-      <c r="Q196" s="1" t="n">
-        <v>46264</v>
-      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>OOCL PANAMA</t>
+          <t>GREEN WAVE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>9355769</t>
+          <t>9867724</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>335S</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>335N</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46259.625</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>46260.625</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46254.25</v>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" s="1" t="n">
-        <v>46254.25</v>
-      </c>
+        <v>46253.91666666666</v>
+      </c>
+      <c r="I197" s="1" t="n">
+        <v>46256.91666666666</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L197" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" s="1" t="n">
+      <c r="M197" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="1" t="n">
+        <v>46260.58333333334</v>
+      </c>
+      <c r="P197" s="1" t="n">
+        <v>46260.58333333334</v>
+      </c>
+      <c r="Q197" s="1" t="n">
+        <v>46264</v>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46258.95833333334</v>
+        <v>46259.5</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>46261.25</v>
+        <v>46261.5</v>
       </c>
       <c r="H198" s="1" t="n">
         <v>46254.23958333334</v>
@@ -10973,7 +10973,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11019,16 +11019,16 @@
         <v>46253.23958333334</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="N199" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="O199" s="1" t="n">
         <v>46259.00069444445</v>
@@ -11042,7 +11042,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11111,76 +11111,76 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>COSCO HONG KONG</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9227778</t>
+          <t>9363376</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>208S</t>
+          <t>044S</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>208N</t>
+          <t>044N</t>
         </is>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46258.91666666666</v>
+        <v>46257.75</v>
       </c>
       <c r="G201" s="1" t="n">
-        <v>46260.58333333334</v>
+        <v>46258.75</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46252.56944444445</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="I201" s="1" t="n">
-        <v>46254.58333333334</v>
-      </c>
-      <c r="J201" t="inlineStr"/>
+        <v>46252.23958333334</v>
+      </c>
+      <c r="J201" s="1" t="n">
+        <v>46252.23958333334</v>
+      </c>
       <c r="K201" s="1" t="n">
+        <v>46256.75</v>
+      </c>
+      <c r="L201" s="1" t="n">
+        <v>46256.75</v>
+      </c>
+      <c r="M201" s="1" t="n">
+        <v>46256.75</v>
+      </c>
+      <c r="N201" s="1" t="n">
         <v>46256.58333333334</v>
       </c>
-      <c r="L201" s="1" t="n">
-        <v>46256.58333333334</v>
-      </c>
-      <c r="M201" s="1" t="n">
-        <v>46256.58333333334</v>
-      </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" s="1" t="n">
-        <v>46260.25</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="P201" s="1" t="n">
-        <v>46260.25</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="Q201" s="1" t="n">
-        <v>46263</v>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46260.00069444445</v>
+      </c>
+      <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11192,64 +11192,64 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>MSC JESSENIA R</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>9363376</t>
+          <t>9215672</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>044S</t>
+          <t>KH634A</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>044N</t>
+          <t>KH634A</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46256.91666666666</v>
+        <v>46257.75</v>
       </c>
       <c r="G202" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46259.75</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="I202" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="J202" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>46256.5</v>
+        <v>46256.75</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>46256.5</v>
+        <v>46256.75</v>
       </c>
       <c r="M202" s="1" t="n">
-        <v>46256.5</v>
+        <v>46256.75</v>
       </c>
       <c r="N202" s="1" t="n">
-        <v>46256.58333333334</v>
+        <v>46258.45833333334</v>
       </c>
       <c r="O202" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="P202" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="Q202" s="1" t="n">
-        <v>46260.00069444445</v>
+        <v>46261.00069444445</v>
       </c>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11261,55 +11261,55 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>UBENA</t>
+          <t>COSCO HONG KONG</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9690078</t>
+          <t>9227778</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>208S</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>208N</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46258.91666666666</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>46258.58333333334</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46252.25</v>
+        <v>46252.56944444445</v>
       </c>
       <c r="I203" s="1" t="n">
-        <v>46254.25</v>
+        <v>46254.58333333334</v>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" s="1" t="n">
-        <v>46256.25</v>
+        <v>46256.58333333334</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>46256.25</v>
+        <v>46256.58333333334</v>
       </c>
       <c r="M203" s="1" t="n">
-        <v>46256.25</v>
+        <v>46256.58333333334</v>
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" s="1" t="n">
-        <v>46258.25</v>
+        <v>46260.25</v>
       </c>
       <c r="P203" s="1" t="n">
-        <v>46258.25</v>
+        <v>46260.25</v>
       </c>
       <c r="Q203" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11330,52 +11330,52 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MAERSK RIO DELTA</t>
+          <t>UBENA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>9357951</t>
+          <t>9690078</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>632N</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46256.58333333334</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="G204" s="1" t="n">
-        <v>46257.58333333334</v>
+        <v>46258.58333333334</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46252.25</v>
       </c>
       <c r="I204" s="1" t="n">
-        <v>46253.91666666666</v>
+        <v>46254.25</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46256.25</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46256.25</v>
       </c>
       <c r="M204" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46256.25</v>
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46258.25</v>
       </c>
       <c r="P204" s="1" t="n">
-        <v>46257.91666666666</v>
+        <v>46258.25</v>
       </c>
       <c r="Q204" s="1" t="n">
         <v>46261</v>
@@ -11387,76 +11387,76 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MSC JESSENIA R</t>
+          <t>MAERSK RIO DELTA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>9215672</t>
+          <t>9357951</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>KH634A</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KH634A</t>
+          <t>632N</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46257.25</v>
+        <v>46256.58333333334</v>
       </c>
       <c r="G205" s="1" t="n">
-        <v>46258.75</v>
+        <v>46257.58333333334</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46251.23958333334</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="I205" s="1" t="n">
-        <v>46251.23958333334</v>
-      </c>
-      <c r="J205" s="1" t="n">
-        <v>46251.23958333334</v>
-      </c>
+        <v>46253.91666666666</v>
+      </c>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" s="1" t="n">
-        <v>46255.75</v>
+        <v>46255.91666666666</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>46255.75</v>
+        <v>46255.91666666666</v>
       </c>
       <c r="M205" s="1" t="n">
-        <v>46255.75</v>
-      </c>
-      <c r="N205" s="1" t="n">
-        <v>46258.45833333334</v>
-      </c>
+        <v>46255.91666666666</v>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" s="1" t="n">
-        <v>46258.00069444445</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="P205" s="1" t="n">
-        <v>46258.00069444445</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="Q205" s="1" t="n">
-        <v>46261.00069444445</v>
-      </c>
-      <c r="R205" t="inlineStr"/>
+        <v>46261</v>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46256.27083333334</v>
+        <v>46256.20833333334</v>
       </c>
       <c r="G208" s="1" t="n">
         <v>46257.25</v>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="F209" s="1" t="n">
-        <v>46255.25</v>
+        <v>46256.25</v>
       </c>
       <c r="G209" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46257.75</v>
       </c>
       <c r="H209" s="1" t="n">
         <v>46250.23958333334</v>
@@ -11708,7 +11708,7 @@
         <v>46254.75</v>
       </c>
       <c r="N209" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46256.25</v>
       </c>
       <c r="O209" s="1" t="n">
         <v>46256.00069444445</v>
@@ -11722,7 +11722,7 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11803,29 +11803,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>HANSA FREYBURG</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9256389</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051W</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051E</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
         <v>46256.25</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>46257.25</v>
+        <v>46256.95833333334</v>
       </c>
       <c r="H211" s="1" t="n">
         <v>46249.23958333334</v>
@@ -11849,18 +11849,18 @@
         <v>46253.75</v>
       </c>
       <c r="O211" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="P211" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46256.00069444445</v>
       </c>
       <c r="Q211" s="1" t="n">
-        <v>46260.00069444445</v>
+        <v>46259.00069444445</v>
       </c>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11872,29 +11872,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HANSA FREYBURG</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>9256389</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>051W</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>051E</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
-        <v>46255.5</v>
+        <v>46256.95833333334</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>46256.25</v>
+        <v>46257.75</v>
       </c>
       <c r="H212" s="1" t="n">
         <v>46249.23958333334</v>
@@ -11915,21 +11915,21 @@
         <v>46253.75</v>
       </c>
       <c r="N212" s="1" t="n">
-        <v>46253.75</v>
+        <v>46256.66666666666</v>
       </c>
       <c r="O212" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="P212" s="1" t="n">
-        <v>46256.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="Q212" s="1" t="n">
-        <v>46259.00069444445</v>
+        <v>46260.00069444445</v>
       </c>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="F213" s="1" t="n">
-        <v>46254.58333333334</v>
+        <v>46254.60277777778</v>
       </c>
       <c r="G213" s="1" t="n">
         <v>46256.625</v>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12016,29 +12016,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F214" s="1" t="n">
-        <v>46280.25</v>
+        <v>46253.12708333333</v>
       </c>
       <c r="G214" s="1" t="n">
-        <v>46281.58333333334</v>
+        <v>46254.26458333333</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46246.91666666666</v>
+        <v>46247.25</v>
       </c>
       <c r="I214" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" s="1" t="n">
-        <v>46251.93055555555</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="L214" s="1" t="n">
         <v>46251.91666666666</v>
@@ -12047,17 +12047,23 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
+      <c r="O214" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="P214" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="Q214" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12079,29 +12085,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F215" s="1" t="n">
-        <v>46253.12708333333</v>
+        <v>46280.25</v>
       </c>
       <c r="G215" s="1" t="n">
-        <v>46254.26458333333</v>
+        <v>46281.58333333334</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>46247.25</v>
+        <v>46246.91666666666</v>
       </c>
       <c r="I215" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46251.93055555555</v>
       </c>
       <c r="L215" s="1" t="n">
         <v>46251.91666666666</v>
@@ -12110,23 +12116,17 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="P215" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="Q215" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12387,10 +12387,10 @@
         <v>46254.04166666666</v>
       </c>
       <c r="O219" s="1" t="n">
-        <v>46254.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="P219" s="1" t="n">
-        <v>46254.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="Q219" s="1" t="n">
         <v>46258.00069444445</v>
@@ -12398,7 +12398,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
         <v>46251.69930555556</v>
       </c>
       <c r="G221" s="1" t="n">
-        <v>46254.99930555555</v>
+        <v>46255.0625</v>
       </c>
       <c r="H221" s="1" t="n">
         <v>46245.23958333334</v>
@@ -12536,7 +12536,7 @@
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="F225" s="1" t="n">
-        <v>46251.91180555556</v>
+        <v>46251.92916666667</v>
       </c>
       <c r="G225" s="1" t="n">
         <v>46254.125</v>
@@ -12804,7 +12804,7 @@
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13551,7 +13551,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13882,7 +13882,7 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14767,7 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14974,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15043,7 +15043,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16537,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16606,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16878,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16947,7 @@
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18925,7 +18925,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18990,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19116,7 +19116,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19248,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19319,7 +19319,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19591,7 +19591,7 @@
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20356,7 +20356,7 @@
       <c r="R337" t="inlineStr"/>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20555,7 +20555,7 @@
       <c r="R340" t="inlineStr"/>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       <c r="R341" t="inlineStr"/>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20673,7 @@
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       <c r="R344" t="inlineStr"/>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-20 13:34:35</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -3792,7 +3792,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -3804,29 +3804,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3835,13 +3835,17 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="O56" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -3853,29 +3857,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3885,16 +3889,16 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -3906,29 +3910,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46240.33125</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3937,17 +3941,13 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -3959,29 +3959,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46288.25</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3990,13 +3990,17 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="O59" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4008,29 +4012,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -4040,16 +4044,16 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" s="1" t="n">
-        <v>46250</v>
+        <v>46248</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>46250</v>
+        <v>46248</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4061,29 +4065,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -4092,13 +4096,17 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4110,29 +4118,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4141,13 +4149,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4159,29 +4171,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4190,17 +4202,13 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4212,29 +4220,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46242.26875</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4244,16 +4252,16 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4265,26 +4273,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46245.29375</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>46363.2625</v>
@@ -4302,7 +4310,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4314,29 +4322,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46253.44375</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46288.25</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4345,17 +4353,13 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>46258</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4408,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4416,29 +4420,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46243.01875</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46281.25</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4447,13 +4451,17 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="O68" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P68" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4465,29 +4473,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46286.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4496,17 +4504,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4518,29 +4522,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46237.34375</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46286.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4549,17 +4553,13 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P70" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4571,29 +4571,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4603,16 +4603,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4624,29 +4624,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4655,13 +4655,17 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="O72" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4673,29 +4677,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4704,13 +4708,17 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4722,29 +4730,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46339.2625</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4754,16 +4762,16 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" s="1" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4775,29 +4783,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4806,13 +4814,17 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="O75" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>46253</v>
+      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4824,29 +4836,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46242.5125</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46243.0625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4856,16 +4868,16 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4877,29 +4889,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4909,16 +4921,16 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4930,29 +4942,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46281.25</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4961,17 +4973,13 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="P78" s="1" t="n">
-        <v>46253</v>
-      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -4983,29 +4991,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46245.31875</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46363.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5014,17 +5022,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P79" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5036,29 +5040,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5067,17 +5071,13 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P80" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
         <v>46255.22638888889</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>46256.375</v>
+        <v>46256.41666666666</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -7581,7 +7581,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8539,29 +8539,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46257.25</v>
+        <v>46266.75</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>46257.72916666666</v>
+        <v>46267.33333333334</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8592,29 +8592,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAERSK BUTON</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>9392925</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>636N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F156" s="1" t="n">
-        <v>46269.58333333334</v>
+        <v>46257.25</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>46270.91666666666</v>
+        <v>46257.72916666666</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -8628,12 +8628,12 @@
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8645,30 +8645,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>MAERSK RIO ALFA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9348106</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46266.75</v>
-      </c>
-      <c r="G157" s="1" t="n">
-        <v>46267.33333333334</v>
-      </c>
+        <v>46263.91666666666</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
@@ -8679,14 +8677,10 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8698,28 +8692,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MAERSK RIO ALFA</t>
+          <t>MAERSK BUTON</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>9348106</t>
+          <t>9392925</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>636N</t>
         </is>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46263.91666666666</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
+        <v>46269.58333333334</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>46270.91666666666</v>
+      </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
@@ -8730,10 +8726,14 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8745,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46266.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46268.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8794,29 +8794,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46269.25</v>
+        <v>46275.25</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46271.25</v>
+        <v>46277.25</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46260.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46262.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8880,7 +8880,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8892,29 +8892,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46269.25</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46271.25</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -8941,29 +8941,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46275.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46277.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -8978,7 +8978,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9080,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9251,29 +9251,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -9282,17 +9282,13 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="P169" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9304,29 +9300,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46235.60625</v>
       </c>
       <c r="G170" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -9335,13 +9331,17 @@
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="O170" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P170" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9353,29 +9353,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
@@ -9384,13 +9384,17 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
+      <c r="O171" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P171" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9402,29 +9406,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -9434,16 +9438,16 @@
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" s="1" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9455,29 +9459,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -9486,17 +9490,13 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
-      <c r="O173" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P173" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9508,29 +9508,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -9540,16 +9540,16 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" s="1" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="P174" s="1" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9919,12 +9919,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9938,17 +9938,17 @@
         </is>
       </c>
       <c r="F181" s="1" t="n">
-        <v>46096.125</v>
+        <v>46204.25</v>
       </c>
       <c r="G181" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" s="1" t="n">
-        <v>46209</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" s="1" t="n">
@@ -9964,7 +9964,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9995,17 +9995,17 @@
         </is>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46356.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G182" s="1" t="n">
         <v>46387.25</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46268</v>
+        <v>46209</v>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" s="1" t="n">
-        <v>46268</v>
+        <v>46209</v>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" s="1" t="n">
@@ -10021,7 +10021,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10052,17 +10052,17 @@
         </is>
       </c>
       <c r="F183" s="1" t="n">
-        <v>46204.25</v>
+        <v>46356.25</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46268</v>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46268</v>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" s="1" t="n">
@@ -10078,7 +10078,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10763,29 +10763,29 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OLIVIA MAERSK</t>
+          <t>ALS KRONOS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>9251638</t>
+          <t>9327786</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -10794,67 +10794,61 @@
         </is>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46262.6875</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="G195" s="1" t="n">
-        <v>46263.91666666666</v>
+        <v>46264.58333333334</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46257.91666666666</v>
-      </c>
-      <c r="I195" s="1" t="n">
-        <v>46259.91666666666</v>
-      </c>
-      <c r="J195" t="inlineStr"/>
+        <v>46257.58333333334</v>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" s="1" t="n">
+        <v>46257.58333333334</v>
+      </c>
       <c r="K195" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L195" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M195" s="1" t="n">
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="P195" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="Q195" s="1" t="n">
-        <v>46268</v>
-      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ALS KRONOS</t>
+          <t>OLIVIA MAERSK</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>9327786</t>
+          <t>9251638</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10863,39 +10857,45 @@
         </is>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46262.91666666666</v>
+        <v>46262.6875</v>
       </c>
       <c r="G196" s="1" t="n">
-        <v>46264.58333333334</v>
+        <v>46263.91666666666</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
+        <v>46257.91666666666</v>
+      </c>
+      <c r="I196" s="1" t="n">
+        <v>46259.91666666666</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L196" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" s="1" t="n">
+      <c r="M196" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="P196" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="Q196" s="1" t="n">
+        <v>46268</v>
+      </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10907,29 +10907,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MSC CAPETOWN III</t>
+          <t>MSC UNITY VI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>9311737</t>
+          <t>9169158</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>FP628A</t>
+          <t>KQ630A</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FP632R</t>
+          <t>KQ635R</t>
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46261.91666666666</v>
+        <v>46262.75</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>46262.91666666666</v>
+        <v>46264.75</v>
       </c>
       <c r="H197" s="1" t="n">
         <v>46257.23958333334</v>
@@ -10958,7 +10958,7 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -10970,29 +10970,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MSC UNITY VI</t>
+          <t>MSC CAPETOWN III</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>9169158</t>
+          <t>9311737</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>KQ630A</t>
+          <t>FP628A</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KQ635R</t>
+          <t>FP632R</t>
         </is>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46262.75</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>46264.75</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="H198" s="1" t="n">
         <v>46257.23958333334</v>
@@ -11021,7 +11021,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11486,139 +11486,139 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OOCL PANAMA</t>
+          <t>GREEN WAVE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>9355769</t>
+          <t>9867724</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>335S</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>335N</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46259.625</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="G206" s="1" t="n">
-        <v>46260.625</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46254.25</v>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" s="1" t="n">
-        <v>46254.25</v>
-      </c>
+        <v>46253.91666666666</v>
+      </c>
+      <c r="I206" s="1" t="n">
+        <v>46256.91666666666</v>
+      </c>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L206" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" s="1" t="n">
-        <v>46258.95833333334</v>
-      </c>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
+      <c r="M206" s="1" t="n">
+        <v>46258.91666666666</v>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" s="1" t="n">
+        <v>46260.58333333334</v>
+      </c>
+      <c r="P206" s="1" t="n">
+        <v>46260.58333333334</v>
+      </c>
+      <c r="Q206" s="1" t="n">
+        <v>46264</v>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GREEN WAVE</t>
+          <t>OOCL PANAMA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>9867724</t>
+          <t>9355769</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>335S</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>335N</t>
         </is>
       </c>
       <c r="F207" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46259.625</v>
       </c>
       <c r="G207" s="1" t="n">
-        <v>46260.91666666666</v>
+        <v>46260.625</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46253.91666666666</v>
-      </c>
-      <c r="I207" s="1" t="n">
-        <v>46256.91666666666</v>
-      </c>
-      <c r="J207" t="inlineStr"/>
+        <v>46254.25</v>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" s="1" t="n">
+        <v>46254.25</v>
+      </c>
       <c r="K207" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
       <c r="L207" s="1" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="M207" s="1" t="n">
-        <v>46258.91666666666</v>
-      </c>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" s="1" t="n">
-        <v>46260.58333333334</v>
-      </c>
-      <c r="P207" s="1" t="n">
-        <v>46260.58333333334</v>
-      </c>
-      <c r="Q207" s="1" t="n">
-        <v>46264</v>
-      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" s="1" t="n">
+        <v>46258.95833333334</v>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11837,38 +11837,38 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MSC JESSENIA R</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>9215672</t>
+          <t>9363376</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>KH634A</t>
+          <t>044S</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>KH634A</t>
+          <t>044N</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
         <v>46257.75</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>46259.75</v>
+        <v>46258.75</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="I211" s="1" t="n">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="J211" s="1" t="n">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="K211" s="1" t="n">
         <v>46256.75</v>
@@ -11880,7 +11880,7 @@
         <v>46256.75</v>
       </c>
       <c r="N211" s="1" t="n">
-        <v>46259.25</v>
+        <v>46256.58333333334</v>
       </c>
       <c r="O211" s="1" t="n">
         <v>46258.00069444445</v>
@@ -11894,7 +11894,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -11906,38 +11906,38 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>MSC JESSENIA R</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>9363376</t>
+          <t>9215672</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>044S</t>
+          <t>KH634A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>044N</t>
+          <t>KH634A</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
         <v>46257.75</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>46258.75</v>
+        <v>46259.75</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="I212" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="J212" s="1" t="n">
-        <v>46252.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="K212" s="1" t="n">
         <v>46256.75</v>
@@ -11949,7 +11949,7 @@
         <v>46256.75</v>
       </c>
       <c r="N212" s="1" t="n">
-        <v>46256.58333333334</v>
+        <v>46259.25</v>
       </c>
       <c r="O212" s="1" t="n">
         <v>46258.00069444445</v>
@@ -11963,7 +11963,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12294,29 +12294,29 @@
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CMA CGM SAMSON</t>
+          <t>OLGA MAERSK</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>9436379</t>
+          <t>9251614</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>629S</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12325,18 +12325,18 @@
         </is>
       </c>
       <c r="F218" s="1" t="n">
-        <v>46252.45</v>
+        <v>46256.20833333334</v>
       </c>
       <c r="G218" s="1" t="n">
-        <v>46259.625</v>
+        <v>46257.25</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>46250.25</v>
-      </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" s="1" t="n">
-        <v>46250.25</v>
-      </c>
+        <v>46250.91666666666</v>
+      </c>
+      <c r="I218" s="1" t="n">
+        <v>46252.91666666666</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" s="1" t="n">
         <v>46254.91666666666</v>
       </c>
@@ -12344,44 +12344,48 @@
         <v>46254.91666666666</v>
       </c>
       <c r="M218" s="1" t="n">
-        <v>46256.54166666666</v>
-      </c>
-      <c r="N218" s="1" t="n">
-        <v>46258.04166666666</v>
-      </c>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
+        <v>46254.91666666666</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="P218" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="Q218" s="1" t="n">
+        <v>46261</v>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>OLGA MAERSK</t>
+          <t>CMA CGM SAMSON</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>9251614</t>
+          <t>9436379</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>629S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12390,18 +12394,18 @@
         </is>
       </c>
       <c r="F219" s="1" t="n">
-        <v>46256.20833333334</v>
+        <v>46256.15694444445</v>
       </c>
       <c r="G219" s="1" t="n">
-        <v>46257.25</v>
+        <v>46259.625</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>46250.91666666666</v>
-      </c>
-      <c r="I219" s="1" t="n">
-        <v>46252.91666666666</v>
-      </c>
-      <c r="J219" t="inlineStr"/>
+        <v>46250.25</v>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" s="1" t="n">
+        <v>46250.25</v>
+      </c>
       <c r="K219" s="1" t="n">
         <v>46254.91666666666</v>
       </c>
@@ -12409,26 +12413,22 @@
         <v>46254.91666666666</v>
       </c>
       <c r="M219" s="1" t="n">
-        <v>46254.91666666666</v>
-      </c>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="P219" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="Q219" s="1" t="n">
-        <v>46261</v>
-      </c>
+        <v>46256.54166666666</v>
+      </c>
+      <c r="N219" s="1" t="n">
+        <v>46258.04166666666</v>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
         </is>
       </c>
       <c r="F220" s="1" t="n">
-        <v>46256.3125</v>
+        <v>46256.36458333334</v>
       </c>
       <c r="G220" s="1" t="n">
         <v>46257.75</v>
@@ -12497,7 +12497,7 @@
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="F223" s="1" t="n">
-        <v>46256.25</v>
+        <v>46256.5</v>
       </c>
       <c r="G223" s="1" t="n">
         <v>46256.95833333334</v>
@@ -12704,7 +12704,7 @@
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12791,29 +12791,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F225" s="1" t="n">
-        <v>46280.25</v>
+        <v>46253.12708333333</v>
       </c>
       <c r="G225" s="1" t="n">
-        <v>46281.58333333334</v>
+        <v>46254.26458333333</v>
       </c>
       <c r="H225" s="1" t="n">
-        <v>46246.91666666666</v>
+        <v>46247.25</v>
       </c>
       <c r="I225" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" s="1" t="n">
-        <v>46251.93055555555</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="L225" s="1" t="n">
         <v>46251.91666666666</v>
@@ -12822,17 +12822,23 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
+      <c r="O225" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="P225" s="1" t="n">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="Q225" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12854,29 +12860,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F226" s="1" t="n">
-        <v>46253.12708333333</v>
+        <v>46280.25</v>
       </c>
       <c r="G226" s="1" t="n">
-        <v>46254.26458333333</v>
+        <v>46281.58333333334</v>
       </c>
       <c r="H226" s="1" t="n">
-        <v>46247.25</v>
+        <v>46246.91666666666</v>
       </c>
       <c r="I226" s="1" t="n">
         <v>46249.91666666666</v>
       </c>
       <c r="J226" t="inlineStr"/>
       <c r="K226" s="1" t="n">
-        <v>46251.91666666666</v>
+        <v>46251.93055555555</v>
       </c>
       <c r="L226" s="1" t="n">
         <v>46251.91666666666</v>
@@ -12885,23 +12891,17 @@
         <v>46251.91666666666</v>
       </c>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="P226" s="1" t="n">
-        <v>46253.58333333334</v>
-      </c>
-      <c r="Q226" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
         <v>46254.22083333333</v>
       </c>
       <c r="G230" s="1" t="n">
-        <v>46256.20833333334</v>
+        <v>46256.26041666666</v>
       </c>
       <c r="H230" s="1" t="n">
         <v>46246.23958333334</v>
@@ -13173,7 +13173,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
         <v>46251.41666666666</v>
       </c>
       <c r="G234" s="1" t="n">
-        <v>46255.95833333334</v>
+        <v>46255.96944444445</v>
       </c>
       <c r="H234" s="1" t="n">
         <v>46245.58333333334</v>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14123,7 @@
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14326,7 @@
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14736,7 +14736,7 @@
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15414,7 +15414,7 @@
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -16985,7 +16985,7 @@
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17123,7 +17123,7 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17192,7 @@
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17537,7 +17537,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
       <c r="R303" t="inlineStr"/>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18331,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18461,7 +18461,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18719,7 +18719,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19495,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19704,7 +19704,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19905,7 +19905,7 @@
       <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20670,7 +20670,7 @@
       <c r="R341" t="inlineStr"/>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20869,7 +20869,7 @@
       <c r="R344" t="inlineStr"/>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20928,7 @@
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -21046,7 +21046,7 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -21105,7 +21105,7 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21164,7 @@
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -21223,7 +21223,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-22 01:00:05</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -3816,29 +3816,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46242.5125</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46243.0625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3848,16 +3848,16 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" s="1" t="n">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -3869,26 +3869,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46339.2625</v>
@@ -3906,7 +3906,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -3918,29 +3918,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46245.31875</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46363.2625</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3949,17 +3949,13 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>46253</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -3971,29 +3967,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46286.2625</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -4002,17 +3998,13 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4053,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4073,29 +4065,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -4104,13 +4096,17 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4122,29 +4118,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46240.33125</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4159,7 +4155,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4171,29 +4167,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4203,16 +4199,16 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" s="1" t="n">
-        <v>46243</v>
+        <v>46258</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46243</v>
+        <v>46258</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4224,29 +4220,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46339.2625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4255,17 +4251,13 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4310,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4330,29 +4322,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46339.2625</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4361,17 +4353,13 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4383,29 +4371,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4414,13 +4402,17 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="O67" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>46253</v>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4432,29 +4424,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46243.01875</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4464,16 +4456,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4485,29 +4477,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46237.34375</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4516,17 +4508,13 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P69" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4538,29 +4526,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46245.29375</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4569,17 +4557,13 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P70" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4591,29 +4575,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4623,16 +4607,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4644,29 +4628,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4676,16 +4660,16 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" s="1" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4697,29 +4681,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4728,13 +4712,17 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4746,29 +4734,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46253.44375</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46288.25</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4777,17 +4765,13 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="P74" s="1" t="n">
-        <v>46258</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4799,29 +4783,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4830,13 +4814,17 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="O75" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4848,29 +4836,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46339.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4879,17 +4867,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46254</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4901,29 +4885,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4932,13 +4916,17 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="O77" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4950,29 +4938,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4981,13 +4969,17 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="O78" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -4999,29 +4991,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5030,13 +5022,17 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5048,29 +5044,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46288.25</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5079,13 +5075,17 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="O80" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5097,29 +5097,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46235.60625</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -5129,16 +5129,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5150,29 +5150,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -5182,16 +5182,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5600,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7307,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8653,29 +8653,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>MAERSK RIO ALFA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9348106</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46270.25</v>
+        <v>46264.02083333334</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>46272.25</v>
+        <v>46265.25</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8865,29 +8865,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MAERSK RIO ALFA</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9348106</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46264.02083333334</v>
+        <v>46270.25</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46265.25</v>
+        <v>46272.25</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8918,29 +8918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46266.25</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46268.25</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8955,7 +8955,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -8967,29 +8967,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46275.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46277.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -9004,7 +9004,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9016,29 +9016,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46269.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>46271.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
@@ -9053,7 +9053,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9065,29 +9065,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46260.25</v>
+        <v>46275.25</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>46262.25</v>
+        <v>46277.25</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46266.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46268.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -9151,7 +9151,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9424,29 +9424,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46363.2625</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -9455,17 +9455,13 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
-      <c r="O172" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P172" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9477,29 +9473,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -9509,16 +9505,16 @@
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" s="1" t="n">
-        <v>46243</v>
+        <v>46255</v>
       </c>
       <c r="P173" s="1" t="n">
-        <v>46243</v>
+        <v>46255</v>
       </c>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9530,29 +9526,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -9561,13 +9557,17 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
+      <c r="O174" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P174" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9579,29 +9579,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9611,16 +9611,16 @@
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="P175" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9632,29 +9632,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9664,16 +9664,16 @@
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="P176" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -9986,12 +9986,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10005,17 +10005,17 @@
         </is>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46386.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G182" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46104.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" s="1" t="n">
-        <v>46284.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" s="1" t="n">
@@ -10031,7 +10031,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10157,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10176,17 +10176,17 @@
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46204.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G185" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46104.25</v>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" s="1" t="n">
@@ -10202,7 +10202,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10578,35 +10578,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TS CHENNAI</t>
+          <t>KOTA LOCENG</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>9953846</t>
+          <t>9628336</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2604S</t>
+          <t>0171S</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2604N</t>
+          <t>0171N</t>
         </is>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46265.35416666666</v>
+        <v>46264.6875</v>
       </c>
       <c r="G192" s="1" t="n">
-        <v>46267.25</v>
+        <v>46266.25</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46259.25</v>
       </c>
       <c r="I192" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.25</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" s="1" t="n">
@@ -10624,12 +10624,12 @@
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10641,35 +10641,35 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>KOTA LOCENG</t>
+          <t>TS CHENNAI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9628336</t>
+          <t>9953846</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0171S</t>
+          <t>2604S</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0171N</t>
+          <t>2604N</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46264.6875</v>
+        <v>46268.25</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>46266.25</v>
+        <v>46270.14583333334</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>46259.25</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="I193" s="1" t="n">
-        <v>46261.25</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" s="1" t="n">
@@ -10687,12 +10687,12 @@
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11088,139 +11088,139 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>101S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>101N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F200" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G200" s="1" t="n">
-        <v>46263.29166666666</v>
+        <v>46263.58333333334</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46256.25</v>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" s="1" t="n">
-        <v>46256.25</v>
-      </c>
+        <v>46255.91666666666</v>
+      </c>
+      <c r="I200" s="1" t="n">
+        <v>46258.58333333334</v>
+      </c>
+      <c r="J200" t="inlineStr"/>
       <c r="K200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" s="1" t="n">
+      <c r="M200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="P200" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="Q200" s="1" t="n">
+        <v>46267</v>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>101S</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>101N</t>
         </is>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46261.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G201" s="1" t="n">
-        <v>46263.58333333334</v>
+        <v>46263.29166666666</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46255.91666666666</v>
-      </c>
-      <c r="I201" s="1" t="n">
-        <v>46258.58333333334</v>
-      </c>
-      <c r="J201" t="inlineStr"/>
+        <v>46256.25</v>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" s="1" t="n">
+        <v>46256.25</v>
+      </c>
       <c r="K201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M201" s="1" t="n">
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="P201" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="Q201" s="1" t="n">
-        <v>46267</v>
-      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46260.625</v>
       </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="F217" s="1" t="n">
-        <v>46256.58333333334</v>
+        <v>46256.62777777778</v>
       </c>
       <c r="G217" s="1" t="n">
         <v>46257.58333333334</v>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
         <v>46256.40625</v>
       </c>
       <c r="G222" s="1" t="n">
-        <v>46257.75</v>
+        <v>46257.91666666666</v>
       </c>
       <c r="H222" s="1" t="n">
         <v>46250.23958333334</v>
@@ -12633,7 +12633,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
         <v>46254.60277777778</v>
       </c>
       <c r="G226" s="1" t="n">
-        <v>46256.625</v>
+        <v>46257.25</v>
       </c>
       <c r="H226" s="1" t="n">
         <v>46248.25</v>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14462,7 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14872,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15481,7 +15481,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15619,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16845,7 +16845,7 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17328,7 @@
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17397,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       <c r="R295" t="inlineStr"/>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17742,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -17949,7 +17949,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18014,7 +18014,7 @@
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18203,7 +18203,7 @@
       <c r="R304" t="inlineStr"/>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18268,7 +18268,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18916,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19111,7 +19111,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19972,7 @@
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20185,7 +20185,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20877,7 +20877,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21054,7 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr">
         <is>
-          <t>2026-08-22 13:26:18</t>
+          <t>2026-08-22 17:59:21</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -3816,29 +3816,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3847,17 +3847,13 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -3869,26 +3865,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46339.2625</v>
@@ -3900,13 +3896,17 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="O57" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="P57" s="1" t="n">
+        <v>46258</v>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -3918,29 +3918,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3949,13 +3949,17 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="O58" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -3967,29 +3971,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3998,13 +4002,17 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="O59" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4016,29 +4024,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46237.34375</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46281.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -4053,7 +4061,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4065,29 +4073,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -4097,16 +4105,16 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" s="1" t="n">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4118,29 +4126,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4149,13 +4157,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4167,29 +4179,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4199,16 +4211,16 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" s="1" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4220,29 +4232,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4251,13 +4263,17 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4269,29 +4285,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46240.33125</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4300,17 +4316,13 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4322,29 +4334,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46253.44375</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46288.25</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4359,7 +4371,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4371,29 +4383,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4403,16 +4415,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46253</v>
+        <v>46241</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46253</v>
+        <v>46241</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4424,29 +4436,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46242.26875</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4456,16 +4468,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" s="1" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4477,29 +4489,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4508,13 +4520,17 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4526,29 +4542,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4563,7 +4579,7 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4575,29 +4591,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46245.29375</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46363.2625</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4606,17 +4622,13 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P71" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4628,29 +4640,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46281.25</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4659,17 +4671,13 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P72" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4681,29 +4689,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46243.01875</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4713,16 +4721,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" s="1" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4734,29 +4742,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46288.25</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4765,13 +4773,17 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="O74" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4783,29 +4795,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46339.2625</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4814,17 +4826,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4836,29 +4844,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4873,7 +4881,7 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4885,29 +4893,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46235.60625</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46242.43472222222</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4917,16 +4925,16 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4938,29 +4946,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4970,16 +4978,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -4991,29 +4999,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5023,16 +5031,16 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" s="1" t="n">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5052,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5076,16 +5084,16 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" s="1" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5097,29 +5105,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46242.5125</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46242.43472222222</v>
+        <v>46243.0625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -5129,16 +5137,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5150,29 +5158,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46286.2625</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -5182,16 +5190,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5245,7 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5293,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5338,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5383,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5428,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5473,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5518,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5563,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5608,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5653,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5698,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5743,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5788,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5833,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5878,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5923,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5968,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6013,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6058,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6103,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6148,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6193,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6238,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6283,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6328,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6373,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6418,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6463,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6508,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6553,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6598,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6651,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6704,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6751,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6798,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6845,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6892,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6939,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6986,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7033,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7080,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7127,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7174,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7221,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7268,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7315,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7362,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7409,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7456,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7503,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7548,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7597,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7648,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7703,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7752,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7797,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7846,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7901,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7946,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7991,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8036,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8085,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8130,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8171,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8220,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8269,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8314,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8363,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8412,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8457,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8502,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8547,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8604,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8649,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8653,29 +8661,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MAERSK RIO ALFA</t>
+          <t>MAERSK BUTON</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9348106</t>
+          <t>9392925</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>636N</t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46264.02083333334</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>46265.25</v>
+        <v>46270.91666666666</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -8689,12 +8697,12 @@
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8706,29 +8714,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46257.25</v>
+        <v>46270.25</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>46257.52083333334</v>
+        <v>46272.25</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -8742,12 +8750,12 @@
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8759,29 +8767,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MAERSK BUTON</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>9392925</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>636N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46269.58333333334</v>
+        <v>46257.25</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46270.91666666666</v>
+        <v>46257.52083333334</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8795,12 +8803,12 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8861,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8865,29 +8873,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>MAERSK RIO ALFA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9348106</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46270.25</v>
+        <v>46264.02083333334</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46272.25</v>
+        <v>46265.25</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8906,7 +8914,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8918,29 +8926,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46266.25</v>
+        <v>46275.25</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8955,7 +8963,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -8967,29 +8975,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46269.25</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46271.25</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -9004,7 +9012,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9061,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9065,29 +9073,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46275.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>46277.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
@@ -9102,7 +9110,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9114,29 +9122,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46269.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46271.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -9151,7 +9159,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9208,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9261,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9314,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9367,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9420,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9424,29 +9432,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -9455,13 +9463,17 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
+      <c r="O172" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P172" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9473,29 +9485,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46245.31875</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46363.2625</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -9504,17 +9516,13 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
-      <c r="O173" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P173" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9526,29 +9534,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -9558,16 +9566,16 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" s="1" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="P174" s="1" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9579,29 +9587,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9610,17 +9618,13 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
-      <c r="O175" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P175" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9632,29 +9636,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9663,17 +9667,13 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
-      <c r="O176" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P176" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -9986,12 +9986,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10005,17 +10005,17 @@
         </is>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46204.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G182" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46104.25</v>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" s="1" t="n">
@@ -10031,7 +10031,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10157,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10176,17 +10176,17 @@
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46386.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G185" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46104.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" s="1" t="n">
-        <v>46284.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" s="1" t="n">
@@ -10202,7 +10202,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -10887,29 +10887,29 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ALS KRONOS</t>
+          <t>OLIVIA MAERSK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>9327786</t>
+          <t>9251638</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10918,61 +10918,67 @@
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46262.91666666666</v>
+        <v>46262.6875</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>46264.58333333334</v>
+        <v>46263.91666666666</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
+        <v>46257.91666666666</v>
+      </c>
+      <c r="I197" s="1" t="n">
+        <v>46259.91666666666</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L197" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" s="1" t="n">
+      <c r="M197" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="P197" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="Q197" s="1" t="n">
+        <v>46268</v>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>OLIVIA MAERSK</t>
+          <t>ALS KRONOS</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>9251638</t>
+          <t>9327786</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10981,45 +10987,39 @@
         </is>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46262.6875</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>46263.91666666666</v>
+        <v>46264.58333333334</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46257.91666666666</v>
-      </c>
-      <c r="I198" s="1" t="n">
-        <v>46259.91666666666</v>
-      </c>
-      <c r="J198" t="inlineStr"/>
+        <v>46257.58333333334</v>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" s="1" t="n">
+        <v>46257.58333333334</v>
+      </c>
       <c r="K198" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L198" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M198" s="1" t="n">
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="P198" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="Q198" s="1" t="n">
-        <v>46268</v>
-      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11088,139 +11088,139 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>101S</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>101N</t>
         </is>
       </c>
       <c r="F200" s="1" t="n">
-        <v>46261.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G200" s="1" t="n">
-        <v>46263.58333333334</v>
+        <v>46263.29166666666</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46255.91666666666</v>
-      </c>
-      <c r="I200" s="1" t="n">
-        <v>46258.58333333334</v>
-      </c>
-      <c r="J200" t="inlineStr"/>
+        <v>46256.25</v>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" s="1" t="n">
+        <v>46256.25</v>
+      </c>
       <c r="K200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M200" s="1" t="n">
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="P200" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="Q200" s="1" t="n">
-        <v>46267</v>
-      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>101S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>101N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G201" s="1" t="n">
-        <v>46263.29166666666</v>
+        <v>46263.58333333334</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>46256.25</v>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" s="1" t="n">
-        <v>46256.25</v>
-      </c>
+        <v>46255.91666666666</v>
+      </c>
+      <c r="I201" s="1" t="n">
+        <v>46258.58333333334</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" s="1" t="n">
+      <c r="M201" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="P201" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="Q201" s="1" t="n">
+        <v>46267</v>
+      </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11289,139 +11289,139 @@
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>COLOMBO</t>
+          <t>TAMPA I</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9256212</t>
+          <t>9196840</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>084S</t>
+          <t>159S</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>084N</t>
+          <t>159N</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46260.58333333334</v>
+        <v>46260.6875</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>46261.625</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46255.25</v>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" s="1" t="n">
-        <v>46255.25</v>
-      </c>
+        <v>46254.91666666666</v>
+      </c>
+      <c r="I203" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
       <c r="L203" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="P203" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="Q203" s="1" t="n">
+        <v>46266</v>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TAMPA I</t>
+          <t>COLOMBO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>9196840</t>
+          <t>9256212</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>159S</t>
+          <t>084S</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>159N</t>
+          <t>084N</t>
         </is>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46260.6875</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="G204" s="1" t="n">
-        <v>46262.58333333334</v>
+        <v>46261.625</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46254.91666666666</v>
-      </c>
-      <c r="I204" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="J204" t="inlineStr"/>
+        <v>46255.25</v>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" s="1" t="n">
+        <v>46255.25</v>
+      </c>
       <c r="K204" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
       <c r="L204" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="M204" s="1" t="n">
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="P204" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="Q204" s="1" t="n">
-        <v>46266</v>
-      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH1</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12340,7 @@
         <v>46256.28680555556</v>
       </c>
       <c r="G218" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46256.82638888889</v>
       </c>
       <c r="H218" s="1" t="n">
         <v>46251.25</v>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
         </is>
       </c>
       <c r="F224" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46257.20486111111</v>
       </c>
       <c r="G224" s="1" t="n">
         <v>46257.75</v>
@@ -12771,7 +12771,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12805,7 @@
         <v>46256.5</v>
       </c>
       <c r="G225" s="1" t="n">
-        <v>46256.95833333334</v>
+        <v>46257.125</v>
       </c>
       <c r="H225" s="1" t="n">
         <v>46249.23958333334</v>
@@ -12840,7 +12840,7 @@
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14462,7 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14872,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15481,7 +15481,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15619,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16845,7 +16845,7 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17328,7 @@
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17397,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       <c r="R295" t="inlineStr"/>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17742,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -17949,7 +17949,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18014,7 +18014,7 @@
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18203,7 +18203,7 @@
       <c r="R304" t="inlineStr"/>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18268,7 +18268,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18916,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19111,7 +19111,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19972,7 @@
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20185,7 +20185,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20877,7 +20877,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21054,7 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr">
         <is>
-          <t>2026-08-22 17:59:21</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -3938,29 +3938,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46339.2625</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3969,17 +3969,13 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -3991,29 +3987,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46286.2625</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -4022,17 +4018,13 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4044,29 +4036,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -4075,13 +4067,17 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="O60" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4093,29 +4089,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -4125,16 +4121,16 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" s="1" t="n">
-        <v>46243</v>
+        <v>46255</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46243</v>
+        <v>46255</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4146,29 +4142,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4177,13 +4173,17 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4195,29 +4195,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46363.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4226,17 +4226,13 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4248,29 +4244,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4279,13 +4275,17 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4297,29 +4297,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4329,16 +4329,16 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" s="1" t="n">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4350,29 +4350,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4381,13 +4381,17 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="O66" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4399,26 +4403,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>46339.2625</v>
@@ -4436,7 +4440,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4448,29 +4452,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46243.01875</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4480,16 +4484,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" s="1" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4501,29 +4505,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4532,13 +4536,17 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>46248</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4550,29 +4558,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46339.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4581,17 +4589,13 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="P70" s="1" t="n">
-        <v>46254</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4603,29 +4607,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.31875</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4634,17 +4638,13 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P71" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4656,29 +4656,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46253.44375</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46288.25</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4693,7 +4693,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4705,29 +4705,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46339.2625</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4737,16 +4737,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" s="1" t="n">
-        <v>46241</v>
+        <v>46258</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46241</v>
+        <v>46258</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4758,29 +4758,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46281.25</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4789,17 +4789,13 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P74" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4848,7 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4864,29 +4860,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46242.5125</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4895,13 +4891,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="O76" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -4966,29 +4966,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4998,16 +4998,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46257</v>
+        <v>46248</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46257</v>
+        <v>46248</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5019,29 +5019,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5056,7 +5056,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46240.33125</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5099,17 +5099,13 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P80" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5121,29 +5117,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46245.29375</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -5152,17 +5148,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5174,29 +5166,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -5206,16 +5198,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5227,29 +5219,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -5259,16 +5251,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" s="1" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5280,29 +5272,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -5311,13 +5303,17 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="O84" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5359,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5407,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5452,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5497,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5542,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5587,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5632,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5677,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5722,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5767,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5812,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5857,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5902,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5947,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5992,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6037,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6082,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6127,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6172,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6217,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6262,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6307,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6352,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6397,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6442,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6487,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6532,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6577,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6622,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6667,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6712,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6765,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6818,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6865,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6912,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6959,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7006,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7053,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7100,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7147,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7194,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7241,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7288,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7335,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7382,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7429,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7476,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7523,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7570,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7617,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7662,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7711,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7762,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7817,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7866,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7911,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7960,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8015,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8060,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8105,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8150,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8199,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8244,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8285,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8334,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8383,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8428,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8477,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8526,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8571,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8616,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8661,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8718,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8763,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8816,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8832,29 +8828,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>MAERSK BUTON</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9392925</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>636N</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46257.25</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46257.52083333334</v>
+        <v>46270.91666666666</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8868,12 +8864,12 @@
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8885,29 +8881,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NORDPACIFIC</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9802487</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46271.02083333334</v>
+        <v>46266.75</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46271.58333333334</v>
+        <v>46267.33333333334</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8921,12 +8917,12 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8938,29 +8934,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MAERSK BUTON</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9392925</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>636N</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46269.58333333334</v>
+        <v>46270.25</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46270.91666666666</v>
+        <v>46272.25</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8974,12 +8970,12 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -8991,29 +8987,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>NORDPACIFIC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9802487</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46266.75</v>
+        <v>46271.02083333334</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>46267.33333333334</v>
+        <v>46271.58333333334</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -9027,12 +9023,12 @@
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9044,29 +9040,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46270.25</v>
+        <v>46257.25</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>46272.25</v>
+        <v>46257.52083333334</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
@@ -9080,12 +9076,12 @@
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9097,29 +9093,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>WEAVER ARROW</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9151826</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46269.25</v>
+        <v>46266.25</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>46271.25</v>
+        <v>46268.25</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
@@ -9134,7 +9130,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9142,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WEAVER ARROW</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>9151826</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9165,10 +9161,10 @@
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46266.25</v>
+        <v>46260.25</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46268.25</v>
+        <v>46262.25</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -9183,7 +9179,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9228,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9244,29 +9240,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46260.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>46262.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -9281,7 +9277,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9326,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9375,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9428,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9481,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9534,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9587,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9603,29 +9599,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9635,16 +9631,16 @@
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" s="1" t="n">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="P175" s="1" t="n">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9656,29 +9652,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9688,16 +9684,16 @@
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="P176" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9709,29 +9705,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46237.34375</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46288.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
@@ -9746,7 +9742,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9758,29 +9754,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46281.25</v>
+        <v>46286.2625</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
@@ -9789,13 +9785,17 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
+      <c r="O178" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="P178" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10108,12 +10108,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10127,17 +10127,17 @@
         </is>
       </c>
       <c r="F184" s="1" t="n">
-        <v>46204.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" s="1" t="n">
@@ -10153,7 +10153,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10184,17 +10184,17 @@
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46356.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46268</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" s="1" t="n">
-        <v>46268</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" s="1" t="n">
@@ -10210,7 +10210,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10298,17 +10298,17 @@
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46096.125</v>
+        <v>46356.25</v>
       </c>
       <c r="G187" s="1" t="n">
         <v>46387.25</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" s="1" t="n">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" s="1" t="n">
@@ -10324,7 +10324,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10700,35 +10700,35 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TS CHENNAI</t>
+          <t>KOTA LOCENG</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>9953846</t>
+          <t>9628336</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2604S</t>
+          <t>0171S</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2604N</t>
+          <t>0171N</t>
         </is>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46266.25</v>
+        <v>46264.72916666666</v>
       </c>
       <c r="G194" s="1" t="n">
-        <v>46267.58333333334</v>
+        <v>46266.58333333334</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46259.58333333334</v>
+        <v>46259.25</v>
       </c>
       <c r="I194" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.25</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" s="1" t="n">
@@ -10746,12 +10746,12 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10763,35 +10763,35 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KOTA LOCENG</t>
+          <t>TS CHENNAI</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>9628336</t>
+          <t>9953846</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0171S</t>
+          <t>2604S</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>0171N</t>
+          <t>2604N</t>
         </is>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46264.72916666666</v>
+        <v>46266.25</v>
       </c>
       <c r="G195" s="1" t="n">
-        <v>46266.58333333334</v>
+        <v>46267.58333333334</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46259.25</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="I195" s="1" t="n">
-        <v>46261.25</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" s="1" t="n">
@@ -10809,12 +10809,12 @@
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11210,139 +11210,139 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>101S</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>101N</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46261.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G202" s="1" t="n">
-        <v>46263.8125</v>
+        <v>46263.29166666666</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46255.91666666666</v>
-      </c>
-      <c r="I202" s="1" t="n">
-        <v>46258.58333333334</v>
-      </c>
-      <c r="J202" t="inlineStr"/>
+        <v>46256.25</v>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" s="1" t="n">
+        <v>46256.25</v>
+      </c>
       <c r="K202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M202" s="1" t="n">
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="P202" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="Q202" s="1" t="n">
-        <v>46267</v>
-      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>101S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>101N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>46263.29166666666</v>
+        <v>46263.8125</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46256.25</v>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" s="1" t="n">
-        <v>46256.25</v>
-      </c>
+        <v>46255.91666666666</v>
+      </c>
+      <c r="I203" s="1" t="n">
+        <v>46258.58333333334</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="P203" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="Q203" s="1" t="n">
+        <v>46267</v>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11411,139 +11411,139 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TAMPA I</t>
+          <t>COLOMBO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>9196840</t>
+          <t>9256212</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>159S</t>
+          <t>084S</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>159N</t>
+          <t>084N</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46261.25</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="G205" s="1" t="n">
-        <v>46263.14583333334</v>
+        <v>46261.625</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>46254.91666666666</v>
-      </c>
-      <c r="I205" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="J205" t="inlineStr"/>
+        <v>46255.25</v>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" s="1" t="n">
+        <v>46255.25</v>
+      </c>
       <c r="K205" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
       <c r="L205" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="M205" s="1" t="n">
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="P205" s="1" t="n">
-        <v>46262.25</v>
-      </c>
-      <c r="Q205" s="1" t="n">
-        <v>46266</v>
-      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH1</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>COLOMBO</t>
+          <t>TAMPA I</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>9256212</t>
+          <t>9196840</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>084S</t>
+          <t>159S</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>084N</t>
+          <t>159N</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46260.58333333334</v>
+        <v>46261.25</v>
       </c>
       <c r="G206" s="1" t="n">
-        <v>46261.625</v>
+        <v>46263.14583333334</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46255.25</v>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" s="1" t="n">
-        <v>46255.25</v>
-      </c>
+        <v>46254.91666666666</v>
+      </c>
+      <c r="I206" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
       <c r="L206" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" s="1" t="n">
+      <c r="M206" s="1" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="P206" s="1" t="n">
+        <v>46262.25</v>
+      </c>
+      <c r="Q206" s="1" t="n">
+        <v>46266</v>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -11934,18 +11934,18 @@
         <v>46258.58333333334</v>
       </c>
       <c r="O212" s="1" t="n">
+        <v>46259.00069444445</v>
+      </c>
+      <c r="P212" s="1" t="n">
+        <v>46259.00069444445</v>
+      </c>
+      <c r="Q212" s="1" t="n">
         <v>46262.00069444445</v>
-      </c>
-      <c r="P212" s="1" t="n">
-        <v>46262.00069444445</v>
-      </c>
-      <c r="Q212" s="1" t="n">
-        <v>46265.00069444445</v>
       </c>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12552,29 +12552,29 @@
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>OLGA MAERSK</t>
+          <t>CMA CGM SAMSON</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>9251614</t>
+          <t>9436379</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>629S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12583,18 +12583,18 @@
         </is>
       </c>
       <c r="F222" s="1" t="n">
-        <v>46256.24305555555</v>
+        <v>46256.15694444445</v>
       </c>
       <c r="G222" s="1" t="n">
-        <v>46257.33472222222</v>
+        <v>46259.625</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46250.91666666666</v>
-      </c>
-      <c r="I222" s="1" t="n">
-        <v>46252.91666666666</v>
-      </c>
-      <c r="J222" t="inlineStr"/>
+        <v>46250.25</v>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" s="1" t="n">
+        <v>46250.25</v>
+      </c>
       <c r="K222" s="1" t="n">
         <v>46254.91666666666</v>
       </c>
@@ -12602,48 +12602,44 @@
         <v>46254.91666666666</v>
       </c>
       <c r="M222" s="1" t="n">
-        <v>46254.91666666666</v>
-      </c>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="P222" s="1" t="n">
-        <v>46257.25</v>
-      </c>
-      <c r="Q222" s="1" t="n">
-        <v>46261</v>
-      </c>
+        <v>46256.54166666666</v>
+      </c>
+      <c r="N222" s="1" t="n">
+        <v>46258.04166666666</v>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CMA CGM SAMSON</t>
+          <t>OLGA MAERSK</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>9436379</t>
+          <t>9251614</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>629S</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12652,18 +12648,18 @@
         </is>
       </c>
       <c r="F223" s="1" t="n">
-        <v>46256.15694444445</v>
+        <v>46256.24305555555</v>
       </c>
       <c r="G223" s="1" t="n">
-        <v>46259.625</v>
+        <v>46257.33472222222</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46250.25</v>
-      </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" s="1" t="n">
-        <v>46250.25</v>
-      </c>
+        <v>46250.91666666666</v>
+      </c>
+      <c r="I223" s="1" t="n">
+        <v>46252.91666666666</v>
+      </c>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" s="1" t="n">
         <v>46254.91666666666</v>
       </c>
@@ -12671,22 +12667,26 @@
         <v>46254.91666666666</v>
       </c>
       <c r="M223" s="1" t="n">
-        <v>46256.54166666666</v>
-      </c>
-      <c r="N223" s="1" t="n">
-        <v>46258.04166666666</v>
-      </c>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
+        <v>46254.91666666666</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="P223" s="1" t="n">
+        <v>46257.25</v>
+      </c>
+      <c r="Q223" s="1" t="n">
+        <v>46261</v>
+      </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12836,29 +12836,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MSC HANISHA III</t>
+          <t>HANSA FREYBURG</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>9283708</t>
+          <t>9256389</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051W</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KI633A</t>
+          <t>051E</t>
         </is>
       </c>
       <c r="F226" s="1" t="n">
-        <v>46257.275</v>
+        <v>46256.5</v>
       </c>
       <c r="G226" s="1" t="n">
-        <v>46257.875</v>
+        <v>46257.21111111111</v>
       </c>
       <c r="H226" s="1" t="n">
         <v>46249.23958333334</v>
@@ -12879,21 +12879,21 @@
         <v>46253.75</v>
       </c>
       <c r="N226" s="1" t="n">
-        <v>46256.66666666666</v>
+        <v>46253.75</v>
       </c>
       <c r="O226" s="1" t="n">
-        <v>46258.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="P226" s="1" t="n">
-        <v>46258.00069444445</v>
+        <v>46257.00069444445</v>
       </c>
       <c r="Q226" s="1" t="n">
-        <v>46261.00069444445</v>
+        <v>46260.00069444445</v>
       </c>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -12905,29 +12905,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HANSA FREYBURG</t>
+          <t>MSC HANISHA III</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>9256389</t>
+          <t>9283708</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>051W</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>051E</t>
+          <t>KI633A</t>
         </is>
       </c>
       <c r="F227" s="1" t="n">
-        <v>46256.5</v>
+        <v>46257.275</v>
       </c>
       <c r="G227" s="1" t="n">
-        <v>46257.21111111111</v>
+        <v>46257.875</v>
       </c>
       <c r="H227" s="1" t="n">
         <v>46249.23958333334</v>
@@ -12948,21 +12948,21 @@
         <v>46253.75</v>
       </c>
       <c r="N227" s="1" t="n">
-        <v>46253.75</v>
+        <v>46256.66666666666</v>
       </c>
       <c r="O227" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="P227" s="1" t="n">
-        <v>46257.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="Q227" s="1" t="n">
-        <v>46260.00069444445</v>
+        <v>46261.00069444445</v>
       </c>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13293,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13374,38 +13374,38 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PRIDE C</t>
+          <t>EVER SUPERB</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>9978640</t>
+          <t>9300427</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>030W</t>
+          <t>0115S</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>030E</t>
+          <t>0115N</t>
         </is>
       </c>
       <c r="F234" s="1" t="n">
-        <v>46251.15416666667</v>
+        <v>46254.22083333333</v>
       </c>
       <c r="G234" s="1" t="n">
-        <v>46251.84583333333</v>
+        <v>46256.28819444445</v>
       </c>
       <c r="H234" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="I234" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="J234" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="K234" s="1" t="n">
         <v>46250.75</v>
@@ -13417,21 +13417,21 @@
         <v>46250.75</v>
       </c>
       <c r="N234" s="1" t="n">
-        <v>46251.45833333334</v>
+        <v>46254.04166666666</v>
       </c>
       <c r="O234" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="P234" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="Q234" s="1" t="n">
-        <v>46255.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13443,38 +13443,38 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EVER SUPERB</t>
+          <t>PRIDE C</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>9300427</t>
+          <t>9978640</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0115S</t>
+          <t>030W</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>0115N</t>
+          <t>030E</t>
         </is>
       </c>
       <c r="F235" s="1" t="n">
-        <v>46254.22083333333</v>
+        <v>46251.15416666667</v>
       </c>
       <c r="G235" s="1" t="n">
-        <v>46256.28819444445</v>
+        <v>46251.84583333333</v>
       </c>
       <c r="H235" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="I235" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="J235" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="K235" s="1" t="n">
         <v>46250.75</v>
@@ -13486,21 +13486,21 @@
         <v>46250.75</v>
       </c>
       <c r="N235" s="1" t="n">
-        <v>46254.04166666666</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="O235" s="1" t="n">
+        <v>46252.00069444445</v>
+      </c>
+      <c r="P235" s="1" t="n">
+        <v>46252.00069444445</v>
+      </c>
+      <c r="Q235" s="1" t="n">
         <v>46255.00069444445</v>
-      </c>
-      <c r="P235" s="1" t="n">
-        <v>46255.00069444445</v>
-      </c>
-      <c r="Q235" s="1" t="n">
-        <v>46258.00069444445</v>
       </c>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14381,7 +14381,7 @@
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16691,7 +16691,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16967,7 @@
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17381,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18067,7 +18067,7 @@
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18256,7 @@
       <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19682,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20025,7 +20025,7 @@
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20585,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20790,7 +20790,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20861,7 +20861,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -20989,7 +20989,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21107,7 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>
@@ -21343,7 +21343,7 @@
       <c r="R352" t="inlineStr"/>
       <c r="S352" t="inlineStr">
         <is>
-          <t>2026-08-23 13:39:06</t>
+          <t>2026-08-23 18:00:25</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -3938,29 +3938,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3969,13 +3969,17 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="O58" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -3987,29 +3991,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -4018,13 +4022,17 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="O59" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4036,29 +4044,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46339.2625</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -4067,17 +4075,13 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="P60" s="1" t="n">
-        <v>46254</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4089,29 +4093,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46281.25</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -4120,17 +4124,13 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4142,29 +4142,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46245.29375</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4173,17 +4173,13 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4195,29 +4191,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4226,13 +4222,17 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="O63" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P63" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4244,29 +4244,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46242.5125</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46243.0625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4276,16 +4276,16 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4297,29 +4297,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4329,16 +4329,16 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4350,29 +4350,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4382,16 +4382,16 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" s="1" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4403,29 +4403,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4434,13 +4434,17 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="O67" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4452,29 +4456,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4484,16 +4488,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" s="1" t="n">
-        <v>46247</v>
+        <v>46243</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46247</v>
+        <v>46243</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4505,29 +4509,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4537,16 +4541,16 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" s="1" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4558,29 +4562,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46247.48055555556</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4589,13 +4593,17 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="O70" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>46257</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4607,29 +4615,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4638,13 +4646,17 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="O71" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P71" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4656,29 +4668,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46288.25</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4687,13 +4699,17 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="O72" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4705,29 +4721,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46245.56041666667</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4737,16 +4753,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" s="1" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4758,29 +4774,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46281.25</v>
+        <v>46339.2625</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4795,7 +4811,7 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4807,29 +4823,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4839,16 +4855,16 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" s="1" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4860,29 +4876,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46245.31875</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4891,17 +4907,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4913,29 +4925,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4944,17 +4956,13 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P77" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -4966,29 +4974,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -5007,7 +5015,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5019,29 +5027,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46239.07847222222</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5050,13 +5058,17 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5068,29 +5080,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5099,13 +5111,17 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="O80" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>46253</v>
+      </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5117,26 +5133,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G81" s="1" t="n">
         <v>46363.2625</v>
@@ -5154,7 +5170,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5166,29 +5182,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -5198,16 +5214,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" s="1" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5219,29 +5235,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46339.2625</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -5250,17 +5266,13 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="P83" s="1" t="n">
-        <v>46241</v>
-      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5272,29 +5284,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46243.01875</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -5304,16 +5316,16 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5371,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5419,7 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5464,7 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5509,7 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5554,7 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5599,7 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5644,7 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5689,7 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5734,7 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5779,7 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5824,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5869,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5914,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5959,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6004,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6049,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6094,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6139,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6184,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6229,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6274,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6319,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6364,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6409,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6454,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6499,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6544,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6589,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6634,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6679,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6724,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6777,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6830,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6877,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6924,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6971,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7018,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7065,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7112,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7159,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7206,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7253,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7300,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7347,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7394,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7441,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7488,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7535,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7582,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7629,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7674,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7723,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7774,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7829,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7878,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7923,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7972,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8027,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8072,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8117,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8162,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8211,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8256,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8297,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8346,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8395,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8440,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8489,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8538,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8583,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8628,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8673,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8730,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8775,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8775,29 +8787,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MAERSK RIO ALFA</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>9348106</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>633N</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46264.58333333334</v>
+        <v>46270.25</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>46265.91666666666</v>
+        <v>46272.25</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8811,12 +8823,12 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8828,29 +8840,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MAERSK BUTON</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9392925</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>636N</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46269.58333333334</v>
+        <v>46266.75</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>46270.91666666666</v>
+        <v>46267.33333333334</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8864,12 +8876,12 @@
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8881,29 +8893,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>MAERSK RIO ALFA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9348106</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>633N</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46266.75</v>
+        <v>46264.58333333334</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>46267.33333333334</v>
+        <v>46265.91666666666</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -8917,12 +8929,12 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -8934,29 +8946,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>MAERSK BUTON</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9392925</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>636N</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46270.25</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>46272.25</v>
+        <v>46270.91666666666</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -8970,12 +8982,12 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9040,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9093,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9142,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9142,29 +9154,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GREAT AGILITY</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>9792890</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46260.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>46262.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -9179,7 +9191,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9191,29 +9203,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F167" s="1" t="n">
-        <v>46275.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G167" s="1" t="n">
-        <v>46277.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
@@ -9228,7 +9240,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9240,29 +9252,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46269.25</v>
+        <v>46275.25</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>46271.25</v>
+        <v>46277.25</v>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -9277,7 +9289,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9289,29 +9301,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>GREAT AGILITY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9792890</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46260.25</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46262.25</v>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -9326,7 +9338,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9387,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9440,7 @@
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9493,7 @@
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9546,7 @@
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9599,7 @@
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9599,29 +9611,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46237.34375</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46286.2625</v>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9630,17 +9642,13 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
-      <c r="O175" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P175" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9652,29 +9660,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46240.33125</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46339.2625</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9683,17 +9691,13 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
-      <c r="O176" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="P176" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9705,26 +9709,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G177" s="1" t="n">
         <v>46286.2625</v>
@@ -9742,7 +9746,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9754,29 +9758,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46247.48055555556</v>
+        <v>46253.44375</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46288.25</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
@@ -9785,17 +9789,13 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="P178" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10108,12 +10108,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EMC MT POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1000008</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10127,17 +10127,17 @@
         </is>
       </c>
       <c r="F184" s="1" t="n">
-        <v>46096.125</v>
+        <v>46386.25</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>46209</v>
+        <v>46104.25</v>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" s="1" t="n">
-        <v>46209</v>
+        <v>46284.25</v>
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" s="1" t="n">
@@ -10153,7 +10153,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>EMC MT POOL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000008</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10184,17 +10184,17 @@
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46204.25</v>
+        <v>46096.125</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46209</v>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" s="1" t="n">
@@ -10210,7 +10210,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10222,12 +10222,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10241,17 +10241,17 @@
         </is>
       </c>
       <c r="F186" s="1" t="n">
-        <v>46386.25</v>
+        <v>46356.25</v>
       </c>
       <c r="G186" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46104.25</v>
+        <v>46268</v>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" s="1" t="n">
-        <v>46284.25</v>
+        <v>46268</v>
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" s="1" t="n">
@@ -10267,7 +10267,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10298,17 +10298,17 @@
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46356.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46268</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" s="1" t="n">
-        <v>46268</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" s="1" t="n">
@@ -10324,7 +10324,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11210,139 +11210,139 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>TS NANSHA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9914149</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>101S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>101N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46261.58333333334</v>
+        <v>46261.91666666666</v>
       </c>
       <c r="G202" s="1" t="n">
-        <v>46263.29166666666</v>
+        <v>46263.8125</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46256.25</v>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" s="1" t="n">
-        <v>46256.25</v>
-      </c>
+        <v>46255.91666666666</v>
+      </c>
+      <c r="I202" s="1" t="n">
+        <v>46258.58333333334</v>
+      </c>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" s="1" t="n">
+      <c r="M202" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="P202" s="1" t="n">
+        <v>46263.25</v>
+      </c>
+      <c r="Q202" s="1" t="n">
+        <v>46267</v>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TS NANSHA</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9914149</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>101S</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>101N</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46261.91666666666</v>
+        <v>46261.58333333334</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>46263.8125</v>
+        <v>46263.29166666666</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46255.91666666666</v>
-      </c>
-      <c r="I203" s="1" t="n">
-        <v>46258.58333333334</v>
-      </c>
-      <c r="J203" t="inlineStr"/>
+        <v>46256.25</v>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" s="1" t="n">
+        <v>46256.25</v>
+      </c>
       <c r="K203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
       <c r="L203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="M203" s="1" t="n">
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" s="1" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="P203" s="1" t="n">
-        <v>46263.25</v>
-      </c>
-      <c r="Q203" s="1" t="n">
-        <v>46267</v>
-      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46260.75</v>
+        <v>46261.75</v>
       </c>
       <c r="G204" s="1" t="n">
-        <v>46261.75</v>
+        <v>46262.75</v>
       </c>
       <c r="H204" s="1" t="n">
         <v>46256.23958333334</v>
@@ -11411,7 +11411,7 @@
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="F211" s="1" t="n">
-        <v>46259.5</v>
+        <v>46259.75</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>46261.5</v>
+        <v>46261.75</v>
       </c>
       <c r="H211" s="1" t="n">
         <v>46254.23958333334</v>
@@ -11876,7 +11876,7 @@
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="F212" s="1" t="n">
-        <v>46258.5</v>
+        <v>46258.875</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>46259.75</v>
+        <v>46259.95833333334</v>
       </c>
       <c r="H212" s="1" t="n">
         <v>46256.48958333334</v>
@@ -11945,7 +11945,7 @@
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
         <v>46258.16666666666</v>
       </c>
       <c r="G213" s="1" t="n">
-        <v>46260.25</v>
+        <v>46259.75</v>
       </c>
       <c r="H213" s="1" t="n">
         <v>46253.23958333334</v>
@@ -12014,7 +12014,7 @@
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
         <v>46257.95833333334</v>
       </c>
       <c r="G216" s="1" t="n">
-        <v>46258.75</v>
+        <v>46258.83333333334</v>
       </c>
       <c r="H216" s="1" t="n">
         <v>46252.23958333334</v>
@@ -12221,7 +12221,7 @@
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
         <v>46257.275</v>
       </c>
       <c r="G227" s="1" t="n">
-        <v>46257.875</v>
+        <v>46257.95833333334</v>
       </c>
       <c r="H227" s="1" t="n">
         <v>46249.23958333334</v>
@@ -12962,7 +12962,7 @@
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13293,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13374,38 +13374,38 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EVER SUPERB</t>
+          <t>PRIDE C</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>9300427</t>
+          <t>9978640</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0115S</t>
+          <t>030W</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>0115N</t>
+          <t>030E</t>
         </is>
       </c>
       <c r="F234" s="1" t="n">
-        <v>46254.22083333333</v>
+        <v>46251.15416666667</v>
       </c>
       <c r="G234" s="1" t="n">
-        <v>46256.28819444445</v>
+        <v>46251.84583333333</v>
       </c>
       <c r="H234" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="I234" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="J234" s="1" t="n">
-        <v>46246.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="K234" s="1" t="n">
         <v>46250.75</v>
@@ -13417,21 +13417,21 @@
         <v>46250.75</v>
       </c>
       <c r="N234" s="1" t="n">
-        <v>46254.04166666666</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="O234" s="1" t="n">
+        <v>46252.00069444445</v>
+      </c>
+      <c r="P234" s="1" t="n">
+        <v>46252.00069444445</v>
+      </c>
+      <c r="Q234" s="1" t="n">
         <v>46255.00069444445</v>
-      </c>
-      <c r="P234" s="1" t="n">
-        <v>46255.00069444445</v>
-      </c>
-      <c r="Q234" s="1" t="n">
-        <v>46258.00069444445</v>
       </c>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13443,38 +13443,38 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PRIDE C</t>
+          <t>OOCL MIAMI</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>9978640</t>
+          <t>9477892</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>030W</t>
+          <t>114S</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>030E</t>
+          <t>114N</t>
         </is>
       </c>
       <c r="F235" s="1" t="n">
-        <v>46251.15416666667</v>
+        <v>46251.7</v>
       </c>
       <c r="G235" s="1" t="n">
-        <v>46251.84583333333</v>
+        <v>46255.12916666667</v>
       </c>
       <c r="H235" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="I235" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="J235" s="1" t="n">
-        <v>46247.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="K235" s="1" t="n">
         <v>46250.75</v>
@@ -13486,7 +13486,7 @@
         <v>46250.75</v>
       </c>
       <c r="N235" s="1" t="n">
-        <v>46251.45833333334</v>
+        <v>46252.99930555555</v>
       </c>
       <c r="O235" s="1" t="n">
         <v>46252.00069444445</v>
@@ -13500,7 +13500,7 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13512,38 +13512,38 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OOCL MIAMI</t>
+          <t>EVER SUPERB</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>9477892</t>
+          <t>9300427</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>114S</t>
+          <t>0115S</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>114N</t>
+          <t>0115N</t>
         </is>
       </c>
       <c r="F236" s="1" t="n">
-        <v>46251.7</v>
+        <v>46254.22083333333</v>
       </c>
       <c r="G236" s="1" t="n">
-        <v>46255.12916666667</v>
+        <v>46256.28819444445</v>
       </c>
       <c r="H236" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="I236" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="J236" s="1" t="n">
-        <v>46245.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="K236" s="1" t="n">
         <v>46250.75</v>
@@ -13555,21 +13555,21 @@
         <v>46250.75</v>
       </c>
       <c r="N236" s="1" t="n">
-        <v>46252.99930555555</v>
+        <v>46254.04166666666</v>
       </c>
       <c r="O236" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="P236" s="1" t="n">
-        <v>46252.00069444445</v>
+        <v>46255.00069444445</v>
       </c>
       <c r="Q236" s="1" t="n">
-        <v>46255.00069444445</v>
+        <v>46258.00069444445</v>
       </c>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -13906,49 +13906,49 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CMA CGM GREEN</t>
+          <t>OOCL YOKOHAMA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>9810915</t>
+          <t>9329538</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>213S</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>213N</t>
         </is>
       </c>
       <c r="F242" s="1" t="n">
-        <v>46250.3375</v>
+        <v>46250.11458333334</v>
       </c>
       <c r="G242" s="1" t="n">
-        <v>46250.72152777778</v>
+        <v>46251.44027777778</v>
       </c>
       <c r="H242" s="1" t="n">
-        <v>46244.91666666666</v>
-      </c>
-      <c r="I242" s="1" t="n">
-        <v>46246.91666666666</v>
-      </c>
-      <c r="J242" t="inlineStr"/>
+        <v>46244.25</v>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" s="1" t="n">
+        <v>46244.25</v>
+      </c>
       <c r="K242" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
@@ -13956,68 +13956,64 @@
         <v>46248.91666666666</v>
       </c>
       <c r="M242" s="1" t="n">
-        <v>46248.91666666666</v>
-      </c>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" s="1" t="n">
-        <v>46250.58333333334</v>
-      </c>
-      <c r="P242" s="1" t="n">
-        <v>46250.58333333334</v>
-      </c>
-      <c r="Q242" s="1" t="n">
-        <v>46254</v>
-      </c>
+        <v>46250.5</v>
+      </c>
+      <c r="N242" s="1" t="n">
+        <v>46249.08333333334</v>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>OOCL YOKOHAMA</t>
+          <t>CMA CGM GREEN</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>9329538</t>
+          <t>9810915</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>213S</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>213N</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F243" s="1" t="n">
-        <v>46250.11458333334</v>
+        <v>46250.3375</v>
       </c>
       <c r="G243" s="1" t="n">
-        <v>46251.44027777778</v>
+        <v>46250.72152777778</v>
       </c>
       <c r="H243" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" s="1" t="n">
-        <v>46244.25</v>
-      </c>
+        <v>46244.91666666666</v>
+      </c>
+      <c r="I243" s="1" t="n">
+        <v>46246.91666666666</v>
+      </c>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" s="1" t="n">
         <v>46248.91666666666</v>
       </c>
@@ -14025,22 +14021,26 @@
         <v>46248.91666666666</v>
       </c>
       <c r="M243" s="1" t="n">
-        <v>46250.5</v>
-      </c>
-      <c r="N243" s="1" t="n">
-        <v>46249.08333333334</v>
-      </c>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
+        <v>46248.91666666666</v>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" s="1" t="n">
+        <v>46250.58333333334</v>
+      </c>
+      <c r="P243" s="1" t="n">
+        <v>46250.58333333334</v>
+      </c>
+      <c r="Q243" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14312,51 +14312,49 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ALS JUNO</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>9948645</t>
+          <t>9919254</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="F248" s="1" t="n">
-        <v>46247.39166666667</v>
+        <v>46251.41319444445</v>
       </c>
       <c r="G248" s="1" t="n">
-        <v>46249.9875</v>
+        <v>46252.48125</v>
       </c>
       <c r="H248" s="1" t="n">
-        <v>46241.23958333334</v>
+        <v>46241.25</v>
       </c>
       <c r="I248" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
-      <c r="J248" s="1" t="n">
-        <v>46241.23958333334</v>
-      </c>
+        <v>46244.25</v>
+      </c>
+      <c r="J248" t="inlineStr"/>
       <c r="K248" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -14366,64 +14364,68 @@
       <c r="M248" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N248" s="1" t="n">
-        <v>46247.91666666666</v>
-      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="O248" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="P248" s="1" t="n">
-        <v>46248.00069444445</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="Q248" s="1" t="n">
-        <v>46251.00069444445</v>
-      </c>
-      <c r="R248" t="inlineStr"/>
+        <v>46256</v>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>ALS JUNO</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>9919254</t>
+          <t>9948645</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F249" s="1" t="n">
-        <v>46251.41319444445</v>
+        <v>46247.39166666667</v>
       </c>
       <c r="G249" s="1" t="n">
-        <v>46252.48125</v>
+        <v>46249.9875</v>
       </c>
       <c r="H249" s="1" t="n">
-        <v>46241.25</v>
+        <v>46241.23958333334</v>
       </c>
       <c r="I249" s="1" t="n">
-        <v>46244.25</v>
-      </c>
-      <c r="J249" t="inlineStr"/>
+        <v>46241.23958333334</v>
+      </c>
+      <c r="J249" s="1" t="n">
+        <v>46241.23958333334</v>
+      </c>
       <c r="K249" s="1" t="n">
         <v>46246.25</v>
       </c>
@@ -14433,24 +14435,22 @@
       <c r="M249" s="1" t="n">
         <v>46246.25</v>
       </c>
-      <c r="N249" t="inlineStr"/>
+      <c r="N249" s="1" t="n">
+        <v>46247.91666666666</v>
+      </c>
       <c r="O249" s="1" t="n">
-        <v>46252.58333333334</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="P249" s="1" t="n">
-        <v>46252.58333333334</v>
+        <v>46248.00069444445</v>
       </c>
       <c r="Q249" s="1" t="n">
-        <v>46256</v>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46251.00069444445</v>
+      </c>
+      <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16691,7 +16691,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16967,7 @@
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17381,7 @@
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       <c r="R294" t="inlineStr"/>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18067,7 +18067,7 @@
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18256,7 @@
       <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19682,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20025,7 +20025,7 @@
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20585,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20790,7 +20790,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20861,7 +20861,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -20989,7 +20989,7 @@
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21107,7 @@
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
@@ -21343,7 +21343,7 @@
       <c r="R352" t="inlineStr"/>
       <c r="S352" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:25</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -574,29 +574,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GRAND VENUS</t>
+          <t>HESTIA LEADER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9303211</t>
+          <t>9355226</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46226.29930555556</v>
+        <v>46226.02986111111</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46227.61805555555</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -605,8 +605,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>46228</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
@@ -618,50 +622,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HESTIA LEADER</t>
+          <t>CNC JAWA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9355226</t>
+          <t>9963748</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46226.02986111111</v>
+        <v>46219.16111111111</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46227.61805555555</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>46220.25416666667</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>46212.55555555555</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>46215.58333333334</v>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" s="1" t="n">
+        <v>46217.58333333334</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46217.58333333334</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>46217.58333333334</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" s="1" t="n">
-        <v>46228</v>
+        <v>46220.25</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>46228</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+        <v>46220.25</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-13 07:05:10</t>
@@ -671,115 +691,113 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CNC JAWA</t>
+          <t>MSC DAVAO III</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9963748</t>
+          <t>9243241</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>KH629A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>KH629A</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46219.16111111111</v>
+        <v>46218.425</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46220.25416666667</v>
+        <v>46219.90833333333</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46212.55555555555</v>
+        <v>46215.23958333334</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>46215.58333333334</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>46215.23958333334</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46215.23958333334</v>
+      </c>
       <c r="K4" s="1" t="n">
-        <v>46217.58333333334</v>
+        <v>46217.25</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46217.58333333334</v>
+        <v>46217.25</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>46217.58333333334</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>46217.25</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>46218.25</v>
+      </c>
       <c r="O4" s="1" t="n">
-        <v>46220.25</v>
+        <v>46219.00069444445</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>46220.25</v>
+        <v>46219.00069444445</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46222.00069444445</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-08-13 07:05:10</t>
+          <t>2026-08-14 09:12:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSC DAVAO III</t>
+          <t>COSCO HONG KONG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9243241</t>
+          <t>9227778</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KH629A</t>
+          <t>207S</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KH629A</t>
+          <t>207N</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46218.425</v>
+        <v>46219.09305555555</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46219.90833333333</v>
+        <v>46220.84375</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46215.23958333334</v>
+        <v>46212.25</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46215.23958333334</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>46215.23958333334</v>
-      </c>
+        <v>46215.25</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" s="1" t="n">
-        <v>46217.25</v>
+        <v>46218.55555555555</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>46217.25</v>
@@ -787,91 +805,77 @@
       <c r="M5" s="1" t="n">
         <v>46217.25</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>46218.25</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" s="1" t="n">
-        <v>46219.00069444445</v>
+        <v>46220.25</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>46219.00069444445</v>
+        <v>46220.25</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46222.00069444445</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>46224</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-14 09:12:18</t>
+          <t>2026-08-14 16:05:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COSCO HONG KONG</t>
+          <t>TYSLA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9227778</t>
+          <t>9515400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>207S</t>
+          <t>EF610</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>207N</t>
+          <t>EF610</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46219.09305555555</v>
+        <v>46227.52777777778</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46220.84375</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>46212.25</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>46215.25</v>
-      </c>
+        <v>46228.39236111111</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" s="1" t="n">
-        <v>46218.55555555555</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>46217.25</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>46217.25</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" s="1" t="n">
-        <v>46220.25</v>
+        <v>46228</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46220.25</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46228</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:05:48</t>
+          <t>2026-08-14 20:37:52</t>
         </is>
       </c>
     </row>
@@ -883,29 +887,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TYSLA</t>
+          <t>ELEGANT ACE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9515400</t>
+          <t>9561265</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EF610</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EF610</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46227.52777777778</v>
+        <v>46227.48402777778</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46228.39236111111</v>
+        <v>46229.15833333333</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -915,10 +919,10 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -936,29 +940,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ELEGANT ACE</t>
+          <t>GOLD XING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9561265</t>
+          <t>9308807</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24S</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46227.48402777778</v>
+        <v>46227.39930555555</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46229.15833333333</v>
+        <v>46227.95694444444</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -968,10 +972,10 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" s="1" t="n">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -989,29 +993,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GOLD XING</t>
+          <t>POSEIDON LEADER</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9308807</t>
+          <t>9335965</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24S</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46227.39930555555</v>
+        <v>46227.69097222222</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46227.95694444444</v>
+        <v>46229.66041666667</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1021,10 +1025,10 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1037,50 +1041,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>POSEIDON LEADER</t>
+          <t>OOCL HOUSTON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9335965</t>
+          <t>9355757</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>219S</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>219N</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46227.69097222222</v>
+        <v>46229.26666666667</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46229.66041666667</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>46230.82986111111</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46224.25</v>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>46230</v>
-      </c>
+      <c r="J10" s="1" t="n">
+        <v>46224.25</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46228.58333333334</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>46228.58333333334</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>46228.54166666666</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>46229.91666666666</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>BTH2</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>2026-08-14 20:37:52</t>
@@ -1095,55 +1111,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OOCL HOUSTON</t>
+          <t>HIGHLAND CHIEF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9355757</t>
+          <t>9689940</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>219S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>219N</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46229.26666666667</v>
+        <v>46228.67569444444</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46230.82986111111</v>
+        <v>46229.57638888889</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46224.25</v>
+        <v>46223.25</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="1" t="n">
-        <v>46224.25</v>
+        <v>46223.25</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46228.58333333334</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46228.58333333334</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>46228.54166666666</v>
+        <v>46228.20833333334</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>46229.91666666666</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>BTH1</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1160,48 +1176,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HIGHLAND CHIEF</t>
+          <t>METHONI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9689940</t>
+          <t>9256755</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>625S</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2617N</t>
+          <t>629N</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46228.67569444444</v>
+        <v>46224.21527777778</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46229.57638888889</v>
+        <v>46226.08888888889</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46223.25</v>
+        <v>46219.25</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" s="1" t="n">
-        <v>46223.25</v>
+        <v>46219.25</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46227.58333333334</v>
+        <v>46223.58333333334</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46227.58333333334</v>
+        <v>46223.58333333334</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46228.20833333334</v>
+        <v>46223.91666666666</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>46227.58333333334</v>
+        <v>46224.58333333334</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1225,55 +1241,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>METHONI</t>
+          <t>KOTA LARIS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9256755</t>
+          <t>9351048</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>625S</t>
+          <t>100S</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>629N</t>
+          <t>100N</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46224.21527777778</v>
+        <v>46223.23958333334</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46226.08888888889</v>
+        <v>46224.8875</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46219.25</v>
+        <v>46218.25</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="1" t="n">
-        <v>46219.25</v>
+        <v>46218.25</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46223.58333333334</v>
+        <v>46222.58333333334</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46223.58333333334</v>
+        <v>46222.58333333334</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46222.95833333334</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>46224.58333333334</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1285,65 +1301,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOTA LARIS</t>
+          <t>ESL WINNER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9351048</t>
+          <t>9347281</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>100S</t>
+          <t>036W</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>036E</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46223.23958333334</v>
+        <v>46219.99166666667</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46224.8875</v>
+        <v>46220.75</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46218.25</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>46213.23958333334</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>46213.23958333334</v>
+      </c>
       <c r="J14" s="1" t="n">
-        <v>46218.25</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46222.58333333334</v>
+        <v>46217.75</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46222.58333333334</v>
+        <v>46217.75</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46222.95833333334</v>
+        <v>46217.75</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>46222.99930555555</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>BTH3</t>
-        </is>
-      </c>
+        <v>46219.75</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>46220.00069444445</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>46220.00069444445</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>46223.00069444445</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-14 20:37:52</t>
+          <t>2026-08-15 06:19:00</t>
         </is>
       </c>
     </row>
@@ -1355,59 +1375,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESL WINNER</t>
+          <t>APL COLUMBUS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9347281</t>
+          <t>9597525</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>036W</t>
+          <t>MA618A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>036E</t>
+          <t>MA626R</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46219.99166666667</v>
+        <v>46218.325</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46220.75</v>
+        <v>46220.49583333333</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46213.23958333334</v>
+        <v>46210.23958333334</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>46213.23958333334</v>
+        <v>46210.23958333334</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>46213.23958333334</v>
+        <v>46210.23958333334</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46217.75</v>
+        <v>46217.25</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46217.75</v>
+        <v>46217.25</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46217.75</v>
+        <v>46217.25</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>46219.75</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>46220.00069444445</v>
+        <v>46219.00069444445</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46220.00069444445</v>
+        <v>46219.00069444445</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46223.00069444445</v>
+        <v>46222.00069444445</v>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -1419,172 +1439,156 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APL COLUMBUS</t>
+          <t>MAERSK WELLINGTON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9597525</t>
+          <t>9391660</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MA618A</t>
+          <t>624S</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MA626R</t>
+          <t>629N</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46218.325</v>
+        <v>46220.58611111111</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46220.49583333333</v>
+        <v>46221.75347222222</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46210.23958333334</v>
+        <v>46214.25</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>46210.23958333334</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>46210.23958333334</v>
-      </c>
+        <v>46217.25</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" s="1" t="n">
-        <v>46217.25</v>
+        <v>46219.25</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46217.25</v>
+        <v>46219.25</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46217.25</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>46218.41666666666</v>
-      </c>
+        <v>46219.25</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" s="1" t="n">
-        <v>46219.00069444445</v>
+        <v>46221.25</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46219.00069444445</v>
+        <v>46221.25</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46222.00069444445</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
+        <v>46225</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-15 06:19:00</t>
+          <t>2026-08-15 17:57:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>AAT APPLETON DOCK MELBOURNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAERSK WELLINGTON</t>
+          <t>GREBE ARROW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9391660</t>
+          <t>9077070</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>624S</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>629N</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>46220.58611111111</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46221.75347222222</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>46214.25</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>46217.25</v>
-      </c>
+        <v>46232.8875</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" s="1" t="n">
-        <v>46219.25</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>46219.25</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>46219.25</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" s="1" t="n">
-        <v>46221.25</v>
+        <v>46234</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46221.25</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46234</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-15 17:57:19</t>
+          <t>2026-08-15 23:57:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAT APPLETON DOCK MELBOURNE</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GREBE ARROW</t>
+          <t>TRANS FUTURE 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9077070</t>
+          <t>9326079</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46228.99305555555</v>
+        <v>46228.77361111111</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46232.8875</v>
+        <v>46229.39097222222</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1594,10 +1598,10 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" s="1" t="n">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1610,191 +1614,191 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 5</t>
+          <t>ALS CLIVIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9326079</t>
+          <t>9969405</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>46228.77361111111</v>
+        <v>46220.66666666666</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46229.39097222222</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>46222.39166666667</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46220.25</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46220.25</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>46220.25</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>46221.25</v>
+      </c>
       <c r="O19" s="1" t="n">
-        <v>46229</v>
+        <v>46221.00069444445</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>46221.00069444445</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>46224.00069444445</v>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-15 23:57:00</t>
+          <t>2026-08-16 05:45:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALS CLIVIA</t>
+          <t>TIAN SHUN HE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9969405</t>
+          <t>9300312</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>2604S</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>2604N</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46220.66666666666</v>
+        <v>46221.00277777778</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46222.39166666667</v>
+        <v>46222.69583333333</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46215.73958333334</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>46215.73958333334</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>46215.73958333334</v>
-      </c>
+        <v>46216.91666666666</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" s="1" t="n">
-        <v>46220.25</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46220.25</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46220.25</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>46221.25</v>
-      </c>
+        <v>46218.91666666666</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" s="1" t="n">
-        <v>46221.00069444445</v>
+        <v>46222.25</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>46221.00069444445</v>
+        <v>46222.25</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46224.00069444445</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
+        <v>46226</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-16 05:45:03</t>
+          <t>2026-08-16 13:36:58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TIAN SHUN HE</t>
+          <t>HOEGH TRACER</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9300312</t>
+          <t>9684990</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2604S</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2604N</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>46221.00277777778</v>
+        <v>46229.77361111111</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46222.69583333333</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>46213.91666666666</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>46216.91666666666</v>
-      </c>
+        <v>46230.58333333334</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" s="1" t="n">
-        <v>46218.91666666666</v>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>46218.91666666666</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>46218.91666666666</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" s="1" t="n">
-        <v>46222.25</v>
+        <v>46231</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>46222.25</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46231</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-16 13:36:58</t>
+          <t>2026-08-16 23:57:13</t>
         </is>
       </c>
     </row>
@@ -1806,29 +1810,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOEGH TRACER</t>
+          <t>GRANDE CALIFORNIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9684990</t>
+          <t>9796377</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0226</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46229.77361111111</v>
+        <v>46229.3625</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46230.58333333334</v>
+        <v>46231.52222222222</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1838,10 +1842,10 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1854,50 +1858,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GRANDE CALIFORNIA</t>
+          <t>CONTI CRYSTAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9796377</t>
+          <t>9293820</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>627S</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0226</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>46229.3625</v>
+        <v>46227.00694444445</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46231.52222222222</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>46230.40625</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46221.25</v>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>46232</v>
-      </c>
+      <c r="J23" s="1" t="n">
+        <v>46221.25</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46225.91666666666</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>46225.91666666666</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>46227.33333333334</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>46228.625</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>BTH3</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>2026-08-16 23:57:13</t>
@@ -1907,184 +1923,188 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONTI CRYSTAL</t>
+          <t>MSC NASSAU IV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9293820</t>
+          <t>9471226</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>627S</t>
+          <t>FP624A</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>FP628R</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>46227.00694444445</v>
+        <v>46220.875</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46230.40625</v>
+        <v>46222.79166666666</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46221.25</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>46215.23958333334</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>46215.23958333334</v>
+      </c>
       <c r="J24" s="1" t="n">
-        <v>46221.25</v>
+        <v>46215.23958333334</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46225.91666666666</v>
+        <v>46219.75</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46225.91666666666</v>
+        <v>46219.75</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46227.33333333334</v>
+        <v>46219.75</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>46228.625</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>BTH3</t>
-        </is>
-      </c>
+        <v>46220.75</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>46221.00069444445</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>46221.00069444445</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>46224.00069444445</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-16 23:57:13</t>
+          <t>2026-08-17 05:42:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MSC NASSAU IV</t>
+          <t>VIKING OCEAN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9471226</t>
+          <t>9514999</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FP624A</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FP628R</t>
+          <t>030</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>46220.875</v>
+        <v>46230.54097222222</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46222.79166666666</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>46215.23958333334</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>46215.23958333334</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>46215.23958333334</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>46219.75</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>46219.75</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>46219.75</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>46220.75</v>
-      </c>
+        <v>46231.89444444444</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>46221.00069444445</v>
+        <v>46231</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46221.00069444445</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>46224.00069444445</v>
-      </c>
+        <v>46231</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-17 05:42:35</t>
+          <t>2026-08-18 00:06:12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VIKING OCEAN</t>
+          <t>FOS EXPRESS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9514999</t>
+          <t>9348699</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>2624S</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>628N</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>46230.54097222222</v>
+        <v>46222.81111111111</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46231.89444444444</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+        <v>46223.99236111111</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46216.91666666666</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>46218.91666666666</v>
+      </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="K26" s="1" t="n">
+        <v>46220.91666666666</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>46220.91666666666</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>46220.91666666666</v>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" s="1" t="n">
-        <v>46231</v>
+        <v>46223.91666666666</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+        <v>46223.91666666666</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>2026-08-18 00:06:12</t>
@@ -2094,69 +2114,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FOS EXPRESS</t>
+          <t>MSC SHAHAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9348699</t>
+          <t>9471238</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2624S</t>
+          <t>KN625A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>628N</t>
+          <t>KN628R</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>46222.81111111111</v>
+        <v>46222.49166666667</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46223.99236111111</v>
+        <v>46223.82916666667</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46216.91666666666</v>
+        <v>46217.23958333334</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46218.91666666666</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>46217.23958333334</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>46217.23958333334</v>
+      </c>
       <c r="K27" s="1" t="n">
-        <v>46220.91666666666</v>
+        <v>46221.75</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46220.91666666666</v>
+        <v>46221.75</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46220.91666666666</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>46221.75</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>46221.75</v>
+      </c>
       <c r="O27" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46223.00069444445</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46223.00069444445</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46226.00069444445</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-18 00:06:12</t>
+          <t>2026-08-18 05:55:58</t>
         </is>
       </c>
     </row>
@@ -2168,50 +2188,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MSC SHAHAR</t>
+          <t>NAVIOS INDIGO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9471238</t>
+          <t>9324875</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KN625A</t>
+          <t>34S</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KN628R</t>
+          <t>34N</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>46222.49166666667</v>
+        <v>46222.97083333333</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46223.82916666667</v>
+        <v>46224.25833333333</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46217.23958333334</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>46217.23958333334</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>46217.23958333334</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46221.75</v>
+        <v>46220.75</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46221.75</v>
+        <v>46220.75</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46221.75</v>
+        <v>46220.75</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>46221.75</v>
+        <v>46221.66666666666</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>46223.00069444445</v>
@@ -2232,69 +2252,53 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAVIOS INDIGO</t>
+          <t>GRACEFUL LEADER</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9324875</t>
+          <t>9357303</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34S</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34N</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46222.97083333333</v>
+        <v>46231.72847222222</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46224.25833333333</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>46216.23958333334</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>46216.23958333334</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>46216.23958333334</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>46220.75</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>46220.75</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>46220.75</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>46221.66666666666</v>
-      </c>
+        <v>46233.06736111111</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" s="1" t="n">
-        <v>46223.00069444445</v>
+        <v>46233</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46223.00069444445</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>46226.00069444445</v>
-      </c>
+        <v>46233</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-18 05:55:58</t>
+          <t>2026-08-18 18:19:48</t>
         </is>
       </c>
     </row>
@@ -2306,29 +2310,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GRACEFUL LEADER</t>
+          <t>MORNING MARGARETA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9357303</t>
+          <t>9367580</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>OK631</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>46231.72847222222</v>
+        <v>46231.97916666666</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46233.06736111111</v>
+        <v>46233.6875</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2359,29 +2363,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MORNING MARGARETA</t>
+          <t>NABUCCO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9367580</t>
+          <t>9731652</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OK631</t>
+          <t>EE610</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>46231.97916666666</v>
+        <v>46231.37013888889</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46233.6875</v>
+        <v>46232.62847222222</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2407,168 +2411,184 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NABUCCO</t>
+          <t>OOCL DURBAN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9731652</t>
+          <t>9567673</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>041S</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EE610</t>
+          <t>041N</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>46231.37013888889</v>
+        <v>46223.95833333334</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46232.62847222222</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+        <v>46225.43333333333</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46218.23958333334</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>46218.23958333334</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>46218.23958333334</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46222.75</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>46222.75</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>46222.75</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>46223.75</v>
+      </c>
       <c r="O32" s="1" t="n">
-        <v>46233</v>
+        <v>46224.00069444445</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>46224.00069444445</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>46227.00069444445</v>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-18 18:19:48</t>
+          <t>2026-08-19 05:52:50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OOCL DURBAN</t>
+          <t>NIAGARA HIGHWAY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9567673</t>
+          <t>9832638</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>041S</t>
+          <t>063</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>041N</t>
+          <t>063</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>46223.95833333334</v>
+        <v>46232.35972222222</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46225.43333333333</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>46218.23958333334</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>46218.23958333334</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>46218.23958333334</v>
-      </c>
-      <c r="K33" s="1" t="n">
-        <v>46222.75</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>46222.75</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>46222.75</v>
-      </c>
-      <c r="N33" s="1" t="n">
-        <v>46223.75</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>46224.00069444445</v>
-      </c>
-      <c r="P33" s="1" t="n">
-        <v>46224.00069444445</v>
-      </c>
-      <c r="Q33" s="1" t="n">
-        <v>46227.00069444445</v>
-      </c>
+        <v>46286.5</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-19 05:52:50</t>
+          <t>2026-08-19 19:06:59</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NIAGARA HIGHWAY</t>
+          <t>TS BANGKOK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9832638</t>
+          <t>9784233</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>46232.35972222222</v>
+        <v>46224.87291666667</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46286.5</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+        <v>46225.83958333333</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>46219.25</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>46221.91666666666</v>
+      </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="K34" s="1" t="n">
+        <v>46223.91666666666</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>46223.91666666666</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>46223.91666666666</v>
+      </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="O34" s="1" t="n">
+        <v>46225.58333333334</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>46225.58333333334</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>2026-08-19 19:06:59</t>
@@ -2583,130 +2603,130 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TS BANGKOK</t>
+          <t>SAN GIORGIO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9784233</t>
+          <t>9625918</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>46224.87291666667</v>
+        <v>46225.58333333334</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46225.83958333333</v>
+        <v>46226.28055555555</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46219.25</v>
+        <v>46220.25</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46221.91666666666</v>
+        <v>46223.25</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46225.25</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46225.25</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46223.91666666666</v>
+        <v>46225.25</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" s="1" t="n">
-        <v>46225.58333333334</v>
+        <v>46226.25</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46225.58333333334</v>
+        <v>46226.25</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-19 19:06:59</t>
+          <t>2026-08-20 01:29:58</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN GIORGIO</t>
+          <t>MSC MARITINA V</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9625918</t>
+          <t>9294408</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>FE630A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>FE630A</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46225.58333333334</v>
+        <v>46224.725</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46226.28055555555</v>
+        <v>46225.95416666667</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46220.25</v>
+        <v>46220.23958333334</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46223.25</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>46220.23958333334</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>46220.23958333334</v>
+      </c>
       <c r="K36" s="1" t="n">
-        <v>46225.25</v>
+        <v>46224.75</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46225.25</v>
+        <v>46224.75</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46225.25</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>46224.75</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>46224.75</v>
+      </c>
       <c r="O36" s="1" t="n">
-        <v>46226.25</v>
+        <v>46225.00069444445</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>46226.25</v>
+        <v>46225.00069444445</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46228.00069444445</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>2026-08-20 01:29:58</t>
@@ -2716,69 +2736,53 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MSC MARITINA V</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9294408</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FE630A</t>
+          <t>043</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FE630A</t>
+          <t>043</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46224.725</v>
+        <v>46233.04861111111</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46225.95416666667</v>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="I37" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="J37" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>46224.75</v>
-      </c>
+        <v>46233.9375</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" s="1" t="n">
-        <v>46225.00069444445</v>
+        <v>46234</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46225.00069444445</v>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>46228.00069444445</v>
-      </c>
+        <v>46234</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-20 01:29:58</t>
+          <t>2026-08-20 19:06:12</t>
         </is>
       </c>
     </row>
@@ -2790,29 +2794,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>DUDD</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46233.04861111111</v>
+        <v>46233.52152777778</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46233.9375</v>
+        <v>46286.25</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2821,12 +2825,8 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -2843,29 +2843,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>PROGRESS ACE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9267687</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DUDD</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46233.52152777778</v>
+        <v>46233.84722222222</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46286.25</v>
+        <v>46235.63472222222</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2874,8 +2874,12 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="O39" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
@@ -2887,50 +2891,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PROGRESS ACE</t>
+          <t>TAKUTAI CHIEF</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9267687</t>
+          <t>9519327</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46233.84722222222</v>
+        <v>46235.33055555556</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46235.63472222222</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>46235.89305555556</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46230.25</v>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>46236</v>
-      </c>
+      <c r="J40" s="1" t="n">
+        <v>46230.25</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>46234.58333333334</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>46234.58333333334</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>46235.5</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>46234.58333333334</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>BTH1</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>2026-08-20 19:06:12</t>
@@ -2945,55 +2961,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TAKUTAI CHIEF</t>
+          <t>COSCO PHILIPPINES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9519327</t>
+          <t>9448762</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>628S</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2617N</t>
+          <t>631N</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46235.33055555556</v>
+        <v>46232.93055555555</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46235.89305555556</v>
+        <v>46235.21180555555</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46230.25</v>
+        <v>46227.25</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" s="1" t="n">
-        <v>46230.25</v>
+        <v>46227.25</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46234.58333333334</v>
+        <v>46231.58333333334</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46234.58333333334</v>
+        <v>46231.58333333334</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>46235.5</v>
+        <v>46232.625</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>46234.58333333334</v>
+        <v>46233.625</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>BTH1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3010,55 +3026,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COSCO PHILIPPINES</t>
+          <t>KOTA LAWA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9448762</t>
+          <t>9439709</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>628S</t>
+          <t>109S</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>631N</t>
+          <t>109N</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46232.93055555555</v>
+        <v>46231.63333333333</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46235.21180555555</v>
+        <v>46232.47708333333</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46227.25</v>
+        <v>46226.25</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" s="1" t="n">
-        <v>46227.25</v>
+        <v>46226.25</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46231.58333333334</v>
+        <v>46230.58333333334</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46231.58333333334</v>
+        <v>46230.58333333334</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>46232.625</v>
+        <v>46231.45833333334</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>46233.625</v>
+        <v>46230.58333333334</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3070,65 +3086,69 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KOTA LAWA</t>
+          <t>PRIDE C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9439709</t>
+          <t>9978640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>109S</t>
+          <t>029W</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>109N</t>
+          <t>029E</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46231.63333333333</v>
+        <v>46226.05833333333</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46232.47708333333</v>
+        <v>46226.6875</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46226.25</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>46221.23958333334</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46221.23958333334</v>
+      </c>
       <c r="J43" s="1" t="n">
-        <v>46226.25</v>
+        <v>46221.23958333334</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46230.58333333334</v>
+        <v>46225.75</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46230.58333333334</v>
+        <v>46225.75</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>46231.45833333334</v>
+        <v>46225.75</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>46230.58333333334</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>BTH2</t>
-        </is>
-      </c>
+        <v>46225.75</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>46226.00069444445</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>46226.00069444445</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>46229.00069444445</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-20 19:06:12</t>
+          <t>2026-08-21 06:01:33</t>
         </is>
       </c>
     </row>
@@ -3140,47 +3160,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRIDE C</t>
+          <t>COSCO ISTANBUL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9978640</t>
+          <t>9484340</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>029W</t>
+          <t>093S</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>029E</t>
+          <t>093N</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46226.05833333333</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46226.6875</v>
+        <v>46226.79166666666</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46221.23958333334</v>
+        <v>46219.73958333334</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>46221.23958333334</v>
+        <v>46219.73958333334</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>46221.23958333334</v>
+        <v>46219.73958333334</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46225.75</v>
+        <v>46224.5</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46225.75</v>
+        <v>46224.5</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>46225.75</v>
+        <v>46224.5</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>46225.75</v>
@@ -3204,69 +3224,53 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COSCO ISTANBUL</t>
+          <t>VIKING CARINA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9484340</t>
+          <t>9338709</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>093S</t>
+          <t>005</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>093N</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46225.54166666666</v>
+        <v>46234.07083333333</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46226.79166666666</v>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>46219.73958333334</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>46219.73958333334</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>46219.73958333334</v>
-      </c>
-      <c r="K45" s="1" t="n">
-        <v>46224.5</v>
-      </c>
-      <c r="L45" s="1" t="n">
-        <v>46224.5</v>
-      </c>
-      <c r="M45" s="1" t="n">
-        <v>46224.5</v>
-      </c>
-      <c r="N45" s="1" t="n">
-        <v>46225.75</v>
-      </c>
+        <v>46235.07847222222</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" s="1" t="n">
-        <v>46226.00069444445</v>
+        <v>46235</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>46226.00069444445</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>46229.00069444445</v>
-      </c>
+        <v>46235</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-21 06:01:33</t>
+          <t>2026-08-21 19:10:53</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3282,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VIKING CARINA</t>
+          <t>HOEGH LONDON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9338709</t>
+          <t>9342205</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46234.07083333333</v>
+        <v>46234.38055555556</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46235.07847222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -3309,12 +3313,8 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
@@ -3331,26 +3331,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HOEGH LONDON</t>
+          <t>ANDROMEDA SPIRIT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9342205</t>
+          <t>9372327</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46234.38055555556</v>
+        <v>46234.42847222222</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>46339.2625</v>
@@ -3380,29 +3380,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ANDROMEDA SPIRIT</t>
+          <t>HOEGH MOONLIGHT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9372327</t>
+          <t>9971252</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46234.42847222222</v>
+        <v>46234.38263888889</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -3429,29 +3429,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HOEGH MOONLIGHT</t>
+          <t>NEPTUNE BARCELONA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9971252</t>
+          <t>9762546</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46234.38263888889</v>
+        <v>46234.38194444445</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3478,29 +3478,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NEPTUNE BARCELONA</t>
+          <t>HOEGH TRAPPER</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9762546</t>
+          <t>9706918</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46234.38194444445</v>
+        <v>46234.38333333333</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -3522,46 +3522,66 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOEGH TRAPPER</t>
+          <t>TS SYDNEY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9706918</t>
+          <t>9477385</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2604S</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2604N</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46234.38333333333</v>
+        <v>46226.39166666667</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46363.2625</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+        <v>46227.82152777778</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46219.25</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>46222.25</v>
+      </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="K51" s="1" t="n">
+        <v>46224.25</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>46224.25</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>46224.25</v>
+      </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="O51" s="1" t="n">
+        <v>46227.58333333334</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>46227.58333333334</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>2026-08-21 19:10:53</t>
@@ -3571,69 +3591,49 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TS SYDNEY</t>
+          <t>MARTI CROWN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9477385</t>
+          <t>9626247</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2604S</t>
+          <t>062E</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2604N</t>
+          <t>062E</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46226.39166666667</v>
+        <v>46267.75</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46227.82152777778</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>46219.25</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>46222.25</v>
-      </c>
+        <v>46268.75</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" s="1" t="n">
-        <v>46224.25</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>46224.25</v>
-      </c>
-      <c r="M52" s="1" t="n">
-        <v>46224.25</v>
-      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" s="1" t="n">
-        <v>46227.58333333334</v>
-      </c>
-      <c r="P52" s="1" t="n">
-        <v>46227.58333333334</v>
-      </c>
-      <c r="Q52" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-21 19:10:53</t>
+          <t>2026-08-22 05:50:45</t>
         </is>
       </c>
     </row>
@@ -3645,40 +3645,60 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MARTI CROWN</t>
+          <t>MSC AUGUSTA III</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9626247</t>
+          <t>9303792</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>062E</t>
+          <t>KH630A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>062E</t>
+          <t>KH630A</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46267.75</v>
+        <v>46226.40833333333</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46268.75</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+        <v>46227.84583333333</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46220.23958333334</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46220.23958333334</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>46220.23958333334</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>46224.75</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>46224.75</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>46224.75</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>46226.25</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>46227.00069444445</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>46227.00069444445</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>46230.00069444445</v>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3689,241 +3709,237 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MSC AUGUSTA III</t>
+          <t>AAL SHANGHAI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9303792</t>
+          <t>9498377</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KH630A</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KH630A</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46226.40833333333</v>
+        <v>46235.60625</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46227.84583333333</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>46220.23958333334</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>46224.75</v>
-      </c>
-      <c r="N54" s="1" t="n">
-        <v>46226.25</v>
-      </c>
+        <v>46242.43472222222</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" s="1" t="n">
-        <v>46227.00069444445</v>
+        <v>46242</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46227.00069444445</v>
-      </c>
-      <c r="Q54" s="1" t="n">
-        <v>46230.00069444445</v>
-      </c>
+        <v>46242</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-22 05:50:45</t>
+          <t>2026-08-22 23:56:37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAL SHANGHAI</t>
+          <t>EVER SMART</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9498377</t>
+          <t>9300403</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0143S</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>0143N</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46235.60625</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46242.43472222222</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+        <v>46228.80833333333</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46222.23958333334</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>46222.23958333334</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>46222.23958333334</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>46226.75</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>46226.75</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <v>46226.75</v>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>46229.25</v>
+      </c>
       <c r="O55" s="1" t="n">
-        <v>46242</v>
+        <v>46227.00069444445</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+        <v>46227.00069444445</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>46230.00069444445</v>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-22 23:56:37</t>
+          <t>2026-08-23 05:48:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVER SMART</t>
+          <t>CHESAPEAKE HIGHWAY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9300403</t>
+          <t>9565546</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0143S</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0143N</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46226.91666666666</v>
+        <v>46236.03611111111</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46228.80833333333</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>46222.23958333334</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>46222.23958333334</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>46222.23958333334</v>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>46226.75</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>46226.75</v>
-      </c>
-      <c r="M56" s="1" t="n">
-        <v>46226.75</v>
-      </c>
-      <c r="N56" s="1" t="n">
-        <v>46229.25</v>
-      </c>
+        <v>46237.14305555556</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" s="1" t="n">
-        <v>46227.00069444445</v>
+        <v>46237</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46227.00069444445</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>46230.00069444445</v>
-      </c>
+        <v>46237</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-23 05:48:05</t>
+          <t>2026-08-23 23:58:19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CHESAPEAKE HIGHWAY</t>
+          <t>KOTA LUMAYAN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9565546</t>
+          <t>9494541</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>191S</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>191N</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46236.03611111111</v>
+        <v>46237.8125</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46237.14305555556</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>46239.125</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>46231.25</v>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>46237</v>
-      </c>
+      <c r="J57" s="1" t="n">
+        <v>46231.25</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>46235.58333333334</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>46235.58333333334</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>46237.58333333334</v>
+      </c>
+      <c r="N57" s="1" t="n">
+        <v>46238.25</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>BTH3</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>2026-08-23 23:58:19</t>
@@ -3938,55 +3954,53 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KOTA LUMAYAN</t>
+          <t>MAERSK FUKUOKA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9494541</t>
+          <t>9991147</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>191S</t>
+          <t>626S</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>191N</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46237.8125</v>
+        <v>46235.58125</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46239.125</v>
+        <v>46237.31597222222</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46231.25</v>
+        <v>46230.25</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" s="1" t="n">
-        <v>46231.25</v>
+        <v>46230.25</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46235.58333333334</v>
+        <v>46234.58333333334</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46235.58333333334</v>
-      </c>
-      <c r="M58" s="1" t="n">
-        <v>46237.58333333334</v>
-      </c>
+        <v>46234.58333333334</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" s="1" t="n">
-        <v>46238.25</v>
+        <v>46235.625</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>BTH2</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -3998,129 +4012,135 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MAERSK FUKUOKA</t>
+          <t>CMA CGM ORANGE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9991147</t>
+          <t>9690092</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>626S</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46235.58125</v>
+        <v>46229.65486111111</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46237.31597222222</v>
+        <v>46230.25</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46230.25</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" s="1" t="n">
-        <v>46230.25</v>
-      </c>
+        <v>46224.25</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46225.91666666666</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" s="1" t="n">
-        <v>46234.58333333334</v>
+        <v>46227.91666666666</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46234.58333333334</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" s="1" t="n">
-        <v>46235.625</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+        <v>46227.91666666666</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <v>46227.91666666666</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="1" t="n">
+        <v>46229.91666666666</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>46229.91666666666</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>BTH2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-23 23:58:19</t>
+          <t>2026-08-24 05:46:47</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CMA CGM ORANGE</t>
+          <t>MSC MARIA CLARA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9690092</t>
+          <t>9287900</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>KN626A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>KN629R</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46229.65486111111</v>
+        <v>46228.36666666667</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46230.25</v>
+        <v>46229.5</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46224.25</v>
+        <v>46224.23958333334</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46225.91666666666</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>46224.23958333334</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>46224.23958333334</v>
+      </c>
       <c r="K60" s="1" t="n">
-        <v>46227.91666666666</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46227.91666666666</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>46227.91666666666</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>46227.58333333334</v>
+      </c>
+      <c r="N60" s="1" t="n">
+        <v>46227.83333333334</v>
+      </c>
       <c r="O60" s="1" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.00069444445</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.00069444445</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+        <v>46232.04166666666</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>2026-08-24 05:46:47</t>
@@ -4130,66 +4150,66 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VICTORIA INTERNATIONAL CONTAINER TERMINAL LIMITED</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MSC MARIA CLARA</t>
+          <t>MAERSK INVERNESS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9287900</t>
+          <t>9348156</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KN626A</t>
+          <t>625S</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KN629R</t>
+          <t>630N</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46228.36666666667</v>
+        <v>46229.03472222222</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46229.5</v>
+        <v>46230.39652777778</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46224.23958333334</v>
+        <v>46222.91666666666</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>46224.23958333334</v>
-      </c>
-      <c r="J61" s="1" t="n">
-        <v>46224.23958333334</v>
-      </c>
+        <v>46224.91666666666</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" s="1" t="n">
-        <v>46227.58333333334</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>46227.58333333334</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>46227.58333333334</v>
-      </c>
-      <c r="N61" s="1" t="n">
-        <v>46227.83333333334</v>
-      </c>
+        <v>46226.91666666666</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" s="1" t="n">
-        <v>46229.00069444445</v>
+        <v>46230.25</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46229.00069444445</v>
+        <v>46230.25</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46232.04166666666</v>
-      </c>
-      <c r="R61" t="inlineStr"/>
+        <v>46233</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>2026-08-24 05:46:47</t>
@@ -4199,69 +4219,53 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>AAT WEST WEBB DOCK, MELBOURNE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MAERSK INVERNESS</t>
+          <t>VIKING PASSAMA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9348156</t>
+          <t>9491874</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>625S</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>630N</t>
+          <t>OO630</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46229.03472222222</v>
+        <v>46237.22222222222</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46230.39652777778</v>
-      </c>
-      <c r="H62" s="1" t="n">
-        <v>46222.91666666666</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>46224.91666666666</v>
-      </c>
+        <v>46239.07847222222</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" s="1" t="n">
-        <v>46226.91666666666</v>
-      </c>
-      <c r="L62" s="1" t="n">
-        <v>46226.91666666666</v>
-      </c>
-      <c r="M62" s="1" t="n">
-        <v>46226.91666666666</v>
-      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" s="1" t="n">
-        <v>46230.25</v>
+        <v>46238</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46230.25</v>
-      </c>
-      <c r="Q62" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>46238</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-24 05:46:47</t>
+          <t>2026-08-24 19:32:46</t>
         </is>
       </c>
     </row>
@@ -4273,29 +4277,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIKING PASSAMA</t>
+          <t>KARIYUSHI LEADER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9491874</t>
+          <t>9403217</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OO630</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46237.22222222222</v>
+        <v>46237.34236111111</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46239.07847222222</v>
+        <v>46286.2625</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4304,12 +4308,8 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>46238</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
@@ -4326,29 +4326,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KARIYUSHI LEADER</t>
+          <t>PLUTO LEADER</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>9403217</t>
+          <t>9338890</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>070</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46237.34236111111</v>
+        <v>46237.35416666666</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4375,29 +4375,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PLUTO LEADER</t>
+          <t>POSITIVE LEADER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9338890</t>
+          <t>9340776</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46237.35416666666</v>
+        <v>46237.34375</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46286.2625</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4424,29 +4424,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>POSITIVE LEADER</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9340776</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46237.34375</v>
+        <v>46245.31875</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46286.2625</v>
+        <v>46363.2625</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-24 19:32:46</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4473,29 +4473,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>CANOPUS LEADER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9367607</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46252.27569444444</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46254.31736111111</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4505,16 +4505,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4526,29 +4526,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PATARA</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>9491898</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46245.31875</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46339.2625</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4563,7 +4563,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4575,29 +4575,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46242.5125</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46243.0625</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4606,13 +4606,17 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4624,29 +4628,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VIKING PAGLIA</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9427940</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OO632</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46243.17916666667</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46247.78958333333</v>
+        <v>46242.26875</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4656,16 +4660,16 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4677,29 +4681,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CANOPUS LEADER</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9367607</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46252.27569444444</v>
+        <v>46257.43541666667</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46254.31736111111</v>
+        <v>46258.17152777778</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4709,16 +4713,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4730,29 +4734,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>MARVELOUS ACE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9293519</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46254.41805555556</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46255.32291666666</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4762,16 +4766,16 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4783,29 +4787,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4815,16 +4819,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4836,29 +4840,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46256.66180555556</v>
+        <v>46281.25</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4867,17 +4871,13 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="P74" s="1" t="n">
-        <v>46257</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4889,29 +4889,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4920,17 +4920,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4942,29 +4938,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GENIUS HIGHWAY</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9672416</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46243.17430555556</v>
+        <v>46245.29375</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46245.66388888889</v>
+        <v>46363.2625</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4973,17 +4969,13 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -4995,29 +4987,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46281.25</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -5026,13 +5018,17 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="O77" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5040,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46257.43541666667</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46258.17152777778</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -5076,16 +5072,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" s="1" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5097,29 +5093,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 7</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9326093</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46242.5125</v>
+        <v>46255.91666666666</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46243.0625</v>
+        <v>46256.66180555556</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5129,16 +5125,16 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" s="1" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5150,29 +5146,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BALTIMORE HIGHWAY</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9510149</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46240.13541666666</v>
+        <v>46243.01875</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46241.32916666667</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5182,16 +5178,16 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5203,29 +5199,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46339.2625</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -5234,17 +5230,13 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5256,29 +5248,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46288.25</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -5287,13 +5279,17 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="O82" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>46248</v>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5305,29 +5301,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UNDINE</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9240160</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EE611</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EE611</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46254.78125</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46256.17152777778</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -5337,16 +5333,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" s="1" t="n">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5358,29 +5354,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>RCC PASSION</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9453107</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>008</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>008</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46245.31666666667</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46339.2625</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -5389,17 +5385,13 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P84" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5411,29 +5403,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>BALTIMORE HIGHWAY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9510149</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46240.13541666666</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46241.32916666667</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -5443,16 +5435,16 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" s="1" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5464,29 +5456,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MARVELOUS ACE</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9293519</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F86" s="1" t="n">
-        <v>46254.41805555556</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46255.32291666666</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -5496,16 +5488,16 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" s="1" t="n">
-        <v>46255</v>
+        <v>46243</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46255</v>
+        <v>46243</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5517,29 +5509,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>GRAND VENUS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9303211</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>040</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>040</t>
         </is>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46256.36944444444</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46259.12013888889</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -5548,13 +5540,17 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="O87" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="P87" s="1" t="n">
+        <v>46259</v>
+      </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5566,29 +5562,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>TOREADOR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9375288</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>OO634</t>
         </is>
       </c>
       <c r="F88" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46240.33125</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46339.2625</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5597,17 +5593,13 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P88" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5619,29 +5611,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>MARGUERITE ACE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9426386</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F89" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46254.05694444444</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46254.62638888889</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5650,13 +5642,17 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="O89" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="P89" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5668,29 +5664,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F90" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46253.44375</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46288.25</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5699,17 +5695,13 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="P90" s="1" t="n">
-        <v>46242</v>
-      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5721,29 +5713,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ASTERIA LEADER</t>
+          <t>LORD VISHNU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9531741</t>
+          <t>9367578</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F91" s="1" t="n">
-        <v>46245.29375</v>
+        <v>46249.46041666667</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46363.2625</v>
+        <v>46250.32569444444</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -5752,13 +5744,17 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="O91" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P91" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5770,29 +5766,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TOREADOR</t>
+          <t>VIKING PAGLIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9375288</t>
+          <t>9427940</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OO634</t>
+          <t>OO632</t>
         </is>
       </c>
       <c r="F92" s="1" t="n">
-        <v>46240.33125</v>
+        <v>46243.17916666667</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.78958333333</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -5801,13 +5797,17 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+      <c r="O92" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P92" s="1" t="n">
+        <v>46248</v>
+      </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5819,29 +5819,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>UNDINE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9240160</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EE611</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EE611</t>
         </is>
       </c>
       <c r="F93" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46254.78125</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46256.17152777778</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -5851,16 +5851,16 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5872,29 +5872,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>DREAM ORCHID</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9360568</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>006</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F94" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46245.84027777778</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46247.03819444445</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -5903,13 +5903,17 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="O94" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5959,7 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6007,7 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6052,7 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6097,7 @@
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6142,7 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6187,7 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6232,7 @@
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6277,7 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6322,7 @@
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6367,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6412,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6457,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6502,7 @@
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6547,7 @@
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6592,7 @@
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6637,7 @@
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6682,7 @@
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6727,7 @@
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6772,7 @@
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6817,7 @@
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6862,7 @@
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6907,7 @@
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6952,7 @@
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6997,7 @@
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7042,7 @@
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7087,7 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7132,7 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7177,7 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7222,7 @@
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7267,7 @@
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7312,7 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7361,7 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7408,7 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7455,7 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7502,7 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7549,7 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7596,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7643,7 @@
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7690,7 @@
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7737,7 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7784,7 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7831,7 @@
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7878,7 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7925,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7972,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8019,7 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8066,7 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8113,7 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8160,7 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8205,7 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8254,7 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8305,7 @@
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8354,7 @@
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8409,7 @@
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8454,7 @@
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8499,7 @@
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8548,7 @@
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8603,7 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8648,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8693,7 @@
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8738,7 @@
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8783,7 @@
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8832,7 @@
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8877,7 @@
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8918,7 @@
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8967,7 @@
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9012,7 @@
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9061,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9110,7 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9155,7 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9200,7 @@
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9245,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9290,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9335,7 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9392,7 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9437,7 @@
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9445,29 +9449,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NORDPACIFIC</t>
+          <t>ALS HERCULES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>9802487</t>
+          <t>9948633</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>009S</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>009N</t>
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46271.02083333334</v>
+        <v>46266.75</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>46271.58333333334</v>
+        <v>46267.33333333334</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
@@ -9481,12 +9485,12 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9498,29 +9502,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ALS LUNA</t>
+          <t>OOCL KUALA LUMPUR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9969390</t>
+          <t>9367176</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>008S</t>
+          <t>192S</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>008N</t>
+          <t>192N</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46257.25</v>
+        <v>46272.41666666666</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>46257.52083333334</v>
+        <v>46274.125</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -9534,12 +9538,12 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9551,29 +9555,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MAERSK BUTON</t>
+          <t>COSCO SINGAPORE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9392925</t>
+          <t>9221102</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>202S</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>636N</t>
+          <t>202N</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46269.58333333334</v>
+        <v>46272.08333333334</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>46270.91666666666</v>
+        <v>46273.41666666666</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -9592,7 +9596,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9604,29 +9608,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OOCL KUALA LUMPUR</t>
+          <t>NORDPACIFIC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9367176</t>
+          <t>9802487</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>192S</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>192N</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46272.41666666666</v>
+        <v>46271.02083333334</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>46274.125</v>
+        <v>46271.58333333334</v>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -9640,12 +9644,12 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9657,30 +9661,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TS MUNDRA</t>
+          <t>LONG BEACH EXPRESS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9953834</t>
+          <t>9348675</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2605S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2605N</t>
+          <t>636N</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46272.91666666666</v>
-      </c>
-      <c r="G175" s="1" t="n">
-        <v>46274.25</v>
-      </c>
+        <v>46272.58333333334</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
@@ -9691,14 +9693,10 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9708,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LONG BEACH EXPRESS</t>
+          <t>MAERSK BUTON</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9348675</t>
+          <t>9392925</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9729,9 +9727,11 @@
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46272.58333333334</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
+        <v>46269.58333333334</v>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>46270.91666666666</v>
+      </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
@@ -9742,10 +9742,14 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9757,29 +9761,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ALS HERCULES</t>
+          <t>ITAL UNICA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9948633</t>
+          <t>9196981</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>009S</t>
+          <t>193S</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>009N</t>
+          <t>193N</t>
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46266.75</v>
+        <v>46270.25</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>46267.33333333334</v>
+        <v>46272.25</v>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
@@ -9793,12 +9797,12 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9810,29 +9814,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ITAL UNICA</t>
+          <t>ALS LUNA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>9196981</t>
+          <t>9969390</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>193S</t>
+          <t>008S</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>193N</t>
+          <t>008N</t>
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46270.25</v>
+        <v>46257.25</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46272.25</v>
+        <v>46257.52083333334</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
@@ -9846,12 +9850,12 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9863,29 +9867,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>COSCO SINGAPORE</t>
+          <t>TS MUNDRA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>9221102</t>
+          <t>9953834</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>202S</t>
+          <t>2605S</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>202N</t>
+          <t>2605N</t>
         </is>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46272.08333333334</v>
+        <v>46272.91666666666</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>46273.41666666666</v>
+        <v>46274.25</v>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -9899,12 +9903,12 @@
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -9916,29 +9920,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ELEGANT SW</t>
+          <t>ANDREAS VIKING</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>9450167</t>
+          <t>9631747</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2601S</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="F180" s="1" t="n">
-        <v>46269.25</v>
+        <v>46241.7875</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>46271.25</v>
+        <v>46241.91666666666</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
@@ -9953,7 +9957,7 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10006,7 @@
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10014,29 +10018,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ANDREAS VIKING</t>
+          <t>DYNAMOGRACHT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>9631747</t>
+          <t>9420849</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46241.7875</v>
+        <v>46275.25</v>
       </c>
       <c r="G182" s="1" t="n">
-        <v>46241.91666666666</v>
+        <v>46277.25</v>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -10051,7 +10055,7 @@
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10063,29 +10067,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DYNAMOGRACHT</t>
+          <t>ELEGANT SW</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>9420849</t>
+          <t>9450167</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2601S</t>
         </is>
       </c>
       <c r="F183" s="1" t="n">
-        <v>46275.25</v>
+        <v>46269.25</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>46277.25</v>
+        <v>46271.25</v>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
@@ -10100,7 +10104,7 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10153,7 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10202,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10255,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10308,7 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10361,7 @@
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10426,7 @@
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10485,7 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10544,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10603,7 @@
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10662,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10717,7 +10721,7 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10733,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SLS MT POOL</t>
+          <t>PIL EMPTY POOL</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>1000042</t>
+          <t>1100001</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10748,17 +10752,17 @@
         </is>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46386.25</v>
+        <v>46204.25</v>
       </c>
       <c r="G195" s="1" t="n">
         <v>46387.99930555555</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>46104.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" s="1" t="n">
-        <v>46284.25</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" s="1" t="n">
@@ -10774,7 +10778,7 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10786,12 +10790,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PIL EMPTY POOL</t>
+          <t>HLC EMPTY POOL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1100001</t>
+          <t>1000007</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10805,17 +10809,17 @@
         </is>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46204.25</v>
+        <v>46356.25</v>
       </c>
       <c r="G196" s="1" t="n">
-        <v>46387.99930555555</v>
+        <v>46387.25</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46268</v>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" s="1" t="n">
-        <v>46285.58333333334</v>
+        <v>46268</v>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" s="1" t="n">
@@ -10831,7 +10835,7 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10843,12 +10847,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HLC EMPTY POOL</t>
+          <t>SLS MT POOL</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1000007</t>
+          <t>1000042</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10862,17 +10866,17 @@
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46356.25</v>
+        <v>46386.25</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>46387.25</v>
+        <v>46387.99930555555</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>46268</v>
+        <v>46104.25</v>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" s="1" t="n">
-        <v>46268</v>
+        <v>46284.25</v>
       </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" s="1" t="n">
@@ -10888,7 +10892,7 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10949,7 @@
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11006,7 @@
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11065,7 @@
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11120,7 +11124,7 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11187,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11250,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11313,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11382,7 @@
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11445,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11508,7 @@
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11571,7 @@
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11634,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11697,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11760,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11829,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11898,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -11957,7 +11961,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12020,29 +12024,29 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PATRICK, VI, EAST SWANSON</t>
+          <t>DP WORLD, VI, WEST SWANSON</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ALS KRONOS</t>
+          <t>OLIVIA MAERSK</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>9327786</t>
+          <t>9251638</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>631S</t>
+          <t>630S</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12051,61 +12055,67 @@
         </is>
       </c>
       <c r="F216" s="1" t="n">
-        <v>46262.91666666666</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="G216" s="1" t="n">
-        <v>46264.58333333334</v>
+        <v>46263.8125</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" s="1" t="n">
-        <v>46257.58333333334</v>
-      </c>
+        <v>46257.91666666666</v>
+      </c>
+      <c r="I216" s="1" t="n">
+        <v>46259.91666666666</v>
+      </c>
+      <c r="J216" t="inlineStr"/>
       <c r="K216" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L216" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" s="1" t="n">
+      <c r="M216" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="P216" s="1" t="n">
+        <v>46264.25</v>
+      </c>
+      <c r="Q216" s="1" t="n">
+        <v>46268</v>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>BTH3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DP WORLD, VI, WEST SWANSON</t>
+          <t>PATRICK, VI, EAST SWANSON</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OLIVIA MAERSK</t>
+          <t>ALS KRONOS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>9251638</t>
+          <t>9327786</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>630S</t>
+          <t>631S</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12114,45 +12124,39 @@
         </is>
       </c>
       <c r="F217" s="1" t="n">
-        <v>46262.58333333334</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="G217" s="1" t="n">
-        <v>46263.8125</v>
+        <v>46264.58333333334</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46257.91666666666</v>
-      </c>
-      <c r="I217" s="1" t="n">
-        <v>46259.91666666666</v>
-      </c>
-      <c r="J217" t="inlineStr"/>
+        <v>46257.58333333334</v>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" s="1" t="n">
+        <v>46257.58333333334</v>
+      </c>
       <c r="K217" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
       <c r="L217" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="M217" s="1" t="n">
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" s="1" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="P217" s="1" t="n">
-        <v>46264.25</v>
-      </c>
-      <c r="Q217" s="1" t="n">
-        <v>46268</v>
-      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BTH3</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12225,7 @@
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12288,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12357,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12426,7 @@
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12489,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12558,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12627,7 @@
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12690,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12759,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12820,7 +12824,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12855,7 @@
         </is>
       </c>
       <c r="F228" s="1" t="n">
-        <v>46258.99930555555</v>
+        <v>46259.125</v>
       </c>
       <c r="G228" s="1" t="n">
         <v>46259.95833333334</v>
@@ -12889,7 +12893,7 @@
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12962,7 @@
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13031,7 @@
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13100,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13169,7 @@
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13238,7 @@
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13307,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13376,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13445,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13510,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13571,7 +13575,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13644,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13713,7 @@
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13778,7 +13782,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13851,7 @@
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13920,7 @@
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -13981,7 +13985,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14048,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14117,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14182,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14251,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14320,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14389,7 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14458,7 @@
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14527,7 @@
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14592,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14653,7 +14657,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14726,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14795,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14864,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14933,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14998,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15063,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15132,7 @@
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15201,7 @@
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15270,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15339,7 @@
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15408,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15473,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15542,7 @@
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15607,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15676,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15745,7 @@
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15814,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15883,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15952,7 @@
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16021,7 @@
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16090,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16159,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16224,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16293,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16358,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16423,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16492,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16557,7 +16561,7 @@
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16630,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16699,7 @@
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16764,7 +16768,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16837,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16906,7 @@
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -16971,7 +16975,7 @@
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17042,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17107,7 +17111,7 @@
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17176,7 +17180,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17245,7 +17249,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17314,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17383,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17452,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17517,7 +17521,7 @@
       <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17590,7 @@
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17659,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17728,7 @@
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17793,7 +17797,7 @@
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17866,7 @@
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17935,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18004,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18069,7 +18073,7 @@
       <c r="R304" t="inlineStr"/>
       <c r="S304" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18142,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18207,7 +18211,7 @@
       <c r="R306" t="inlineStr"/>
       <c r="S306" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18280,7 @@
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18349,7 @@
       <c r="R308" t="inlineStr"/>
       <c r="S308" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18418,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18487,7 @@
       <c r="R310" t="inlineStr"/>
       <c r="S310" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18556,7 @@
       <c r="R311" t="inlineStr"/>
       <c r="S311" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18625,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18690,7 @@
       <c r="R313" t="inlineStr"/>
       <c r="S313" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18755,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18820,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18879,7 @@
       <c r="R316" t="inlineStr"/>
       <c r="S316" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18944,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19009,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19074,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19135,7 +19139,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19200,7 +19204,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19267,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19332,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19397,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19462,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19527,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19588,7 +19592,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19653,7 +19657,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19722,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19783,7 +19787,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19852,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19917,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -19978,7 +19982,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20047,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20104,7 +20108,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20169,7 +20173,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20238,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20305,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20372,7 +20376,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20447,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20518,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20589,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20648,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20719,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20790,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20861,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20930,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -20997,7 +21001,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21070,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21133,7 +21137,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21208,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21275,7 +21279,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21346,7 +21350,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21413,7 @@
       <c r="R354" t="inlineStr"/>
       <c r="S354" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21480,7 +21484,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21549,7 +21553,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21612,7 @@
       <c r="R357" t="inlineStr"/>
       <c r="S357" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21667,7 +21671,7 @@
       <c r="R358" t="inlineStr"/>
       <c r="S358" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21726,7 +21730,7 @@
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21785,7 +21789,7 @@
       <c r="R360" t="inlineStr"/>
       <c r="S360" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21844,7 +21848,7 @@
       <c r="R361" t="inlineStr"/>
       <c r="S361" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21907,7 @@
       <c r="R362" t="inlineStr"/>
       <c r="S362" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>
@@ -21962,7 +21966,7 @@
       <c r="R363" t="inlineStr"/>
       <c r="S363" t="inlineStr">
         <is>
-          <t>2026-08-25 01:21:49</t>
+          <t>2026-08-25 06:01:00</t>
         </is>
       </c>
     </row>

--- a/Gateway_Vessel_Schedule.xlsx
+++ b/Gateway_Vessel_Schedule.xlsx
@@ -4672,7 +4672,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4684,29 +4684,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COMET ACE</t>
+          <t>KANG QIAN KOU</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9182356</t>
+          <t>9990284</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>002</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46245.31458333333</v>
+        <v>46241.29861111111</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46242.26875</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4715,13 +4715,17 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="O70" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4733,29 +4737,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LORD VISHNU</t>
+          <t>MAO HONG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9367578</t>
+          <t>9903217</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46249.46041666667</v>
+        <v>46255.91666666666</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46250.32569444444</v>
+        <v>46256.66180555556</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4765,16 +4769,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4786,29 +4790,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRANQUIL ACE</t>
+          <t>GLOVIS COUNTESS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9561253</t>
+          <t>9476721</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>035</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>035</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46261.57152777778</v>
+        <v>46250.84722222222</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46281.25</v>
+        <v>46251.95277777778</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4817,13 +4821,17 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="O72" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4835,29 +4843,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MARGUERITE ACE</t>
+          <t>NEPTUNE ACE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9426386</t>
+          <t>9584059</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46254.05694444444</v>
+        <v>46253.44375</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46254.62638888889</v>
+        <v>46288.25</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4866,17 +4874,13 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="P73" s="1" t="n">
-        <v>46255</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4888,29 +4892,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GRANDE NAPOLI</t>
+          <t>AAL HONG KONG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9247924</t>
+          <t>9498468</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0626</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46247.10416666666</v>
+        <v>46245.52152777778</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46248.94722222222</v>
+        <v>46339.2625</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4919,17 +4923,13 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="P74" s="1" t="n">
-        <v>46248</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4941,29 +4941,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HEROIC LEADER</t>
+          <t>GENIUS HIGHWAY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9441570</t>
+          <t>9672416</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>087</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>087</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46253.04513888889</v>
+        <v>46243.17430555556</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46254.07986111111</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4973,16 +4973,16 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" s="1" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -4994,29 +4994,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GRAND VENUS</t>
+          <t>GRANDE NAPOLI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9303211</t>
+          <t>9247924</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>0626</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46256.36944444444</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46259.12013888889</v>
+        <v>46248.94722222222</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -5026,16 +5026,16 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" s="1" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5047,29 +5047,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PALMELA</t>
+          <t>TALISMAN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9207388</t>
+          <t>9191319</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>EF611</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46248.85069444445</v>
+        <v>46243.01875</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46249.63333333333</v>
+        <v>46247.45208333333</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -5079,16 +5079,16 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" s="1" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5100,29 +5100,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NEPTUNE ACE</t>
+          <t>PALMELA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9584059</t>
+          <t>9207388</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46253.44375</v>
+        <v>46248.85069444445</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46288.25</v>
+        <v>46249.63333333333</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -5131,13 +5131,17 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="O78" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5149,29 +5153,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SWIFT ACE</t>
+          <t>TRANQUIL ACE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9338838</t>
+          <t>9561253</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46242.32916666667</v>
+        <v>46261.57152777778</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46243.04027777778</v>
+        <v>46281.25</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -5180,17 +5184,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="P79" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5202,29 +5202,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GLOVIS COUNTESS</t>
+          <t>ASTERIA LEADER</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9476721</t>
+          <t>9531741</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>044</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>044</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46250.84722222222</v>
+        <v>46245.29375</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46251.95277777778</v>
+        <v>46363.2625</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -5233,17 +5233,13 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="P80" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5255,29 +5251,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAO HONG</t>
+          <t>UNDINE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9903217</t>
+          <t>9240160</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>EE611</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>EE611</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46255.91666666666</v>
+        <v>46254.78125</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46256.66180555556</v>
+        <v>46256.17152777778</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -5287,16 +5283,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" s="1" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5308,26 +5304,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RCC PASSION</t>
+          <t>COMET ACE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9453107</t>
+          <t>9182356</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46245.31666666667</v>
+        <v>46245.31458333333</v>
       </c>
       <c r="G82" s="1" t="n">
         <v>46339.2625</v>
@@ -5345,7 +5341,7 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5357,29 +5353,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MORNING CARA</t>
+          <t>TRANS FUTURE 6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9574092</t>
+          <t>9326081</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OO635</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46245.52361111111</v>
+        <v>46257.43541666667</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46339.2625</v>
+        <v>46258.17152777778</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -5388,13 +5384,17 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="O83" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <v>46258</v>
+      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5406,26 +5406,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AAL HONG KONG</t>
+          <t>MORNING CARA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9498468</t>
+          <t>9574092</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>OO635</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46245.52152777778</v>
+        <v>46245.52361111111</v>
       </c>
       <c r="G84" s="1" t="n">
         <v>46339.2625</v>
@@ -5443,7 +5443,7 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5455,29 +5455,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRANS FUTURE 6</t>
+          <t>TRANS FUTURE 7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9326081</t>
+          <t>9326093</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46257.43541666667</v>
+        <v>46242.5125</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46258.17152777778</v>
+        <v>46243.0625</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -5487,16 +5487,16 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" s="1" t="n">
-        <v>46258</v>
+        <v>46243</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46258</v>
+        <v>46243</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5508,29 +5508,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DREAM ORCHID</t>
+          <t>PATARA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9360568</t>
+          <t>9491898</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>004</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>004</t>
         </is>
       </c>
       <c r="F86" s="1" t="n">
-        <v>46245.84027777778</v>
+        <v>46245.31875</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46247.03819444445</v>
+        <v>46363.2625</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -5539,17 +5539,13 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="P86" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5561,29 +5557,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TALISMAN</t>
+          <t>HEROIC LEADER</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9191319</t>
+          <t>9441570</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EF611</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46243.01875</v>
+        <v>46253.04513888889</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46247.45208333333</v>
+        <v>46254.07986111111</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -5593,16 +5589,16 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-26 01:29:36</t>
+          <t>2026-08-26 06:00:30</t>
         </is>
       </c>
     </row>
@@ -5614,29 +5610,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KANG QIAN KOU</t>
+          <t>SWIFT ACE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9990284</t>
+          <t>9338838</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F88" s="1" t="n">
-        <v>46241.29861111111</v>
+        <v>46242.32916666667</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46242.26875</v>
+        <v>46243.04027777778</v>
       </c>
       <c r="H88"